--- a/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
@@ -589,19 +589,19 @@
         <v>6.793188115614059</v>
       </c>
       <c r="C2" t="n">
-        <v>6.66658857128015</v>
+        <v>6.666588571280143</v>
       </c>
       <c r="D2" t="n">
-        <v>6.711126719326204</v>
+        <v>6.711126719326201</v>
       </c>
       <c r="E2" t="n">
-        <v>4.467856115673328</v>
+        <v>4.467856115673325</v>
       </c>
       <c r="F2" t="n">
-        <v>6.698080792176478</v>
+        <v>6.698080792176471</v>
       </c>
       <c r="G2" t="n">
-        <v>6.89721611579163</v>
+        <v>6.897216115791625</v>
       </c>
       <c r="H2" t="n">
         <v>6.793188115614059</v>
@@ -610,7 +610,7 @@
         <v>6.793188115614059</v>
       </c>
       <c r="J2" t="n">
-        <v>6.786669121160364</v>
+        <v>6.786669121160362</v>
       </c>
       <c r="K2" t="n">
         <v>6.793188115614059</v>
@@ -619,10 +619,10 @@
         <v>6.793188115614059</v>
       </c>
       <c r="M2" t="n">
-        <v>6.863347580586046</v>
+        <v>6.863347580586042</v>
       </c>
       <c r="N2" t="n">
-        <v>6.76500442060812</v>
+        <v>6.765004420608118</v>
       </c>
       <c r="O2" t="n">
         <v>6.793188115614059</v>
@@ -646,7 +646,7 @@
         <v>6.793188115614059</v>
       </c>
       <c r="V2" t="n">
-        <v>6.889319071582013</v>
+        <v>6.889319071582008</v>
       </c>
       <c r="W2" t="n">
         <v>6.793188115614059</v>
@@ -658,7 +658,7 @@
         <v>6.793188115614059</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.734506348947472</v>
+        <v>6.73450634894747</v>
       </c>
       <c r="AA2" t="n">
         <v>6.793188115614059</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="C3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="D3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="E3" t="n">
         <v>10.74493854104783</v>
       </c>
       <c r="F3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="G3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="H3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="I3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="J3" t="n">
         <v>12.97679796516363</v>
       </c>
       <c r="K3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="L3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="M3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="N3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="O3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="P3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="R3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="S3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="T3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="U3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="V3" t="n">
         <v>13.18772375988154</v>
       </c>
       <c r="W3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="X3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.98331770662437</v>
+        <v>12.98331770662436</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.03110534504761</v>
+        <v>38.03110534504762</v>
       </c>
       <c r="C4" t="n">
         <v>17.77332380704205</v>
       </c>
       <c r="D4" t="n">
-        <v>31.55256812557809</v>
+        <v>31.55256812557803</v>
       </c>
       <c r="E4" t="n">
-        <v>18.52814252967908</v>
+        <v>18.52814252967902</v>
       </c>
       <c r="F4" t="n">
-        <v>28.14110336467327</v>
+        <v>28.14110336467316</v>
       </c>
       <c r="G4" t="n">
-        <v>80.45138854235765</v>
+        <v>80.45138854235751</v>
       </c>
       <c r="H4" t="n">
         <v>55.5550173129697</v>
       </c>
       <c r="I4" t="n">
-        <v>30.50991311292861</v>
+        <v>30.50991311292854</v>
       </c>
       <c r="J4" t="n">
-        <v>52.73844678466047</v>
+        <v>52.73844678466044</v>
       </c>
       <c r="K4" t="n">
-        <v>44.26161426064098</v>
+        <v>44.26161426064099</v>
       </c>
       <c r="L4" t="n">
-        <v>53.95829175722015</v>
+        <v>53.9582917572202</v>
       </c>
       <c r="M4" t="n">
-        <v>78.59902724133248</v>
+        <v>78.59902724133237</v>
       </c>
       <c r="N4" t="n">
-        <v>59.31997227371523</v>
+        <v>59.31997227371517</v>
       </c>
       <c r="O4" t="n">
-        <v>37.92724035278579</v>
+        <v>37.92724035278569</v>
       </c>
       <c r="P4" t="n">
-        <v>42.51340532905363</v>
+        <v>42.5134053290536</v>
       </c>
       <c r="Q4" t="n">
-        <v>35.38529039052575</v>
+        <v>35.38529039052565</v>
       </c>
       <c r="R4" t="n">
-        <v>34.92015209149178</v>
+        <v>34.92015209149181</v>
       </c>
       <c r="S4" t="n">
-        <v>54.73399303992566</v>
+        <v>54.7339930399256</v>
       </c>
       <c r="T4" t="n">
-        <v>44.04824146874218</v>
+        <v>44.04824146874214</v>
       </c>
       <c r="U4" t="n">
-        <v>59.31997227371524</v>
+        <v>59.31997227371513</v>
       </c>
       <c r="V4" t="n">
-        <v>22.16167367233821</v>
+        <v>22.16167367233812</v>
       </c>
       <c r="W4" t="n">
-        <v>56.18257209062274</v>
+        <v>56.18257209062278</v>
       </c>
       <c r="X4" t="n">
-        <v>42.12469711976208</v>
+        <v>42.12469711976205</v>
       </c>
       <c r="Y4" t="n">
-        <v>40.63448932274886</v>
+        <v>40.63448932274873</v>
       </c>
       <c r="Z4" t="n">
-        <v>35.32834754424353</v>
+        <v>35.32834754424344</v>
       </c>
       <c r="AA4" t="n">
-        <v>51.95598742279979</v>
+        <v>51.95598742279972</v>
       </c>
       <c r="AB4" t="n">
-        <v>65.58356995902116</v>
+        <v>65.58356995902105</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="C5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="D5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="E5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="F5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="G5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="H5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="I5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="J5" t="n">
-        <v>1.247915134413419</v>
+        <v>1.247915134413412</v>
       </c>
       <c r="K5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="L5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="M5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="N5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="O5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="P5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="R5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="S5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="T5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="U5" t="n">
-        <v>1.219043091451987</v>
+        <v>1.219043091451979</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23318082068737</v>
+        <v>1.233180820687364</v>
       </c>
       <c r="W5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="X5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.219043091451987</v>
+        <v>1.219043091451979</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.250583431946773</v>
+        <v>1.250583431946765</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.250583431946772</v>
+        <v>1.250583431946765</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.419428390431674</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="C6" t="n">
-        <v>2.091802999612557</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="D6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="E6" t="n">
-        <v>2.091802999612557</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="F6" t="n">
-        <v>1.419428390431674</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="G6" t="n">
-        <v>1.419428390431674</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="H6" t="n">
-        <v>2.091802999612557</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="I6" t="n">
-        <v>2.091802999612557</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="J6" t="n">
-        <v>1.416760092898292</v>
+        <v>2.089134702079196</v>
       </c>
       <c r="K6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="L6" t="n">
-        <v>2.091802999612557</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="M6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="N6" t="n">
-        <v>1.425769145113629</v>
+        <v>1.425769145113622</v>
       </c>
       <c r="O6" t="n">
-        <v>2.126315783288431</v>
+        <v>2.126315783288426</v>
       </c>
       <c r="P6" t="n">
-        <v>2.126321047023243</v>
+        <v>2.12632104702324</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="R6" t="n">
-        <v>2.091802999612557</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="S6" t="n">
-        <v>2.091802999612557</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="T6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="U6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="V6" t="n">
-        <v>2.074400388353153</v>
+        <v>2.074400388353145</v>
       </c>
       <c r="W6" t="n">
-        <v>1.454088070746186</v>
+        <v>2.126319111443491</v>
       </c>
       <c r="X6" t="n">
-        <v>2.091802999612557</v>
+        <v>2.09180299961255</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.438903948983367</v>
+        <v>1.438903948983397</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.419428390431674</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.091802999612557</v>
+        <v>1.419428390431679</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.432967499020793</v>
+        <v>1.432967499020789</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="C7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="D7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="E7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="F7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="G7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="H7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="I7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0425542948178</v>
+        <v>2.042554294817798</v>
       </c>
       <c r="K7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="L7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="M7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="N7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="O7" t="n">
-        <v>2.043040719789315</v>
+        <v>2.04304071978931</v>
       </c>
       <c r="P7" t="n">
-        <v>2.043040719789315</v>
+        <v>2.04304071978931</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="R7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="S7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="T7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="U7" t="n">
         <v>2.043599069941398</v>
       </c>
       <c r="V7" t="n">
-        <v>2.027819981091755</v>
+        <v>2.027819981091751</v>
       </c>
       <c r="W7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="X7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.045222592351155</v>
+        <v>2.045222592351152</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.405031136046866</v>
+        <v>2.405031136046858</v>
       </c>
       <c r="C8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="D8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="E8" t="n">
-        <v>3.317391578442232</v>
+        <v>2.831586555943328</v>
       </c>
       <c r="F8" t="n">
-        <v>2.547166229915927</v>
+        <v>2.547166229915918</v>
       </c>
       <c r="G8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.506575459603263</v>
       </c>
       <c r="H8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="I8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="J8" t="n">
-        <v>3.31472328090888</v>
+        <v>3.314723280908863</v>
       </c>
       <c r="K8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="L8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="M8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442286</v>
       </c>
       <c r="N8" t="n">
-        <v>2.610159600846876</v>
+        <v>2.610159600846867</v>
       </c>
       <c r="O8" t="n">
-        <v>2.804513088756447</v>
+        <v>2.80451308875644</v>
       </c>
       <c r="P8" t="n">
-        <v>2.756872352665842</v>
+        <v>2.756872352665834</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.225731485674329</v>
+        <v>2.225731485674326</v>
       </c>
       <c r="R8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="S8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="T8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="U8" t="n">
-        <v>2.756378773026007</v>
+        <v>2.872513330932214</v>
       </c>
       <c r="V8" t="n">
-        <v>3.299988967182823</v>
+        <v>3.051104365061584</v>
       </c>
       <c r="W8" t="n">
-        <v>3.317570882780407</v>
+        <v>3.317570882780395</v>
       </c>
       <c r="X8" t="n">
-        <v>2.30935113272086</v>
+        <v>2.309351132720853</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.225271036390712</v>
+        <v>4.225271036390696</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.317391578442232</v>
+        <v>2.388083572476103</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.317391578442232</v>
+        <v>3.317391578442217</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.270428350277218</v>
+        <v>4.270428350277204</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.561688152631879</v>
+        <v>4.561688152631877</v>
       </c>
       <c r="C9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="D9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="E9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.325925153670845</v>
       </c>
       <c r="F9" t="n">
-        <v>5.555230389891952</v>
+        <v>3.264843929164174</v>
       </c>
       <c r="G9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230727323246</v>
       </c>
       <c r="H9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="I9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="J9" t="n">
-        <v>5.552562092358599</v>
+        <v>5.552562092358595</v>
       </c>
       <c r="K9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="L9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="M9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="N9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="O9" t="n">
-        <v>5.884489435643016</v>
+        <v>5.884489435643009</v>
       </c>
       <c r="P9" t="n">
-        <v>5.956097555574507</v>
+        <v>5.956097555574503</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.555230727323249</v>
+        <v>5.555230727323246</v>
       </c>
       <c r="R9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="S9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="T9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="U9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="V9" t="n">
-        <v>5.537827778632547</v>
+        <v>6.68435345491208</v>
       </c>
       <c r="W9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="X9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.555230389891952</v>
+        <v>4.95621290403725</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.555230389891952</v>
+        <v>5.555230389891945</v>
       </c>
     </row>
     <row r="10">
@@ -1299,13 +1299,13 @@
         <v>12.39923332047777</v>
       </c>
       <c r="E10" t="n">
-        <v>10.39090073945233</v>
+        <v>10.39090073945232</v>
       </c>
       <c r="F10" t="n">
         <v>12.47813147287067</v>
       </c>
       <c r="G10" t="n">
-        <v>11.28395054203786</v>
+        <v>11.28395054203785</v>
       </c>
       <c r="H10" t="n">
         <v>11.98330130994829</v>
@@ -1323,22 +1323,22 @@
         <v>11.90323338940559</v>
       </c>
       <c r="M10" t="n">
-        <v>11.51319808970032</v>
+        <v>11.51319808970031</v>
       </c>
       <c r="N10" t="n">
-        <v>12.07983344401308</v>
+        <v>12.07983344401307</v>
       </c>
       <c r="O10" t="n">
-        <v>12.15188003800938</v>
+        <v>12.15188003800937</v>
       </c>
       <c r="P10" t="n">
-        <v>12.08663572798882</v>
+        <v>12.08663572798881</v>
       </c>
       <c r="Q10" t="n">
         <v>12.30987971349775</v>
       </c>
       <c r="R10" t="n">
-        <v>12.35169112586318</v>
+        <v>12.35169112586317</v>
       </c>
       <c r="S10" t="n">
         <v>11.83955230026547</v>
@@ -1378,85 +1378,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.423157172100459</v>
+        <v>6.423157172100458</v>
       </c>
       <c r="C11" t="n">
-        <v>6.519360254427228</v>
+        <v>6.519360254427223</v>
       </c>
       <c r="D11" t="n">
-        <v>6.445366462263009</v>
+        <v>6.445366462263006</v>
       </c>
       <c r="E11" t="n">
-        <v>4.306767787695844</v>
+        <v>4.306767787695841</v>
       </c>
       <c r="F11" t="n">
-        <v>6.468219445885541</v>
+        <v>6.468219445885535</v>
       </c>
       <c r="G11" t="n">
-        <v>6.123998640342943</v>
+        <v>6.12399864034294</v>
       </c>
       <c r="H11" t="n">
         <v>6.338177468263281</v>
       </c>
       <c r="I11" t="n">
-        <v>6.539804941019763</v>
+        <v>6.539804941019759</v>
       </c>
       <c r="J11" t="n">
-        <v>6.296915165430073</v>
+        <v>6.296915165430071</v>
       </c>
       <c r="K11" t="n">
-        <v>6.412708497499719</v>
+        <v>6.412708497499718</v>
       </c>
       <c r="L11" t="n">
-        <v>6.301746309255029</v>
+        <v>6.301746309255027</v>
       </c>
       <c r="M11" t="n">
-        <v>6.194438469892355</v>
+        <v>6.194438469892354</v>
       </c>
       <c r="N11" t="n">
         <v>6.35391620188647</v>
       </c>
       <c r="O11" t="n">
-        <v>6.414881326759602</v>
+        <v>6.414881326759601</v>
       </c>
       <c r="P11" t="n">
-        <v>6.385194957778974</v>
+        <v>6.38519495777897</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.486771682621908</v>
+        <v>6.486771682621913</v>
       </c>
       <c r="R11" t="n">
-        <v>6.505796008493239</v>
+        <v>6.505796008493241</v>
       </c>
       <c r="S11" t="n">
         <v>6.272771210756687</v>
       </c>
       <c r="T11" t="n">
-        <v>6.419597138316814</v>
+        <v>6.419597138316816</v>
       </c>
       <c r="U11" t="n">
-        <v>6.240388145986508</v>
+        <v>6.240388145986507</v>
       </c>
       <c r="V11" t="n">
-        <v>6.681175379903637</v>
+        <v>6.681175379903632</v>
       </c>
       <c r="W11" t="n">
-        <v>6.28563590262964</v>
+        <v>6.285635902629641</v>
       </c>
       <c r="X11" t="n">
-        <v>6.42957988859978</v>
+        <v>6.429579888599777</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.429540659610299</v>
+        <v>6.429540659610301</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.40166600593967</v>
+        <v>6.401666005939668</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.328157847400689</v>
+        <v>6.328157847400686</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.255154370984905</v>
+        <v>6.255154370984904</v>
       </c>
     </row>
   </sheetData>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.354594288751458</v>
+        <v>6.354594288751455</v>
       </c>
       <c r="C2" t="n">
-        <v>6.36063304082227</v>
+        <v>6.360633040822271</v>
       </c>
       <c r="D2" t="n">
         <v>6.372331478905728</v>
@@ -1637,22 +1637,22 @@
         <v>6.314921044293468</v>
       </c>
       <c r="G2" t="n">
-        <v>6.391468243888166</v>
+        <v>6.391468243888164</v>
       </c>
       <c r="H2" t="n">
-        <v>6.392439834753098</v>
+        <v>6.3924398347531</v>
       </c>
       <c r="I2" t="n">
-        <v>6.361759008198532</v>
+        <v>6.361759008198529</v>
       </c>
       <c r="J2" t="n">
-        <v>6.377976798020953</v>
+        <v>6.377976798020951</v>
       </c>
       <c r="K2" t="n">
         <v>6.36176672294422</v>
       </c>
       <c r="L2" t="n">
-        <v>6.269841850069467</v>
+        <v>6.269841850069465</v>
       </c>
       <c r="M2" t="n">
         <v>6.354874249983736</v>
@@ -1661,46 +1661,46 @@
         <v>6.363182441258933</v>
       </c>
       <c r="O2" t="n">
-        <v>6.329253865989523</v>
+        <v>6.329253865989524</v>
       </c>
       <c r="P2" t="n">
-        <v>6.35615503431262</v>
+        <v>6.356155034312617</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.369164028089937</v>
+        <v>6.369164028089936</v>
       </c>
       <c r="R2" t="n">
-        <v>6.224061327766949</v>
+        <v>6.22406132776695</v>
       </c>
       <c r="S2" t="n">
-        <v>6.32723270432479</v>
+        <v>6.327232704324794</v>
       </c>
       <c r="T2" t="n">
         <v>6.332780575113662</v>
       </c>
       <c r="U2" t="n">
-        <v>6.391065213718531</v>
+        <v>6.391065213718536</v>
       </c>
       <c r="V2" t="n">
-        <v>6.62763158663988</v>
+        <v>6.627631586639879</v>
       </c>
       <c r="W2" t="n">
-        <v>6.512544112707496</v>
+        <v>6.512544112707493</v>
       </c>
       <c r="X2" t="n">
-        <v>6.556558104537376</v>
+        <v>6.556558104537378</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.466271787084527</v>
+        <v>6.466271787084528</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.394564999099882</v>
+        <v>6.394564999099881</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.517337421337727</v>
+        <v>6.517337421337726</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.380486227046917</v>
+        <v>6.380486227046916</v>
       </c>
     </row>
     <row r="3">
@@ -1734,7 +1734,7 @@
         <v>12.73425973525076</v>
       </c>
       <c r="J3" t="n">
-        <v>12.73448825500347</v>
+        <v>12.73448825500346</v>
       </c>
       <c r="K3" t="n">
         <v>12.7338708723732</v>
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.538392659490794</v>
+        <v>-1.538392659490799</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06724106455782763</v>
+        <v>0.06724106455782675</v>
       </c>
       <c r="D4" t="n">
-        <v>2.708269239841195</v>
+        <v>2.708269239841201</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06588679213691506</v>
+        <v>-0.06588679213690973</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.69724824896631</v>
+        <v>-11.69724824896628</v>
       </c>
       <c r="G4" t="n">
-        <v>6.811809354933015</v>
+        <v>6.811809354932988</v>
       </c>
       <c r="H4" t="n">
-        <v>8.248206087407173</v>
+        <v>8.24820608740716</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03497954710397044</v>
+        <v>0.03497954710397844</v>
       </c>
       <c r="J4" t="n">
-        <v>3.757009519381518</v>
+        <v>3.757009519381517</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2967442845044137</v>
+        <v>0.2967442845044181</v>
       </c>
       <c r="L4" t="n">
-        <v>-20.67610508420404</v>
+        <v>-20.67610508420399</v>
       </c>
       <c r="M4" t="n">
         <v>-1.225449344759329</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.885579584479244</v>
+        <v>-6.885579584479225</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7861713097165696</v>
+        <v>-0.7861713097165659</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.870813107215325</v>
+        <v>1.870813107215328</v>
       </c>
       <c r="R4" t="n">
-        <v>-37.30130385605318</v>
+        <v>-37.30130385605314</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.632998150922758</v>
+        <v>-7.632998150922743</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.281128281357773</v>
+        <v>-7.281128281357775</v>
       </c>
       <c r="U4" t="n">
-        <v>6.077238547301321</v>
+        <v>6.077238547301317</v>
       </c>
       <c r="V4" t="n">
-        <v>9.481520008601656</v>
+        <v>9.481520008601661</v>
       </c>
       <c r="W4" t="n">
-        <v>37.95424434862475</v>
+        <v>37.95424434862471</v>
       </c>
       <c r="X4" t="n">
-        <v>46.87867498661542</v>
+        <v>46.8786749866153</v>
       </c>
       <c r="Y4" t="n">
-        <v>27.60042445553592</v>
+        <v>27.60042445553593</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.240846637160112</v>
+        <v>7.240846637160119</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.72685472290082</v>
+        <v>39.72685472290087</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.500504105318874</v>
+        <v>2.500504105318884</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6832150584158553</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6819610087322555</v>
+        <v>0.6819610087322553</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="N5" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6522447312356474</v>
+        <v>0.6522447312356439</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6748332397524707</v>
+        <v>0.6748332397524711</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6832150584158565</v>
+        <v>0.6832150584158588</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6522447312356474</v>
+        <v>0.6522447312356442</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6832150584158557</v>
+        <v>0.6832150584158589</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6832150584158555</v>
+        <v>0.6832150584158566</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="C6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="D6" t="n">
-        <v>1.040463386578261</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="E6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="F6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="J6" t="n">
-        <v>0.764975101703489</v>
+        <v>1.03920933689466</v>
       </c>
       <c r="K6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="N6" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O6" t="n">
-        <v>1.077014833345457</v>
+        <v>1.077014833345459</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7536708404623154</v>
+        <v>1.076593810636813</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.040463386578261</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="T6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7662291513870917</v>
+        <v>1.040463386578269</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7578473327237085</v>
+        <v>1.032081567914878</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7910316682764523</v>
+        <v>0.7910316682764534</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7662291513870917</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7798755794850871</v>
+        <v>0.7798755794850806</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.040463386578261</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7662291513870917</v>
+        <v>0.7662291513870974</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7673088678927261</v>
+        <v>0.7673088678927333</v>
       </c>
     </row>
     <row r="7">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="C7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="D7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="E7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="F7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="G7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="H7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="I7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="J7" t="n">
         <v>1.128112918920266</v>
       </c>
       <c r="K7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="L7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="M7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="N7" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O7" t="n">
-        <v>1.127474596491986</v>
+        <v>1.127474596491988</v>
       </c>
       <c r="P7" t="n">
-        <v>1.127474596491986</v>
+        <v>1.127474596491988</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="R7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="S7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="T7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="U7" t="n">
-        <v>1.119508700437931</v>
+        <v>1.119508700437935</v>
       </c>
       <c r="V7" t="n">
         <v>1.120985149940481</v>
       </c>
       <c r="W7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="X7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.129366968603865</v>
+        <v>1.129366968603867</v>
       </c>
     </row>
     <row r="8">
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.245773778521758</v>
+        <v>1.245773778521761</v>
       </c>
       <c r="C8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="D8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="E8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.459161807344749</v>
       </c>
       <c r="F8" t="n">
-        <v>1.316878085457713</v>
+        <v>1.316878085457719</v>
       </c>
       <c r="G8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.796830829679709</v>
       </c>
       <c r="H8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="I8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="J8" t="n">
-        <v>1.70093591131857</v>
+        <v>1.700935911318579</v>
       </c>
       <c r="K8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="L8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="M8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961001551</v>
       </c>
       <c r="N8" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O8" t="n">
-        <v>1.445618071741402</v>
+        <v>1.445618071741405</v>
       </c>
       <c r="P8" t="n">
-        <v>1.421785382515115</v>
+        <v>1.421785382515116</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.156077581581129</v>
+        <v>1.156077581581135</v>
       </c>
       <c r="R8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="S8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="T8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="U8" t="n">
-        <v>1.415538498302751</v>
+        <v>1.473245939922697</v>
       </c>
       <c r="V8" t="n">
-        <v>1.693808142338789</v>
+        <v>1.562253666774435</v>
       </c>
       <c r="W8" t="n">
-        <v>1.702279659461425</v>
+        <v>1.702279659461428</v>
       </c>
       <c r="X8" t="n">
-        <v>1.197909031374151</v>
+        <v>1.197909031374156</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.145433335814586</v>
+        <v>2.14543333581459</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.237295613642539</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.702189961002167</v>
+        <v>1.702189961002181</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.178954828130765</v>
+        <v>2.178954828130768</v>
       </c>
     </row>
     <row r="9">
@@ -2238,85 +2238,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.553229218182917</v>
+        <v>1.553229218182912</v>
       </c>
       <c r="C9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="D9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="E9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.771440977068276</v>
       </c>
       <c r="F9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.182942698924459</v>
       </c>
       <c r="G9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.836914347869336</v>
       </c>
       <c r="H9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="I9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="J9" t="n">
-        <v>1.835660063746305</v>
+        <v>1.835660063746295</v>
       </c>
       <c r="K9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="L9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="M9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="N9" t="n">
-        <v>0.365007306300656</v>
+        <v>0.3650073063006674</v>
       </c>
       <c r="O9" t="n">
-        <v>1.93092722839349</v>
+        <v>1.930927228393485</v>
       </c>
       <c r="P9" t="n">
-        <v>1.951373416918067</v>
+        <v>1.951373416918066</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.836914347869329</v>
+        <v>1.836914347869336</v>
       </c>
       <c r="R9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="S9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="T9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="U9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="V9" t="n">
-        <v>1.828532294766525</v>
+        <v>2.155898876613892</v>
       </c>
       <c r="W9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="X9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.665877440934417</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.836914113429903</v>
+        <v>1.8369141134299</v>
       </c>
     </row>
     <row r="10">
@@ -2326,16 +2326,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.79205871054495</v>
+        <v>12.79205871054496</v>
       </c>
       <c r="C10" t="n">
-        <v>12.74934542192471</v>
+        <v>12.7493454219247</v>
       </c>
       <c r="D10" t="n">
-        <v>12.68728167015162</v>
+        <v>12.68728167015163</v>
       </c>
       <c r="E10" t="n">
-        <v>10.61247380706864</v>
+        <v>10.61247380706865</v>
       </c>
       <c r="F10" t="n">
         <v>13.01784719903909</v>
@@ -2347,7 +2347,7 @@
         <v>12.57061179693179</v>
       </c>
       <c r="I10" t="n">
-        <v>12.74918341203685</v>
+        <v>12.74918341203686</v>
       </c>
       <c r="J10" t="n">
         <v>12.65453485432618</v>
@@ -2404,7 +2404,7 @@
         <v>11.8318336552217</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.70547453758018</v>
+        <v>12.70547453758019</v>
       </c>
     </row>
     <row r="11">
@@ -2414,85 +2414,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.380893006704718</v>
+        <v>6.380893006704719</v>
       </c>
       <c r="C11" t="n">
-        <v>6.367961065334557</v>
+        <v>6.367961065334556</v>
       </c>
       <c r="D11" t="n">
-        <v>6.35095630957541</v>
+        <v>6.350956309575411</v>
       </c>
       <c r="E11" t="n">
         <v>4.261424706935838</v>
       </c>
       <c r="F11" t="n">
-        <v>6.444264158822214</v>
+        <v>6.444264158822213</v>
       </c>
       <c r="G11" t="n">
-        <v>6.317191217413564</v>
+        <v>6.317191217413563</v>
       </c>
       <c r="H11" t="n">
-        <v>6.317979501302935</v>
+        <v>6.317979501302933</v>
       </c>
       <c r="I11" t="n">
-        <v>6.368549328695137</v>
+        <v>6.368549328695133</v>
       </c>
       <c r="J11" t="n">
-        <v>6.341597745916419</v>
+        <v>6.341597745916418</v>
       </c>
       <c r="K11" t="n">
-        <v>6.36760950474233</v>
+        <v>6.367609504742328</v>
       </c>
       <c r="L11" t="n">
         <v>6.523953336733824</v>
       </c>
       <c r="M11" t="n">
-        <v>6.375648829276334</v>
+        <v>6.375648829276333</v>
       </c>
       <c r="N11" t="n">
         <v>6.366202808624633</v>
       </c>
       <c r="O11" t="n">
-        <v>6.422028948340804</v>
+        <v>6.422028948340805</v>
       </c>
       <c r="P11" t="n">
-        <v>6.374088573446321</v>
+        <v>6.374088573446318</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.356172617023155</v>
+        <v>6.356172617023156</v>
       </c>
       <c r="R11" t="n">
-        <v>6.601696644254174</v>
+        <v>6.601696644254176</v>
       </c>
       <c r="S11" t="n">
-        <v>6.427287293357598</v>
+        <v>6.427287293357599</v>
       </c>
       <c r="T11" t="n">
-        <v>6.413620163202603</v>
+        <v>6.413620163202604</v>
       </c>
       <c r="U11" t="n">
-        <v>6.326564671702216</v>
+        <v>6.326564671702219</v>
       </c>
       <c r="V11" t="n">
-        <v>6.521955893601693</v>
+        <v>6.52195589360169</v>
       </c>
       <c r="W11" t="n">
-        <v>6.114475164863853</v>
+        <v>6.11447516486385</v>
       </c>
       <c r="X11" t="n">
-        <v>6.05132846684705</v>
+        <v>6.051328466847049</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.184578965161796</v>
+        <v>6.184578965161799</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.312536002625137</v>
+        <v>6.31253600262514</v>
       </c>
       <c r="AA11" t="n">
         <v>6.106730679063221</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.362665283199405</v>
+        <v>6.362665283199402</v>
       </c>
     </row>
   </sheetData>
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="C2" t="n">
-        <v>6.62353214744835</v>
+        <v>6.623532147448344</v>
       </c>
       <c r="D2" t="n">
         <v>6.68759420187895</v>
       </c>
       <c r="E2" t="n">
-        <v>4.452484687448869</v>
+        <v>4.452484687448873</v>
       </c>
       <c r="F2" t="n">
-        <v>6.649470553768966</v>
+        <v>6.649470553768963</v>
       </c>
       <c r="G2" t="n">
         <v>6.859488187886983</v>
       </c>
       <c r="H2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="I2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="J2" t="n">
-        <v>6.751843462716175</v>
+        <v>6.751843462716176</v>
       </c>
       <c r="K2" t="n">
-        <v>6.758790681461963</v>
+        <v>6.75879068146196</v>
       </c>
       <c r="L2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="M2" t="n">
-        <v>6.815536584284085</v>
+        <v>6.815536584284086</v>
       </c>
       <c r="N2" t="n">
-        <v>6.71156283791831</v>
+        <v>6.711562837918307</v>
       </c>
       <c r="O2" t="n">
-        <v>6.758344684835491</v>
+        <v>6.758344684835487</v>
       </c>
       <c r="P2" t="n">
-        <v>6.758825554912993</v>
+        <v>6.75882555491299</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.758977003543813</v>
+        <v>6.758977003543809</v>
       </c>
       <c r="R2" t="n">
-        <v>6.758949978612095</v>
+        <v>6.75894997861209</v>
       </c>
       <c r="S2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="T2" t="n">
-        <v>6.758707100471256</v>
+        <v>6.758707100471254</v>
       </c>
       <c r="U2" t="n">
-        <v>6.759616072945151</v>
+        <v>6.759616072945146</v>
       </c>
       <c r="V2" t="n">
-        <v>6.825203662515243</v>
+        <v>6.825203662515244</v>
       </c>
       <c r="W2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="X2" t="n">
-        <v>6.759509361274514</v>
+        <v>6.75950936127451</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.757513343240711</v>
+        <v>6.757513343240708</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.681940082026447</v>
+        <v>6.681940082026448</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.758986105314787</v>
+        <v>6.758986105314783</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.76847292678239</v>
+        <v>6.768472926782387</v>
       </c>
     </row>
     <row r="3">
@@ -2755,7 +2755,7 @@
         <v>12.95113016938281</v>
       </c>
       <c r="E3" t="n">
-        <v>10.73138134116351</v>
+        <v>10.73138134116352</v>
       </c>
       <c r="F3" t="n">
         <v>12.95076657405313</v>
@@ -2779,7 +2779,7 @@
         <v>12.95113016938281</v>
       </c>
       <c r="M3" t="n">
-        <v>12.95087839198564</v>
+        <v>12.95087839198563</v>
       </c>
       <c r="N3" t="n">
         <v>12.95113016938281</v>
@@ -2791,7 +2791,7 @@
         <v>12.95095447839598</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.95112020923294</v>
+        <v>12.95112020923293</v>
       </c>
       <c r="R3" t="n">
         <v>12.95109063563299</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.17481096180474</v>
+        <v>29.17481096180459</v>
       </c>
       <c r="C4" t="n">
-        <v>13.50407966432559</v>
+        <v>13.50407966432557</v>
       </c>
       <c r="D4" t="n">
-        <v>31.93350463499363</v>
+        <v>31.9335046349936</v>
       </c>
       <c r="E4" t="n">
         <v>16.82833906348402</v>
       </c>
       <c r="F4" t="n">
-        <v>21.15780207386002</v>
+        <v>21.15780207386004</v>
       </c>
       <c r="G4" t="n">
-        <v>73.08848365391165</v>
+        <v>73.08848365391152</v>
       </c>
       <c r="H4" t="n">
-        <v>41.97842721653759</v>
+        <v>41.97842721653772</v>
       </c>
       <c r="I4" t="n">
         <v>21.76850023411929</v>
       </c>
       <c r="J4" t="n">
-        <v>48.49681910758071</v>
+        <v>48.49681910758069</v>
       </c>
       <c r="K4" t="n">
-        <v>33.85261223609241</v>
+        <v>33.85261223609245</v>
       </c>
       <c r="L4" t="n">
-        <v>45.66188031337887</v>
+        <v>45.66188031337891</v>
       </c>
       <c r="M4" t="n">
-        <v>68.68946213767411</v>
+        <v>68.68946213767423</v>
       </c>
       <c r="N4" t="n">
-        <v>47.26084469223843</v>
+        <v>47.26084469223834</v>
       </c>
       <c r="O4" t="n">
         <v>30.03995954633319</v>
       </c>
       <c r="P4" t="n">
-        <v>45.60339971178606</v>
+        <v>45.60339971178612</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.57587231229367</v>
+        <v>27.57587231229371</v>
       </c>
       <c r="R4" t="n">
-        <v>27.53727536097669</v>
+        <v>27.53727536097675</v>
       </c>
       <c r="S4" t="n">
-        <v>49.29345973016185</v>
+        <v>49.29345973016203</v>
       </c>
       <c r="T4" t="n">
-        <v>32.43494051684129</v>
+        <v>32.43494051684127</v>
       </c>
       <c r="U4" t="n">
-        <v>47.26084469223843</v>
+        <v>47.26084469223834</v>
       </c>
       <c r="V4" t="n">
-        <v>14.00919872650368</v>
+        <v>14.00919872650367</v>
       </c>
       <c r="W4" t="n">
-        <v>55.25957397510713</v>
+        <v>55.2595739751071</v>
       </c>
       <c r="X4" t="n">
-        <v>41.84496292268697</v>
+        <v>41.84496292268698</v>
       </c>
       <c r="Y4" t="n">
-        <v>35.72912041545779</v>
+        <v>35.7291204154578</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.5337459270852</v>
+        <v>27.53374592708516</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.35771119519931</v>
+        <v>39.35771119519936</v>
       </c>
       <c r="AB4" t="n">
-        <v>60.26173363877872</v>
+        <v>60.26173363877862</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="C5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="D5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="E5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="F5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="G5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="H5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="I5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="J5" t="n">
-        <v>1.19611806670771</v>
+        <v>1.196118066707706</v>
       </c>
       <c r="K5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="L5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="M5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="N5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="O5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="P5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="R5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="S5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="T5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="U5" t="n">
-        <v>1.166472838078308</v>
+        <v>1.166472838078301</v>
       </c>
       <c r="V5" t="n">
-        <v>1.180642591238246</v>
+        <v>1.180642591238237</v>
       </c>
       <c r="W5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="X5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.166472838078308</v>
+        <v>1.166472838078301</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.198922951680812</v>
+        <v>1.198922951680806</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.198922951680813</v>
+        <v>1.198922951680805</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.9467825839289</v>
+        <v>1.341517903148443</v>
       </c>
       <c r="C6" t="n">
         <v>1.9467825839289</v>
       </c>
       <c r="D6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.9467825839289</v>
       </c>
       <c r="E6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.341517903148443</v>
       </c>
       <c r="F6" t="n">
+        <v>1.341517903148443</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.341517903148443</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.9467825839289</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>1.341517903148443</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.943977698955791</v>
+      </c>
+      <c r="K6" t="n">
         <v>1.9467825839289</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.341517903148446</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.341517903148446</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.943977698955798</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.341517903148446</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.341517903148443</v>
       </c>
       <c r="M6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.341517903148443</v>
       </c>
       <c r="N6" t="n">
-        <v>1.345405320215989</v>
+        <v>1.345405320216077</v>
       </c>
       <c r="O6" t="n">
-        <v>1.97730915503382</v>
+        <v>1.977309155033825</v>
       </c>
       <c r="P6" t="n">
-        <v>1.977258454410516</v>
+        <v>1.97725845441052</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.9467825839289</v>
       </c>
       <c r="R6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.9467825839289</v>
       </c>
       <c r="S6" t="n">
-        <v>1.341517903148446</v>
+        <v>1.9467825839289</v>
       </c>
       <c r="T6" t="n">
+        <v>1.341517903148443</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.341517903148443</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.928502223486329</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.977326928929724</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.9467825839289</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>1.355933607533463</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.9467825839289</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.928502223486335</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.977326928929722</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.341517903148446</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.355933607533483</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.341517903148446</v>
-      </c>
       <c r="AA6" t="n">
-        <v>1.9467825839289</v>
+        <v>1.341517903148443</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.353995530021429</v>
+        <v>1.353995530021433</v>
       </c>
     </row>
     <row r="7">
@@ -3122,7 +3122,7 @@
         <v>1.907981315236742</v>
       </c>
       <c r="J7" t="n">
-        <v>1.90517643026364</v>
+        <v>1.905176430263641</v>
       </c>
       <c r="K7" t="n">
         <v>1.907981315236742</v>
@@ -3137,10 +3137,10 @@
         <v>1.907981315236742</v>
       </c>
       <c r="O7" t="n">
-        <v>1.905941196919768</v>
+        <v>1.905941196919763</v>
       </c>
       <c r="P7" t="n">
-        <v>1.905941196919768</v>
+        <v>1.905941196919763</v>
       </c>
       <c r="Q7" t="n">
         <v>1.907981315236742</v>
@@ -3155,10 +3155,10 @@
         <v>1.907981315236742</v>
       </c>
       <c r="U7" t="n">
-        <v>1.906162666938792</v>
+        <v>1.906162666938793</v>
       </c>
       <c r="V7" t="n">
-        <v>1.889700954794176</v>
+        <v>1.889700954794171</v>
       </c>
       <c r="W7" t="n">
         <v>1.907981315236742</v>
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.226418123731921</v>
+        <v>2.226418123731918</v>
       </c>
       <c r="C8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="D8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="E8" t="n">
-        <v>3.039956758850439</v>
+        <v>2.60677143365554</v>
       </c>
       <c r="F8" t="n">
-        <v>2.353157934988084</v>
+        <v>2.353157934988078</v>
       </c>
       <c r="G8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.208649294507985</v>
       </c>
       <c r="H8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="I8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="J8" t="n">
-        <v>3.037151873877333</v>
+        <v>3.037151873877327</v>
       </c>
       <c r="K8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="L8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="M8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850399</v>
       </c>
       <c r="N8" t="n">
-        <v>2.40932821443377</v>
+        <v>2.40932821443376</v>
       </c>
       <c r="O8" t="n">
-        <v>2.582630413793732</v>
+        <v>2.582630413793721</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5401498571943</v>
+        <v>2.540149857194294</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.066539213975526</v>
+        <v>2.066539213975519</v>
       </c>
       <c r="R8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="S8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="T8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="U8" t="n">
-        <v>2.539508603647628</v>
+        <v>2.643051042706651</v>
       </c>
       <c r="V8" t="n">
-        <v>3.021676398407869</v>
+        <v>2.799513329497374</v>
       </c>
       <c r="W8" t="n">
-        <v>3.040116641918006</v>
+        <v>3.040116641918008</v>
       </c>
       <c r="X8" t="n">
-        <v>2.141101646050963</v>
+        <v>2.141101646050965</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.849133321794617</v>
+        <v>3.849133321794619</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.039956758850439</v>
+        <v>2.211306225963348</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.039956758850439</v>
+        <v>3.039956758850442</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.889765889681242</v>
+        <v>3.889765889681231</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.892407810907186</v>
+        <v>3.892407810907184</v>
       </c>
       <c r="C9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="D9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="E9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.519181055531464</v>
       </c>
       <c r="F9" t="n">
-        <v>4.707241012135277</v>
+        <v>2.828827716499191</v>
       </c>
       <c r="G9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241301519494</v>
       </c>
       <c r="H9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="J9" t="n">
-        <v>4.704436127162174</v>
+        <v>4.704436127162169</v>
       </c>
       <c r="K9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="L9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="M9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="N9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="O9" t="n">
-        <v>4.97727605337505</v>
+        <v>4.977276053375046</v>
       </c>
       <c r="P9" t="n">
-        <v>5.036003978887521</v>
+        <v>5.036003978887524</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.707241301519496</v>
+        <v>4.707241301519494</v>
       </c>
       <c r="R9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="S9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="T9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="U9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="V9" t="n">
-        <v>4.68896065169271</v>
+        <v>5.629259966828783</v>
       </c>
       <c r="W9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="X9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.215969164501375</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.707241012135277</v>
+        <v>4.707241012135276</v>
       </c>
     </row>
     <row r="10">
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.28581822106938</v>
+        <v>12.28581822106937</v>
       </c>
       <c r="C10" t="n">
-        <v>12.68690919330623</v>
+        <v>12.68690919330624</v>
       </c>
       <c r="D10" t="n">
         <v>12.31816219601444</v>
@@ -3377,7 +3377,7 @@
         <v>12.5411752487208</v>
       </c>
       <c r="G10" t="n">
-        <v>11.28582721677521</v>
+        <v>11.2858272167752</v>
       </c>
       <c r="H10" t="n">
         <v>12.14508930837992</v>
@@ -3392,19 +3392,19 @@
         <v>12.22361079844347</v>
       </c>
       <c r="L10" t="n">
-        <v>11.977413842645</v>
+        <v>11.97741384264499</v>
       </c>
       <c r="M10" t="n">
-        <v>11.57239034507896</v>
+        <v>11.57239034507895</v>
       </c>
       <c r="N10" t="n">
-        <v>12.17449002596748</v>
+        <v>12.17449002596747</v>
       </c>
       <c r="O10" t="n">
         <v>12.24537427758927</v>
       </c>
       <c r="P10" t="n">
-        <v>11.9170419597508</v>
+        <v>11.91704195975079</v>
       </c>
       <c r="Q10" t="n">
         <v>12.39182699732125</v>
@@ -3413,25 +3413,25 @@
         <v>12.42303272761559</v>
       </c>
       <c r="S10" t="n">
-        <v>11.84071151043524</v>
+        <v>11.84071151043523</v>
       </c>
       <c r="T10" t="n">
         <v>12.30674020626497</v>
       </c>
       <c r="U10" t="n">
-        <v>11.91948871622308</v>
+        <v>11.91948871622307</v>
       </c>
       <c r="V10" t="n">
         <v>12.83903017901943</v>
       </c>
       <c r="W10" t="n">
-        <v>11.77814225114898</v>
+        <v>11.77814225114897</v>
       </c>
       <c r="X10" t="n">
         <v>12.09811736141279</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.19233771482153</v>
+        <v>12.19233771482152</v>
       </c>
       <c r="Z10" t="n">
         <v>12.34221053991972</v>
@@ -3440,7 +3440,7 @@
         <v>12.12192851717846</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.80233873167644</v>
+        <v>11.80233873167645</v>
       </c>
     </row>
     <row r="11">
@@ -3450,85 +3450,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.456267048608794</v>
+        <v>6.45626704860879</v>
       </c>
       <c r="C11" t="n">
-        <v>6.50375430256733</v>
+        <v>6.503754302567328</v>
       </c>
       <c r="D11" t="n">
-        <v>6.399591756847093</v>
+        <v>6.399591756847091</v>
       </c>
       <c r="E11" t="n">
         <v>4.296332866332151</v>
       </c>
       <c r="F11" t="n">
-        <v>6.463105195452656</v>
+        <v>6.463105195452652</v>
       </c>
       <c r="G11" t="n">
-        <v>6.101820899416351</v>
+        <v>6.101820899416341</v>
       </c>
       <c r="H11" t="n">
-        <v>6.392234944858657</v>
+        <v>6.392234944858656</v>
       </c>
       <c r="I11" t="n">
-        <v>6.568579500279986</v>
+        <v>6.568579500279983</v>
       </c>
       <c r="J11" t="n">
-        <v>6.268517923639651</v>
+        <v>6.268517923639648</v>
       </c>
       <c r="K11" t="n">
         <v>6.427864352870895</v>
       </c>
       <c r="L11" t="n">
-        <v>6.315942073599259</v>
+        <v>6.315942073599256</v>
       </c>
       <c r="M11" t="n">
         <v>6.188320129960796</v>
       </c>
       <c r="N11" t="n">
-        <v>6.358189097659046</v>
+        <v>6.358189097659039</v>
       </c>
       <c r="O11" t="n">
-        <v>6.437542875069547</v>
+        <v>6.437542875069544</v>
       </c>
       <c r="P11" t="n">
-        <v>6.288392064045738</v>
+        <v>6.288392064045731</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.50449680976228</v>
+        <v>6.504496809762276</v>
       </c>
       <c r="R11" t="n">
-        <v>6.51868194764347</v>
+        <v>6.518681947643465</v>
       </c>
       <c r="S11" t="n">
-        <v>6.253742076799336</v>
+        <v>6.253742076799332</v>
       </c>
       <c r="T11" t="n">
-        <v>6.465646533339208</v>
+        <v>6.465646533339204</v>
       </c>
       <c r="U11" t="n">
-        <v>6.28990225675564</v>
+        <v>6.289902256755639</v>
       </c>
       <c r="V11" t="n">
         <v>6.684542552467437</v>
       </c>
       <c r="W11" t="n">
-        <v>6.225272864427689</v>
+        <v>6.225272864427685</v>
       </c>
       <c r="X11" t="n">
         <v>6.371125280724776</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.412993661984081</v>
+        <v>6.412993661984078</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.40490445631041</v>
+        <v>6.404904456310412</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.381696711052927</v>
+        <v>6.381696711052923</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.241045574470477</v>
+        <v>6.241045574470475</v>
       </c>
     </row>
   </sheetData>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="C2" t="n">
-        <v>6.611061361168417</v>
+        <v>6.611061361168421</v>
       </c>
       <c r="D2" t="n">
-        <v>6.682705294307056</v>
+        <v>6.682705294307058</v>
       </c>
       <c r="E2" t="n">
-        <v>4.441935661085712</v>
+        <v>4.441935661085713</v>
       </c>
       <c r="F2" t="n">
-        <v>6.612522237810526</v>
+        <v>6.612522237810528</v>
       </c>
       <c r="G2" t="n">
         <v>6.826052601708088</v>
       </c>
       <c r="H2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="I2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="J2" t="n">
-        <v>6.724631413388658</v>
+        <v>6.724631413388656</v>
       </c>
       <c r="K2" t="n">
-        <v>6.730301978625401</v>
+        <v>6.730301978625406</v>
       </c>
       <c r="L2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="M2" t="n">
-        <v>6.769370293148637</v>
+        <v>6.76937029314864</v>
       </c>
       <c r="N2" t="n">
         <v>6.664128289537047</v>
       </c>
       <c r="O2" t="n">
-        <v>6.729862903813733</v>
+        <v>6.729862903813738</v>
       </c>
       <c r="P2" t="n">
-        <v>6.730498178989508</v>
+        <v>6.730498178989513</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.730570071684935</v>
+        <v>6.73057007168494</v>
       </c>
       <c r="R2" t="n">
-        <v>6.731617449985388</v>
+        <v>6.731617449985394</v>
       </c>
       <c r="S2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="T2" t="n">
-        <v>6.729757506026041</v>
+        <v>6.729757506026046</v>
       </c>
       <c r="U2" t="n">
-        <v>6.731564048291894</v>
+        <v>6.731564048291899</v>
       </c>
       <c r="V2" t="n">
         <v>6.830877384291967</v>
       </c>
       <c r="W2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="X2" t="n">
-        <v>6.736824934700681</v>
+        <v>6.736824934700686</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.72880897278215</v>
+        <v>6.728808972782155</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.664221275060849</v>
+        <v>6.664221275060851</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.730579173455909</v>
+        <v>6.730579173455914</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.740065994923513</v>
+        <v>6.740065994923518</v>
       </c>
     </row>
     <row r="3">
@@ -3785,7 +3785,7 @@
         <v>12.93072293848464</v>
       </c>
       <c r="C3" t="n">
-        <v>12.92969918545532</v>
+        <v>12.92969918545533</v>
       </c>
       <c r="D3" t="n">
         <v>12.93072293848464</v>
@@ -3794,7 +3794,7 @@
         <v>10.72015269890902</v>
       </c>
       <c r="F3" t="n">
-        <v>12.93020975962852</v>
+        <v>12.93020975962853</v>
       </c>
       <c r="G3" t="n">
         <v>12.93051293357809</v>
@@ -3836,25 +3836,25 @@
         <v>12.93072293848464</v>
       </c>
       <c r="T3" t="n">
-        <v>12.92982378643167</v>
+        <v>12.92982378643168</v>
       </c>
       <c r="U3" t="n">
         <v>12.93180068751711</v>
       </c>
       <c r="V3" t="n">
-        <v>13.13472594421718</v>
+        <v>13.13472594421717</v>
       </c>
       <c r="W3" t="n">
         <v>12.93072293848464</v>
       </c>
       <c r="X3" t="n">
-        <v>12.93755768122915</v>
+        <v>12.93755768122916</v>
       </c>
       <c r="Y3" t="n">
         <v>12.9287858054361</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.93063148927714</v>
+        <v>12.93063148927715</v>
       </c>
       <c r="AA3" t="n">
         <v>12.93072293848464</v>
@@ -3876,79 +3876,79 @@
         <v>14.19228085306641</v>
       </c>
       <c r="D4" t="n">
-        <v>33.51557602403945</v>
+        <v>33.51557602403957</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9030546692483</v>
+        <v>15.90305466924834</v>
       </c>
       <c r="F4" t="n">
-        <v>15.13692951655219</v>
+        <v>15.13692951655216</v>
       </c>
       <c r="G4" t="n">
-        <v>63.88941428931211</v>
+        <v>63.88941428931217</v>
       </c>
       <c r="H4" t="n">
-        <v>34.75578858485039</v>
+        <v>34.75578858485035</v>
       </c>
       <c r="I4" t="n">
-        <v>21.72439433172423</v>
+        <v>21.72439433172427</v>
       </c>
       <c r="J4" t="n">
-        <v>42.7548450665959</v>
+        <v>42.75484506659591</v>
       </c>
       <c r="K4" t="n">
-        <v>27.92406601596584</v>
+        <v>27.92406601596588</v>
       </c>
       <c r="L4" t="n">
-        <v>37.06300849042506</v>
+        <v>37.06300849042509</v>
       </c>
       <c r="M4" t="n">
-        <v>57.31629784204404</v>
+        <v>57.31629784204407</v>
       </c>
       <c r="N4" t="n">
-        <v>37.00673983470087</v>
+        <v>37.00673983470109</v>
       </c>
       <c r="O4" t="n">
-        <v>22.87448750346063</v>
+        <v>22.87448750346068</v>
       </c>
       <c r="P4" t="n">
-        <v>42.00802655753519</v>
+        <v>42.00802655753551</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.33944007737279</v>
+        <v>14.33944007737282</v>
       </c>
       <c r="R4" t="n">
         <v>22.71932473854302</v>
       </c>
       <c r="S4" t="n">
-        <v>42.33912808460843</v>
+        <v>42.33912808460847</v>
       </c>
       <c r="T4" t="n">
-        <v>28.05918401571337</v>
+        <v>28.05918401571348</v>
       </c>
       <c r="U4" t="n">
-        <v>37.00673983470087</v>
+        <v>37.00673983470109</v>
       </c>
       <c r="V4" t="n">
-        <v>17.14469586200591</v>
+        <v>17.14469586200596</v>
       </c>
       <c r="W4" t="n">
-        <v>47.9220634903222</v>
+        <v>47.92206349032209</v>
       </c>
       <c r="X4" t="n">
-        <v>47.37932795567738</v>
+        <v>47.37932795567754</v>
       </c>
       <c r="Y4" t="n">
-        <v>45.27639897206198</v>
+        <v>45.27639897206205</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.72788526897192</v>
+        <v>24.72788526897191</v>
       </c>
       <c r="AA4" t="n">
-        <v>36.07736583818</v>
+        <v>36.07736583818002</v>
       </c>
       <c r="AB4" t="n">
-        <v>53.50811171729966</v>
+        <v>53.50811171729965</v>
       </c>
     </row>
     <row r="5">
@@ -3958,61 +3958,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="C5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="D5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="E5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="F5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="G5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="H5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="I5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="J5" t="n">
-        <v>1.135260662697644</v>
+        <v>1.135260662697643</v>
       </c>
       <c r="K5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="L5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="M5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="N5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="O5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="P5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="R5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="S5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="T5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="U5" t="n">
         <v>1.112687370979283</v>
@@ -4021,22 +4021,22 @@
         <v>1.12107589623536</v>
       </c>
       <c r="W5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607188</v>
       </c>
       <c r="X5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="Y5" t="n">
         <v>1.112687370979283</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.137825710607189</v>
+        <v>1.137825710607187</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.137825710607191</v>
+        <v>1.137825710607187</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="C6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="D6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="E6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="F6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="G6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="H6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="I6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="J6" t="n">
-        <v>1.823833070881631</v>
+        <v>1.823833070881639</v>
       </c>
       <c r="K6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="L6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="M6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="N6" t="n">
-        <v>1.286862874638962</v>
+        <v>1.286862874638961</v>
       </c>
       <c r="O6" t="n">
-        <v>1.853569438361963</v>
+        <v>1.286862874638963</v>
       </c>
       <c r="P6" t="n">
         <v>1.853462350455162</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="R6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="S6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="T6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="U6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="V6" t="n">
-        <v>1.809648304419348</v>
+        <v>1.809648304419358</v>
       </c>
       <c r="W6" t="n">
-        <v>1.853586024437376</v>
+        <v>1.311806062793084</v>
       </c>
       <c r="X6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.297620007207128</v>
+        <v>1.297620007207127</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.826398118791181</v>
+        <v>1.283148238855607</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.283148238855609</v>
+        <v>1.826398118791185</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.293880213732512</v>
+        <v>1.293880213732513</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="C7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="D7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="E7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="F7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="G7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="H7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="I7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="J7" t="n">
-        <v>1.759413160479221</v>
+        <v>1.759413160479222</v>
       </c>
       <c r="K7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="L7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="M7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="N7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="O7" t="n">
-        <v>1.760078643665977</v>
+        <v>1.760078643665976</v>
       </c>
       <c r="P7" t="n">
-        <v>1.760078643665977</v>
+        <v>1.760078643665976</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="S7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="T7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="U7" t="n">
-        <v>1.758356835373428</v>
+        <v>1.758356835373426</v>
       </c>
       <c r="V7" t="n">
-        <v>1.745228394016932</v>
+        <v>1.745228394016938</v>
       </c>
       <c r="W7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="X7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.761978208388765</v>
+        <v>1.761978208388767</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.036474754606192</v>
+        <v>2.036474754606194</v>
       </c>
       <c r="C8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="D8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="E8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.369290718575283</v>
       </c>
       <c r="F8" t="n">
         <v>2.147374361246737</v>
       </c>
       <c r="G8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.895944635388022</v>
       </c>
       <c r="H8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="I8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="J8" t="n">
         <v>2.745770594990774</v>
       </c>
       <c r="K8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="L8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="M8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900243</v>
       </c>
       <c r="N8" t="n">
         <v>2.196524362601858</v>
       </c>
       <c r="O8" t="n">
-        <v>2.348166893445997</v>
+        <v>2.348166893445998</v>
       </c>
       <c r="P8" t="n">
-        <v>2.310995644967766</v>
+        <v>2.310995644967772</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.896577842771738</v>
+        <v>1.896577842771735</v>
       </c>
       <c r="R8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="S8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="T8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="U8" t="n">
-        <v>2.309040573370933</v>
+        <v>2.39955148494391</v>
       </c>
       <c r="V8" t="n">
-        <v>2.731585828528481</v>
+        <v>2.535551754775548</v>
       </c>
       <c r="W8" t="n">
-        <v>2.748475543422507</v>
+        <v>2.748475543422509</v>
       </c>
       <c r="X8" t="n">
-        <v>1.961821307341481</v>
+        <v>1.961821307341484</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.453840020683136</v>
+        <v>3.453840020683142</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.023251573184372</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.748335642900317</v>
+        <v>2.748335642900319</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.49193386505693</v>
+        <v>3.491933865056939</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.417618040587214</v>
+        <v>3.417618040587218</v>
       </c>
       <c r="C9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="D9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="E9" t="n">
-        <v>4.109419919574701</v>
+        <v>3.94975509254426</v>
       </c>
       <c r="F9" t="n">
-        <v>4.109419919574701</v>
+        <v>2.514627396342749</v>
       </c>
       <c r="G9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109420211865647</v>
       </c>
       <c r="H9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="I9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="J9" t="n">
-        <v>4.106854871665153</v>
+        <v>4.106854871665155</v>
       </c>
       <c r="K9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="L9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="M9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="N9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="O9" t="n">
-        <v>4.338682545589724</v>
+        <v>4.338682545589728</v>
       </c>
       <c r="P9" t="n">
-        <v>4.38854316969549</v>
+        <v>4.388543169695488</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.109420211865644</v>
+        <v>4.109420211865647</v>
       </c>
       <c r="R9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="S9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="T9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="U9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="V9" t="n">
-        <v>4.092670105202874</v>
+        <v>4.890994121525231</v>
       </c>
       <c r="W9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="X9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.109419919574701</v>
+        <v>3.692325020034083</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.109419919574701</v>
+        <v>4.109419919574695</v>
       </c>
     </row>
     <row r="10">
@@ -4428,7 +4428,7 @@
         <v>12.25962868856717</v>
       </c>
       <c r="L10" t="n">
-        <v>12.0820338207592</v>
+        <v>12.08203382075921</v>
       </c>
       <c r="M10" t="n">
         <v>11.700998532534</v>
@@ -4437,7 +4437,7 @@
         <v>12.31449918819541</v>
       </c>
       <c r="O10" t="n">
-        <v>12.35456326426202</v>
+        <v>12.35456326426203</v>
       </c>
       <c r="P10" t="n">
         <v>11.89625250301516</v>
@@ -4446,7 +4446,7 @@
         <v>12.62410395441572</v>
       </c>
       <c r="R10" t="n">
-        <v>12.46758817176346</v>
+        <v>12.46758817176347</v>
       </c>
       <c r="S10" t="n">
         <v>11.90050010804607</v>
@@ -4464,10 +4464,10 @@
         <v>11.84185714999806</v>
       </c>
       <c r="X10" t="n">
-        <v>11.8902402622322</v>
+        <v>11.89024026223219</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.89298770753949</v>
+        <v>11.8929877075395</v>
       </c>
       <c r="Z10" t="n">
         <v>12.30703684448223</v>
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.488678638886506</v>
+        <v>6.488678638886509</v>
       </c>
       <c r="C11" t="n">
-        <v>6.470637593704623</v>
+        <v>6.470637593704628</v>
       </c>
       <c r="D11" t="n">
-        <v>6.35399285264892</v>
+        <v>6.353992852648923</v>
       </c>
       <c r="E11" t="n">
         <v>4.284235397092359</v>
       </c>
       <c r="F11" t="n">
-        <v>6.470310621536822</v>
+        <v>6.470310621536824</v>
       </c>
       <c r="G11" t="n">
-        <v>6.104048473935887</v>
+        <v>6.104048473935888</v>
       </c>
       <c r="H11" t="n">
-        <v>6.408395336540111</v>
+        <v>6.408395336540115</v>
       </c>
       <c r="I11" t="n">
-        <v>6.52533722561644</v>
+        <v>6.525337225616444</v>
       </c>
       <c r="J11" t="n">
-        <v>6.263741102200752</v>
+        <v>6.263741102200754</v>
       </c>
       <c r="K11" t="n">
-        <v>6.425089974615402</v>
+        <v>6.425089974615406</v>
       </c>
       <c r="L11" t="n">
-        <v>6.344422920279096</v>
+        <v>6.344422920279097</v>
       </c>
       <c r="M11" t="n">
-        <v>6.210151639775384</v>
+        <v>6.210151639775388</v>
       </c>
       <c r="N11" t="n">
-        <v>6.383744519366875</v>
+        <v>6.383744519366878</v>
       </c>
       <c r="O11" t="n">
-        <v>6.468065054273381</v>
+        <v>6.468065054273383</v>
       </c>
       <c r="P11" t="n">
-        <v>6.259851162245066</v>
+        <v>6.259851162245067</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.591061988696787</v>
+        <v>6.59106198869679</v>
       </c>
       <c r="R11" t="n">
-        <v>6.520372686442386</v>
+        <v>6.520372686442392</v>
       </c>
       <c r="S11" t="n">
-        <v>6.261824502480999</v>
+        <v>6.261824502481004</v>
       </c>
       <c r="T11" t="n">
-        <v>6.459371920548154</v>
+        <v>6.459371920548157</v>
       </c>
       <c r="U11" t="n">
-        <v>6.334207950769551</v>
+        <v>6.334207950769552</v>
       </c>
       <c r="V11" t="n">
-        <v>6.638965706769363</v>
+        <v>6.638965706769361</v>
       </c>
       <c r="W11" t="n">
-        <v>6.235141769685136</v>
+        <v>6.23514176968514</v>
       </c>
       <c r="X11" t="n">
-        <v>6.260292171454483</v>
+        <v>6.260292171454487</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.257517537346519</v>
+        <v>6.257517537346517</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.38048372440094</v>
+        <v>6.380483724400942</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.360944372131379</v>
+        <v>6.360944372131383</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.240121543608197</v>
+        <v>6.240121543608199</v>
       </c>
     </row>
   </sheetData>
@@ -4736,16 +4736,16 @@
         <v>6.597402960344534</v>
       </c>
       <c r="D2" t="n">
-        <v>6.624098160696784</v>
+        <v>6.624098160696782</v>
       </c>
       <c r="E2" t="n">
-        <v>4.406013407731606</v>
+        <v>4.406013407731603</v>
       </c>
       <c r="F2" t="n">
-        <v>6.598704511127698</v>
+        <v>6.598704511127699</v>
       </c>
       <c r="G2" t="n">
-        <v>6.766640789690497</v>
+        <v>6.766640789690496</v>
       </c>
       <c r="H2" t="n">
         <v>6.69091279479595</v>
@@ -4754,7 +4754,7 @@
         <v>6.69091279479595</v>
       </c>
       <c r="J2" t="n">
-        <v>6.68769481132856</v>
+        <v>6.687694811328564</v>
       </c>
       <c r="K2" t="n">
         <v>6.690557442242795</v>
@@ -4766,7 +4766,7 @@
         <v>6.716372333430218</v>
       </c>
       <c r="N2" t="n">
-        <v>6.628766048813048</v>
+        <v>6.628766048813046</v>
       </c>
       <c r="O2" t="n">
         <v>6.690093391036507</v>
@@ -4790,7 +4790,7 @@
         <v>6.693712884633197</v>
       </c>
       <c r="V2" t="n">
-        <v>6.859004030082791</v>
+        <v>6.859004030082789</v>
       </c>
       <c r="W2" t="n">
         <v>6.69091279479595</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.43189189040342</v>
+        <v>19.43189189040343</v>
       </c>
       <c r="C4" t="n">
-        <v>15.96209247645095</v>
+        <v>15.96209247645096</v>
       </c>
       <c r="D4" t="n">
-        <v>22.82685806401447</v>
+        <v>22.82685806401445</v>
       </c>
       <c r="E4" t="n">
-        <v>10.99211459380697</v>
+        <v>10.99211459380698</v>
       </c>
       <c r="F4" t="n">
-        <v>17.00115640473198</v>
+        <v>17.00115640473197</v>
       </c>
       <c r="G4" t="n">
-        <v>53.06867049194735</v>
+        <v>53.06867049194744</v>
       </c>
       <c r="H4" t="n">
-        <v>31.48021874705386</v>
+        <v>31.48021874705391</v>
       </c>
       <c r="I4" t="n">
-        <v>22.16254340646405</v>
+        <v>22.16254340646406</v>
       </c>
       <c r="J4" t="n">
-        <v>37.42515870906769</v>
+        <v>37.42515870906774</v>
       </c>
       <c r="K4" t="n">
-        <v>32.33949573508518</v>
+        <v>32.33949573508531</v>
       </c>
       <c r="L4" t="n">
-        <v>30.7604659405408</v>
+        <v>30.76046594054082</v>
       </c>
       <c r="M4" t="n">
-        <v>47.08010948444289</v>
+        <v>47.08010948444293</v>
       </c>
       <c r="N4" t="n">
-        <v>38.40376759715988</v>
+        <v>38.40376759715976</v>
       </c>
       <c r="O4" t="n">
-        <v>18.52449668441787</v>
+        <v>18.52449668441783</v>
       </c>
       <c r="P4" t="n">
-        <v>37.9337216547784</v>
+        <v>37.93372165477842</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.47637881654292</v>
+        <v>17.47637881654295</v>
       </c>
       <c r="R4" t="n">
-        <v>21.13796389165825</v>
+        <v>21.13796389165827</v>
       </c>
       <c r="S4" t="n">
-        <v>37.6681382581567</v>
+        <v>37.66813825815675</v>
       </c>
       <c r="T4" t="n">
-        <v>25.48111974976629</v>
+        <v>25.48111974976627</v>
       </c>
       <c r="U4" t="n">
-        <v>38.40376759715983</v>
+        <v>38.40376759715978</v>
       </c>
       <c r="V4" t="n">
-        <v>24.97301109202464</v>
+        <v>24.97301109202463</v>
       </c>
       <c r="W4" t="n">
         <v>48.62181421265576</v>
       </c>
       <c r="X4" t="n">
-        <v>47.50843998697339</v>
+        <v>47.50843998697359</v>
       </c>
       <c r="Y4" t="n">
-        <v>67.1135703552272</v>
+        <v>67.11357035522728</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.90090912892285</v>
+        <v>20.90090912892286</v>
       </c>
       <c r="AA4" t="n">
-        <v>38.15881037109958</v>
+        <v>38.15881037109965</v>
       </c>
       <c r="AB4" t="n">
-        <v>47.87280554395611</v>
+        <v>47.87280554395615</v>
       </c>
     </row>
     <row r="5">
@@ -5018,7 +5018,7 @@
         <v>1.075439327334707</v>
       </c>
       <c r="J5" t="n">
-        <v>1.073422770923023</v>
+        <v>1.073422770923024</v>
       </c>
       <c r="K5" t="n">
         <v>1.075439327334707</v>
@@ -5051,7 +5051,7 @@
         <v>1.075439327334707</v>
       </c>
       <c r="U5" t="n">
-        <v>1.060258833958201</v>
+        <v>1.060258833958202</v>
       </c>
       <c r="V5" t="n">
         <v>1.062196482706474</v>
@@ -5063,7 +5063,7 @@
         <v>1.075439327334707</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.060258833958201</v>
+        <v>1.060258833958202</v>
       </c>
       <c r="Z5" t="n">
         <v>1.075439327334707</v>
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="C6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="D6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="E6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="F6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="G6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="H6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="I6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="J6" t="n">
-        <v>1.240243742630971</v>
+        <v>1.746648572209579</v>
       </c>
       <c r="K6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="L6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="M6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="N6" t="n">
-        <v>1.249051247933559</v>
+        <v>1.249051247933515</v>
       </c>
       <c r="O6" t="n">
-        <v>1.249051247933558</v>
+        <v>1.776502077577484</v>
       </c>
       <c r="P6" t="n">
-        <v>1.776368436939842</v>
+        <v>1.227611888039842</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="R6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="S6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="T6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="U6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="V6" t="n">
-        <v>1.735422283993028</v>
+        <v>1.229017454414421</v>
       </c>
       <c r="W6" t="n">
-        <v>1.776521670363256</v>
+        <v>1.776521670363252</v>
       </c>
       <c r="X6" t="n">
-        <v>1.242260299042654</v>
+        <v>1.242260299042655</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.262693558113379</v>
+        <v>1.262693558113255</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.748665128621259</v>
+        <v>1.74866512862126</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.252956394616203</v>
+        <v>1.252956394616202</v>
       </c>
     </row>
     <row r="7">
@@ -5194,7 +5194,7 @@
         <v>1.676605609811215</v>
       </c>
       <c r="J7" t="n">
-        <v>1.674589053399534</v>
+        <v>1.674589053399533</v>
       </c>
       <c r="K7" t="n">
         <v>1.676605609811215</v>
@@ -5227,10 +5227,10 @@
         <v>1.676605609811215</v>
       </c>
       <c r="U7" t="n">
-        <v>1.669883703504255</v>
+        <v>1.669883703504254</v>
       </c>
       <c r="V7" t="n">
-        <v>1.663362765182985</v>
+        <v>1.663362765182984</v>
       </c>
       <c r="W7" t="n">
         <v>1.676605609811215</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.928718949210412</v>
+        <v>1.928718949210413</v>
       </c>
       <c r="C8" t="n">
         <v>2.604682480778997</v>
@@ -5267,13 +5267,13 @@
         <v>2.604682480778997</v>
       </c>
       <c r="E8" t="n">
-        <v>2.604682480778997</v>
+        <v>2.244751840001306</v>
       </c>
       <c r="F8" t="n">
-        <v>2.034026167216096</v>
+        <v>2.034026167216095</v>
       </c>
       <c r="G8" t="n">
-        <v>2.604682480778997</v>
+        <v>2.744847922501131</v>
       </c>
       <c r="H8" t="n">
         <v>2.604682480778997</v>
@@ -5291,10 +5291,10 @@
         <v>2.604682480778997</v>
       </c>
       <c r="M8" t="n">
-        <v>2.604682480778997</v>
+        <v>2.604682480778835</v>
       </c>
       <c r="N8" t="n">
-        <v>2.080697657444111</v>
+        <v>2.080697657444109</v>
       </c>
       <c r="O8" t="n">
         <v>2.224693236309688</v>
@@ -5303,7 +5303,7 @@
         <v>2.189396440536419</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.795876687284808</v>
+        <v>1.795876687284809</v>
       </c>
       <c r="R8" t="n">
         <v>2.604682480778997</v>
@@ -5315,28 +5315,28 @@
         <v>2.604682480778997</v>
       </c>
       <c r="U8" t="n">
-        <v>2.185219433006809</v>
+        <v>2.271015320818186</v>
       </c>
       <c r="V8" t="n">
-        <v>2.591439636150764</v>
+        <v>2.402565284568245</v>
       </c>
       <c r="W8" t="n">
-        <v>2.604815326458062</v>
+        <v>2.604815326458059</v>
       </c>
       <c r="X8" t="n">
-        <v>1.85783008779162</v>
+        <v>1.857830087791619</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.270382350426292</v>
+        <v>3.270382350426291</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.604682480778997</v>
+        <v>1.916162579617806</v>
       </c>
       <c r="AA8" t="n">
         <v>2.604682480778997</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.310782912163107</v>
+        <v>3.310782912163105</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.129516526835546</v>
+        <v>3.129516526835543</v>
       </c>
       <c r="C9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="D9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="E9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.611270732067983</v>
       </c>
       <c r="F9" t="n">
-        <v>3.755818516553156</v>
+        <v>2.312021224543675</v>
       </c>
       <c r="G9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818724693432</v>
       </c>
       <c r="H9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="I9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="J9" t="n">
-        <v>3.753801960141472</v>
+        <v>3.753801960141469</v>
       </c>
       <c r="K9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="L9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="M9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="N9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="O9" t="n">
-        <v>3.963374452990851</v>
+        <v>3.96337445299085</v>
       </c>
       <c r="P9" t="n">
         <v>4.008514262838937</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.755818724693435</v>
+        <v>3.755818724693432</v>
       </c>
       <c r="R9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="S9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="T9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="U9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="V9" t="n">
-        <v>3.742575671924925</v>
+        <v>4.465314322970716</v>
       </c>
       <c r="W9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="X9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.37821419234956</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.755818516553156</v>
+        <v>3.755818516553152</v>
       </c>
     </row>
     <row r="10">
@@ -5458,16 +5458,16 @@
         <v>12.43860482056617</v>
       </c>
       <c r="J10" t="n">
-        <v>12.00042202403215</v>
+        <v>12.00042202403214</v>
       </c>
       <c r="K10" t="n">
         <v>12.1253307200865</v>
       </c>
       <c r="L10" t="n">
-        <v>12.1790246228363</v>
+        <v>12.17902462283629</v>
       </c>
       <c r="M10" t="n">
-        <v>11.85552814084365</v>
+        <v>11.85552814084364</v>
       </c>
       <c r="N10" t="n">
         <v>12.37363177118875</v>
@@ -5482,13 +5482,13 @@
         <v>12.51796921718031</v>
       </c>
       <c r="R10" t="n">
-        <v>12.47950299286142</v>
+        <v>12.47950299286141</v>
       </c>
       <c r="S10" t="n">
         <v>11.98086636629424</v>
       </c>
       <c r="T10" t="n">
-        <v>12.36956376447246</v>
+        <v>12.36956376447245</v>
       </c>
       <c r="U10" t="n">
         <v>11.96867847345279</v>
@@ -5503,16 +5503,16 @@
         <v>11.82563646745553</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.38758345360958</v>
+        <v>11.38758345360957</v>
       </c>
       <c r="Z10" t="n">
         <v>12.35480887149722</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.05179245609259</v>
+        <v>12.05179245609258</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.92267141956687</v>
+        <v>11.92267141956686</v>
       </c>
     </row>
     <row r="11">
@@ -5525,82 +5525,82 @@
         <v>6.474696838335009</v>
       </c>
       <c r="C11" t="n">
-        <v>6.43582294017709</v>
+        <v>6.435822940177087</v>
       </c>
       <c r="D11" t="n">
-        <v>6.394041375090462</v>
+        <v>6.39404137509046</v>
       </c>
       <c r="E11" t="n">
-        <v>4.294182331109335</v>
+        <v>4.294182331109334</v>
       </c>
       <c r="F11" t="n">
-        <v>6.435470046448695</v>
+        <v>6.435470046448696</v>
       </c>
       <c r="G11" t="n">
-        <v>6.146673384001301</v>
+        <v>6.146673384001296</v>
       </c>
       <c r="H11" t="n">
-        <v>6.40052592955988</v>
+        <v>6.400525929559877</v>
       </c>
       <c r="I11" t="n">
-        <v>6.476950744039606</v>
+        <v>6.476950744039605</v>
       </c>
       <c r="J11" t="n">
-        <v>6.275822552135302</v>
+        <v>6.275822552135303</v>
       </c>
       <c r="K11" t="n">
-        <v>6.334231611271401</v>
+        <v>6.334231611271399</v>
       </c>
       <c r="L11" t="n">
-        <v>6.358840926839508</v>
+        <v>6.358840926839506</v>
       </c>
       <c r="M11" t="n">
-        <v>6.237911691345226</v>
+        <v>6.237911691345225</v>
       </c>
       <c r="N11" t="n">
         <v>6.385241053533149</v>
       </c>
       <c r="O11" t="n">
-        <v>6.480656039757429</v>
+        <v>6.480656039757427</v>
       </c>
       <c r="P11" t="n">
-        <v>6.249301915670046</v>
+        <v>6.249301915670042</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.513057227547326</v>
+        <v>6.513057227547324</v>
       </c>
       <c r="R11" t="n">
         <v>6.49656445897052</v>
       </c>
       <c r="S11" t="n">
-        <v>6.268678288619981</v>
+        <v>6.268678288619979</v>
       </c>
       <c r="T11" t="n">
-        <v>6.444944372353957</v>
+        <v>6.444944372353955</v>
       </c>
       <c r="U11" t="n">
-        <v>6.264538654633211</v>
+        <v>6.264538654633207</v>
       </c>
       <c r="V11" t="n">
         <v>6.56857426422808</v>
       </c>
       <c r="W11" t="n">
-        <v>6.188345643393639</v>
+        <v>6.188345643393637</v>
       </c>
       <c r="X11" t="n">
-        <v>6.199485856768936</v>
+        <v>6.19948585676893</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.9971732660254</v>
+        <v>5.997173266025402</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.378863500885778</v>
+        <v>6.378863500885777</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.300949885506264</v>
+        <v>6.300949885506263</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.246962636695916</v>
+        <v>6.246962636695915</v>
       </c>
     </row>
   </sheetData>
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="C2" t="n">
-        <v>6.425849638803927</v>
+        <v>6.425849638803925</v>
       </c>
       <c r="D2" t="n">
-        <v>6.445825771102951</v>
+        <v>6.445825771102949</v>
       </c>
       <c r="E2" t="n">
-        <v>4.289989398683787</v>
+        <v>4.289989398683783</v>
       </c>
       <c r="F2" t="n">
         <v>6.411268231540282</v>
@@ -5784,67 +5784,67 @@
         <v>6.484140504397479</v>
       </c>
       <c r="H2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="I2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="J2" t="n">
-        <v>6.453973254841024</v>
+        <v>6.453973254841026</v>
       </c>
       <c r="K2" t="n">
-        <v>6.455902478900645</v>
+        <v>6.455902478900644</v>
       </c>
       <c r="L2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="M2" t="n">
-        <v>6.474590713009931</v>
+        <v>6.47459071300993</v>
       </c>
       <c r="N2" t="n">
         <v>6.435955287810482</v>
       </c>
       <c r="O2" t="n">
-        <v>6.455456482274173</v>
+        <v>6.455456482274172</v>
       </c>
       <c r="P2" t="n">
-        <v>6.455937352351675</v>
+        <v>6.455937352351674</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.456088800982495</v>
+        <v>6.456088800982494</v>
       </c>
       <c r="R2" t="n">
-        <v>6.456061776050777</v>
+        <v>6.456061776050776</v>
       </c>
       <c r="S2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="T2" t="n">
-        <v>6.455818897909938</v>
+        <v>6.455818897909937</v>
       </c>
       <c r="U2" t="n">
         <v>6.456727870383832</v>
       </c>
       <c r="V2" t="n">
-        <v>6.624533821892913</v>
+        <v>6.624533821892901</v>
       </c>
       <c r="W2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="X2" t="n">
-        <v>6.456621158713197</v>
+        <v>6.456621158713196</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.454625140679393</v>
+        <v>6.454625140679392</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.426304604041649</v>
+        <v>6.426304604041645</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.456097902753469</v>
+        <v>6.456097902753468</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.465584724221071</v>
+        <v>6.46558472422107</v>
       </c>
     </row>
     <row r="3">
@@ -5887,7 +5887,7 @@
         <v>12.77464215674497</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7743903793478</v>
+        <v>12.77439037934779</v>
       </c>
       <c r="N3" t="n">
         <v>12.77464215674497</v>
@@ -5899,7 +5899,7 @@
         <v>12.77446646575814</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.7746321965951</v>
+        <v>12.77463219659509</v>
       </c>
       <c r="R3" t="n">
         <v>12.77460262299515</v>
@@ -5908,7 +5908,7 @@
         <v>12.77464215674497</v>
       </c>
       <c r="T3" t="n">
-        <v>12.77433684100309</v>
+        <v>12.77433684100308</v>
       </c>
       <c r="U3" t="n">
         <v>12.77533153072009</v>
@@ -5920,7 +5920,7 @@
         <v>12.77464215674497</v>
       </c>
       <c r="X3" t="n">
-        <v>12.7752147561034</v>
+        <v>12.77521475610339</v>
       </c>
       <c r="Y3" t="n">
         <v>12.77303051155635</v>
@@ -5932,7 +5932,7 @@
         <v>12.77464215674497</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.78502359430704</v>
+        <v>12.78502359430703</v>
       </c>
     </row>
     <row r="4">
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.037694308559423</v>
+        <v>5.03769430855942</v>
       </c>
       <c r="C4" t="n">
-        <v>6.795144857912182</v>
+        <v>6.795144857912176</v>
       </c>
       <c r="D4" t="n">
         <v>12.28968027674642</v>
       </c>
       <c r="E4" t="n">
-        <v>1.46136021342935</v>
+        <v>1.461360213429357</v>
       </c>
       <c r="F4" t="n">
-        <v>2.732551752680536</v>
+        <v>2.732551752680551</v>
       </c>
       <c r="G4" t="n">
-        <v>19.28352943583782</v>
+        <v>19.28352943583787</v>
       </c>
       <c r="H4" t="n">
-        <v>10.75991295006091</v>
+        <v>10.75991295006089</v>
       </c>
       <c r="I4" t="n">
-        <v>7.227347534033391</v>
+        <v>7.227347534033374</v>
       </c>
       <c r="J4" t="n">
         <v>13.46236295078907</v>
       </c>
       <c r="K4" t="n">
-        <v>12.67523842665525</v>
+        <v>12.67523842665523</v>
       </c>
       <c r="L4" t="n">
-        <v>4.239943727519029</v>
+        <v>4.239943727519014</v>
       </c>
       <c r="M4" t="n">
-        <v>18.87137621433824</v>
+        <v>18.87137621433826</v>
       </c>
       <c r="N4" t="n">
-        <v>22.49670686335844</v>
+        <v>22.49670686335841</v>
       </c>
       <c r="O4" t="n">
-        <v>4.291524535668194</v>
+        <v>4.291524535668086</v>
       </c>
       <c r="P4" t="n">
-        <v>7.131104437799972</v>
+        <v>7.131104437799893</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.566022588292349</v>
+        <v>5.566022588292355</v>
       </c>
       <c r="R4" t="n">
         <v>-11.93743534912217</v>
       </c>
       <c r="S4" t="n">
-        <v>10.36715104250501</v>
+        <v>10.36715104250502</v>
       </c>
       <c r="T4" t="n">
-        <v>4.697299730391749</v>
+        <v>4.697299730391735</v>
       </c>
       <c r="U4" t="n">
-        <v>22.49670686335843</v>
+        <v>22.49670686335841</v>
       </c>
       <c r="V4" t="n">
-        <v>5.16981635939161</v>
+        <v>5.169816359391607</v>
       </c>
       <c r="W4" t="n">
-        <v>48.56464221446662</v>
+        <v>48.56464221446667</v>
       </c>
       <c r="X4" t="n">
-        <v>21.47955051535502</v>
+        <v>21.479550515355</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.99400517799641</v>
+        <v>9.99400517799624</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.04069610602281</v>
+        <v>6.040696106022796</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.0665799319689</v>
+        <v>23.06657993196895</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.18184678340066</v>
+        <v>16.18184678340071</v>
       </c>
     </row>
     <row r="5">
@@ -6030,85 +6030,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7713759139073183</v>
+        <v>0.7713759139073194</v>
       </c>
       <c r="C5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7696096934459449</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7713759139073195</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="E5" t="n">
+      <c r="P5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="Q5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="H5" t="n">
+      <c r="R5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.7570866311338869</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.759729259761975</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="I5" t="n">
+      <c r="X5" t="n">
         <v>0.7713759139073194</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.7696096934459453</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="Y5" t="n">
+        <v>0.7570866311338869</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.7713759139073193</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.7713759139073194</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.7570866311338853</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.7597292597619736</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.7713759139073183</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.7570866311338853</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.7713759139073194</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.7713759139073183</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8680394265399135</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="C6" t="n">
-        <v>1.233438426257366</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="D6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="E6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="F6" t="n">
-        <v>1.233438426257366</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8680394265399135</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8680394265399135</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="I6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8662732060785672</v>
+        <v>0.8662732060785415</v>
       </c>
       <c r="K6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="L6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8680394265399135</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8707406714949988</v>
+        <v>0.8707406714949834</v>
       </c>
       <c r="O6" t="n">
-        <v>1.266229309411426</v>
+        <v>1.266229309411432</v>
       </c>
       <c r="P6" t="n">
-        <v>1.266125295707892</v>
+        <v>0.85429284172275</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.233438426257366</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="R6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="S6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8680394265399135</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="U6" t="n">
-        <v>1.233438426257366</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8563927723946083</v>
+        <v>1.221791772112022</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8978740597958297</v>
+        <v>0.8978740597957712</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8680394265399135</v>
+        <v>0.8680394265399159</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8814248834235464</v>
+        <v>0.8814248834236985</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8680394265399135</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8680394265399135</v>
+        <v>1.233438426257367</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8726351241259861</v>
+        <v>0.8726351241259875</v>
       </c>
     </row>
     <row r="7">
@@ -6206,43 +6206,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="C7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="D7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="E7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="F7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="G7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="H7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="I7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="J7" t="n">
-        <v>1.300176067971094</v>
+        <v>1.300176067971095</v>
       </c>
       <c r="K7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="L7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="M7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="N7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="O7" t="n">
         <v>1.299909794650451</v>
@@ -6251,40 +6251,40 @@
         <v>1.299909794650451</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="R7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="S7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="T7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="U7" t="n">
-        <v>1.294567127276562</v>
+        <v>1.294567127276563</v>
       </c>
       <c r="V7" t="n">
-        <v>1.290295634287124</v>
+        <v>1.290295634287125</v>
       </c>
       <c r="W7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="X7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.301942288432468</v>
+        <v>1.301942288432469</v>
       </c>
     </row>
     <row r="8">
@@ -6294,85 +6294,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.475181202627736</v>
+        <v>1.475181202627734</v>
       </c>
       <c r="C8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="D8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="E8" t="n">
-        <v>2.043700025711066</v>
+        <v>1.740980522769248</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5637497907852</v>
+        <v>1.563749790785195</v>
       </c>
       <c r="G8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.161586107189565</v>
       </c>
       <c r="H8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="I8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="J8" t="n">
-        <v>2.041933805249683</v>
+        <v>2.04193380524969</v>
       </c>
       <c r="K8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="L8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="M8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025710332</v>
       </c>
       <c r="N8" t="n">
-        <v>1.603002826562953</v>
+        <v>1.603002826562951</v>
       </c>
       <c r="O8" t="n">
-        <v>1.724110243145163</v>
+        <v>1.724110243145162</v>
       </c>
       <c r="P8" t="n">
-        <v>1.694423889002396</v>
+        <v>1.694423889002397</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.363454278213283</v>
+        <v>1.363454278213279</v>
       </c>
       <c r="R8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="S8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="T8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="U8" t="n">
-        <v>1.689975334064713</v>
+        <v>1.762073139743084</v>
       </c>
       <c r="V8" t="n">
-        <v>2.032053371565716</v>
+        <v>1.872101824895831</v>
       </c>
       <c r="W8" t="n">
-        <v>2.043811755454713</v>
+        <v>2.043811755454707</v>
       </c>
       <c r="X8" t="n">
-        <v>1.415560157709829</v>
+        <v>1.415560157709827</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.601882269584883</v>
+        <v>2.601882269584888</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.043700025711066</v>
+        <v>1.464620673651239</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.043700025711066</v>
+        <v>2.043700025711063</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.637565474734282</v>
+        <v>2.637565474734285</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.492959690820093</v>
+        <v>2.492959690820097</v>
       </c>
       <c r="C9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="D9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="E9" t="n">
-        <v>3.021881258803136</v>
+        <v>2.89980837986666</v>
       </c>
       <c r="F9" t="n">
-        <v>3.021881258803136</v>
+        <v>1.802572583812514</v>
       </c>
       <c r="G9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881338784822</v>
       </c>
       <c r="H9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="I9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="J9" t="n">
-        <v>3.020115038341758</v>
+        <v>3.020115038341761</v>
       </c>
       <c r="K9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="L9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="M9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="N9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="O9" t="n">
         <v>3.197165280356529</v>
       </c>
       <c r="P9" t="n">
-        <v>3.235286530282401</v>
+        <v>3.235286530282399</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.021881338784823</v>
+        <v>3.021881338784822</v>
       </c>
       <c r="R9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="S9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="T9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="U9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="V9" t="n">
-        <v>3.010234604657795</v>
+        <v>3.62059848785169</v>
       </c>
       <c r="W9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="X9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.021881258803136</v>
+        <v>2.702988618610141</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.021881258803136</v>
+        <v>3.021881258803137</v>
       </c>
     </row>
     <row r="10">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.67275463710405</v>
+        <v>12.67275463710404</v>
       </c>
       <c r="C10" t="n">
         <v>12.6443116919674</v>
       </c>
       <c r="D10" t="n">
-        <v>12.53364418582385</v>
+        <v>12.53364418582384</v>
       </c>
       <c r="E10" t="n">
         <v>10.60931259688249</v>
@@ -6497,7 +6497,7 @@
         <v>12.4682193342901</v>
       </c>
       <c r="K10" t="n">
-        <v>12.5016283519395</v>
+        <v>12.50162835193949</v>
       </c>
       <c r="L10" t="n">
         <v>12.69270594311634</v>
@@ -6506,16 +6506,16 @@
         <v>12.36511489218454</v>
       </c>
       <c r="N10" t="n">
-        <v>12.59068295510708</v>
+        <v>12.59068295510709</v>
       </c>
       <c r="O10" t="n">
-        <v>12.68857365907681</v>
+        <v>12.6885736590768</v>
       </c>
       <c r="P10" t="n">
         <v>12.62462292963546</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.66849299095171</v>
+        <v>12.6684929909517</v>
       </c>
       <c r="R10" t="n">
         <v>13.02873338434127</v>
@@ -6524,7 +6524,7 @@
         <v>12.52164995545601</v>
       </c>
       <c r="T10" t="n">
-        <v>12.69058361216844</v>
+        <v>12.69058361216843</v>
       </c>
       <c r="U10" t="n">
         <v>12.27439068140258</v>
@@ -6558,73 +6558,73 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.409738756620587</v>
+        <v>6.409738756620585</v>
       </c>
       <c r="C11" t="n">
-        <v>6.366992403247698</v>
+        <v>6.366992403247701</v>
       </c>
       <c r="D11" t="n">
-        <v>6.336170926318879</v>
+        <v>6.336170926318875</v>
       </c>
       <c r="E11" t="n">
-        <v>4.283355443009865</v>
+        <v>4.283355443009864</v>
       </c>
       <c r="F11" t="n">
-        <v>6.39292200041824</v>
+        <v>6.392922000418242</v>
       </c>
       <c r="G11" t="n">
-        <v>6.268894668002771</v>
+        <v>6.268894668002774</v>
       </c>
       <c r="H11" t="n">
         <v>6.365968603347174</v>
       </c>
       <c r="I11" t="n">
-        <v>6.395625625434502</v>
+        <v>6.395625625434497</v>
       </c>
       <c r="J11" t="n">
-        <v>6.31551672593548</v>
+        <v>6.315516725935484</v>
       </c>
       <c r="K11" t="n">
-        <v>6.331777631323789</v>
+        <v>6.331777631323787</v>
       </c>
       <c r="L11" t="n">
-        <v>6.418816664437221</v>
+        <v>6.41881666443722</v>
       </c>
       <c r="M11" t="n">
         <v>6.288369062067058</v>
       </c>
       <c r="N11" t="n">
-        <v>6.352253264822053</v>
+        <v>6.352253264822052</v>
       </c>
       <c r="O11" t="n">
-        <v>6.416614411661826</v>
+        <v>6.416614411661828</v>
       </c>
       <c r="P11" t="n">
         <v>6.387758065892839</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.407795124169168</v>
+        <v>6.407795124169169</v>
       </c>
       <c r="R11" t="n">
-        <v>6.571692082329941</v>
+        <v>6.571692082329942</v>
       </c>
       <c r="S11" t="n">
-        <v>6.34098564492868</v>
+        <v>6.340985644928683</v>
       </c>
       <c r="T11" t="n">
-        <v>6.417710911884464</v>
+        <v>6.417710911884465</v>
       </c>
       <c r="U11" t="n">
-        <v>6.228798187540598</v>
+        <v>6.228798187540599</v>
       </c>
       <c r="V11" t="n">
-        <v>6.576510296871313</v>
+        <v>6.5765102968713</v>
       </c>
       <c r="W11" t="n">
-        <v>5.98407069731384</v>
+        <v>5.984070697313835</v>
       </c>
       <c r="X11" t="n">
-        <v>6.256537786834161</v>
+        <v>6.256537786834158</v>
       </c>
       <c r="Y11" t="n">
         <v>6.362480012893371</v>
@@ -6636,7 +6636,7 @@
         <v>6.235317374610629</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.322323081533134</v>
+        <v>6.322323081533132</v>
       </c>
     </row>
   </sheetData>
@@ -6802,85 +6802,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="C2" t="n">
-        <v>6.34714554449001</v>
+        <v>6.347145544490014</v>
       </c>
       <c r="D2" t="n">
-        <v>6.350870229754055</v>
+        <v>6.350870229754064</v>
       </c>
       <c r="E2" t="n">
-        <v>4.156153275213761</v>
+        <v>4.156153275213757</v>
       </c>
       <c r="F2" t="n">
-        <v>6.285028656877277</v>
+        <v>6.285028656877276</v>
       </c>
       <c r="G2" t="n">
-        <v>6.37875125043685</v>
+        <v>6.378751250436859</v>
       </c>
       <c r="H2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="I2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="J2" t="n">
-        <v>6.352505341350699</v>
+        <v>6.352505341350702</v>
       </c>
       <c r="K2" t="n">
-        <v>6.352950640058816</v>
+        <v>6.352950640058813</v>
       </c>
       <c r="L2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="M2" t="n">
-        <v>6.33511423991978</v>
+        <v>6.335114239919785</v>
       </c>
       <c r="N2" t="n">
-        <v>6.367233393311808</v>
+        <v>6.367233393311812</v>
       </c>
       <c r="O2" t="n">
-        <v>6.352511565247148</v>
+        <v>6.352511565247145</v>
       </c>
       <c r="P2" t="n">
-        <v>6.353146840422923</v>
+        <v>6.353146840422919</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.35321873311835</v>
+        <v>6.353218733118347</v>
       </c>
       <c r="R2" t="n">
-        <v>6.354266111418804</v>
+        <v>6.3542661114188</v>
       </c>
       <c r="S2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="T2" t="n">
-        <v>6.352406167459456</v>
+        <v>6.352406167459453</v>
       </c>
       <c r="U2" t="n">
-        <v>6.354212709725309</v>
+        <v>6.354212709725305</v>
       </c>
       <c r="V2" t="n">
-        <v>6.56222941760229</v>
+        <v>6.562229417602286</v>
       </c>
       <c r="W2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="X2" t="n">
-        <v>6.359473596134096</v>
+        <v>6.359473596134093</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.351457634215565</v>
+        <v>6.351457634215562</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.345162345701527</v>
+        <v>6.345162345701532</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.353227834889324</v>
+        <v>6.353227834889321</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.362714656356928</v>
+        <v>6.362714656356924</v>
       </c>
     </row>
     <row r="3">
@@ -6899,7 +6899,7 @@
         <v>12.70584514999819</v>
       </c>
       <c r="E3" t="n">
-        <v>10.55702265819722</v>
+        <v>10.55702265819723</v>
       </c>
       <c r="F3" t="n">
         <v>12.70533197114208</v>
@@ -6981,82 +6981,82 @@
         <v>-7.725783606184333</v>
       </c>
       <c r="C4" t="n">
-        <v>3.510852870925393</v>
+        <v>3.510852870925398</v>
       </c>
       <c r="D4" t="n">
-        <v>4.196116988767852</v>
+        <v>4.196116988767864</v>
       </c>
       <c r="E4" t="n">
-        <v>-15.56811289698702</v>
+        <v>-15.56811289698704</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.116200929279</v>
+        <v>-12.11620092927905</v>
       </c>
       <c r="G4" t="n">
-        <v>9.579263584056058</v>
+        <v>9.579263584056063</v>
       </c>
       <c r="H4" t="n">
-        <v>4.326214077736074</v>
+        <v>4.3262140777361</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9209884749506445</v>
+        <v>-0.9209884749506063</v>
       </c>
       <c r="J4" t="n">
-        <v>4.353303718229011</v>
+        <v>4.353303718229004</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3627971772007963</v>
+        <v>-0.3627971772007883</v>
       </c>
       <c r="L4" t="n">
-        <v>-12.10906111515836</v>
+        <v>-12.1090611151584</v>
       </c>
       <c r="M4" t="n">
-        <v>0.676763140506236</v>
+        <v>0.6767631405062531</v>
       </c>
       <c r="N4" t="n">
-        <v>2.762281055893322</v>
+        <v>2.762281055893312</v>
       </c>
       <c r="O4" t="n">
-        <v>1.012527880752524</v>
+        <v>1.012527880752552</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.423628618828607</v>
+        <v>-7.42362861882853</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.966885231196022</v>
+        <v>1.966885231196029</v>
       </c>
       <c r="R4" t="n">
-        <v>-33.98631116394361</v>
+        <v>-33.9863111639436</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6126142838049775</v>
+        <v>-0.6126142838049802</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.3581943966145</v>
+        <v>-4.358194396614479</v>
       </c>
       <c r="U4" t="n">
-        <v>2.76228105589332</v>
+        <v>2.762281055893304</v>
       </c>
       <c r="V4" t="n">
-        <v>4.513829206642028</v>
+        <v>4.513829206642023</v>
       </c>
       <c r="W4" t="n">
-        <v>23.44970098454129</v>
+        <v>23.44970098454131</v>
       </c>
       <c r="X4" t="n">
-        <v>41.21190267645503</v>
+        <v>41.21190267645505</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.06059512353611</v>
+        <v>14.06059512353609</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.603028211573101</v>
+        <v>2.603028211573119</v>
       </c>
       <c r="AA4" t="n">
-        <v>32.6804690169598</v>
+        <v>32.68046901695972</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.027663912499402</v>
+        <v>1.027663912499401</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6265582280683523</v>
+        <v>0.6265582280683586</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6202407376341555</v>
+        <v>0.6202407376341699</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6181907367011217</v>
+        <v>0.6181907367011228</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6202407376341555</v>
+        <v>0.6202407376341699</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6280405881015662</v>
+        <v>0.6280405881015614</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6280405881015597</v>
+        <v>0.6280405881015627</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9732447112563334</v>
+        <v>0.6865462632175037</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="N6" t="n">
-        <v>0.694016700214017</v>
+        <v>0.6940167002140096</v>
       </c>
       <c r="O6" t="n">
-        <v>0.694016700214017</v>
+        <v>0.6940167002140547</v>
       </c>
       <c r="P6" t="n">
-        <v>1.002220335235601</v>
+        <v>0.6817700042224182</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6781787718502746</v>
+        <v>0.9648772198891026</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7121195077359872</v>
+        <v>0.7121195077360082</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.6880286232507179</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7028181412696727</v>
+        <v>0.7028181412696473</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9747270712895437</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6880286232507209</v>
+        <v>0.9747270712895464</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6935622958816179</v>
+        <v>0.6935622958816372</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="C7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="D7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="E7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="F7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="G7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="H7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="I7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="J7" t="n">
-        <v>1.060754184345734</v>
+        <v>1.060754184345735</v>
       </c>
       <c r="K7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="L7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="M7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="N7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="O7" t="n">
-        <v>1.060344548448029</v>
+        <v>1.060344548448025</v>
       </c>
       <c r="P7" t="n">
-        <v>1.060344548448029</v>
+        <v>1.060344548448025</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="R7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="S7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="T7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="U7" t="n">
-        <v>1.051437154021216</v>
+        <v>1.051437154021222</v>
       </c>
       <c r="V7" t="n">
         <v>1.052386692978506</v>
       </c>
       <c r="W7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="X7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.062236544378953</v>
+        <v>1.06223654437896</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.165439137821584</v>
+        <v>1.165439137821588</v>
       </c>
       <c r="C8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="D8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="E8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.369241478898377</v>
       </c>
       <c r="F8" t="n">
-        <v>1.233349340172749</v>
+        <v>1.233349340172765</v>
       </c>
       <c r="G8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.691741938037232</v>
       </c>
       <c r="H8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="I8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5998701090791</v>
+        <v>1.599870109079099</v>
       </c>
       <c r="K8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="L8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="M8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.601352469110525</v>
       </c>
       <c r="N8" t="n">
-        <v>1.263446710567464</v>
+        <v>1.263446710567466</v>
       </c>
       <c r="O8" t="n">
-        <v>1.356306146841461</v>
+        <v>1.356306146841463</v>
       </c>
       <c r="P8" t="n">
-        <v>1.333544055229261</v>
+        <v>1.333544055229263</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.07977221906945</v>
+        <v>1.079772219069459</v>
       </c>
       <c r="R8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="S8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="T8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="U8" t="n">
-        <v>1.326632273891709</v>
+        <v>1.381685977973977</v>
       </c>
       <c r="V8" t="n">
-        <v>1.591502617711871</v>
+        <v>1.464747111072678</v>
       </c>
       <c r="W8" t="n">
-        <v>1.601438138258954</v>
+        <v>1.60143813825896</v>
       </c>
       <c r="X8" t="n">
-        <v>1.119724541863134</v>
+        <v>1.119724541863142</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.022962127138501</v>
+        <v>2.022962127138509</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.157341823919683</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.601352469112314</v>
+        <v>1.60135246911232</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.056700393836</v>
+        <v>2.056700393836005</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.933059216582135</v>
+        <v>1.933059216582137</v>
       </c>
       <c r="C9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="D9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="E9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.242296223299947</v>
       </c>
       <c r="F9" t="n">
-        <v>2.335081155125487</v>
+        <v>1.408310708855819</v>
       </c>
       <c r="G9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081274434076</v>
       </c>
       <c r="H9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="I9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33359879509227</v>
+        <v>2.333598795092277</v>
       </c>
       <c r="K9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="L9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="M9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="N9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="O9" t="n">
-        <v>2.468310858003234</v>
+        <v>2.468310858003237</v>
       </c>
       <c r="P9" t="n">
-        <v>2.497286006594822</v>
+        <v>2.497286006594812</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.335081274434077</v>
+        <v>2.335081274434076</v>
       </c>
       <c r="R9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="S9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="T9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="U9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="V9" t="n">
-        <v>2.325231303725037</v>
+        <v>2.789156122684226</v>
       </c>
       <c r="W9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="X9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.092697722745561</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.335081155125487</v>
+        <v>2.335081155125483</v>
       </c>
     </row>
     <row r="10">
@@ -7512,7 +7512,7 @@
         <v>12.63735268942944</v>
       </c>
       <c r="D10" t="n">
-        <v>12.62211775311876</v>
+        <v>12.62211775311877</v>
       </c>
       <c r="E10" t="n">
         <v>10.94223146036298</v>
@@ -7539,16 +7539,16 @@
         <v>13.0977616318098</v>
       </c>
       <c r="M10" t="n">
-        <v>12.71006640766474</v>
+        <v>12.71006640766475</v>
       </c>
       <c r="N10" t="n">
         <v>12.52550749540976</v>
       </c>
       <c r="O10" t="n">
-        <v>12.69697353940599</v>
+        <v>12.696973539406</v>
       </c>
       <c r="P10" t="n">
-        <v>12.91356012848016</v>
+        <v>12.91356012848017</v>
       </c>
       <c r="Q10" t="n">
         <v>12.67315922143817</v>
@@ -7563,13 +7563,13 @@
         <v>12.82801036387179</v>
       </c>
       <c r="U10" t="n">
-        <v>12.65173941128252</v>
+        <v>12.65173941128253</v>
       </c>
       <c r="V10" t="n">
         <v>12.81490663147529</v>
       </c>
       <c r="W10" t="n">
-        <v>12.13900732377151</v>
+        <v>12.1390073237715</v>
       </c>
       <c r="X10" t="n">
         <v>11.72721587054309</v>
@@ -7594,22 +7594,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.450088757994572</v>
+        <v>6.450088757994574</v>
       </c>
       <c r="C11" t="n">
-        <v>6.316447067549549</v>
+        <v>6.316447067549563</v>
       </c>
       <c r="D11" t="n">
-        <v>6.312773997350526</v>
+        <v>6.312773997350532</v>
       </c>
       <c r="E11" t="n">
-        <v>4.331424507786795</v>
+        <v>4.331424507786794</v>
       </c>
       <c r="F11" t="n">
-        <v>6.420500449533057</v>
+        <v>6.420500449533064</v>
       </c>
       <c r="G11" t="n">
-        <v>6.264127791101757</v>
+        <v>6.264127791101751</v>
       </c>
       <c r="H11" t="n">
         <v>6.317149292685848</v>
@@ -7618,43 +7618,43 @@
         <v>6.369843859147565</v>
       </c>
       <c r="J11" t="n">
-        <v>6.307504044267973</v>
+        <v>6.30750404426797</v>
       </c>
       <c r="K11" t="n">
-        <v>6.366391672465805</v>
+        <v>6.366391672465804</v>
       </c>
       <c r="L11" t="n">
-        <v>6.531551083077326</v>
+        <v>6.531551083077331</v>
       </c>
       <c r="M11" t="n">
-        <v>6.337344795843852</v>
+        <v>6.337344795843858</v>
       </c>
       <c r="N11" t="n">
-        <v>6.28517918577206</v>
+        <v>6.285179185772067</v>
       </c>
       <c r="O11" t="n">
-        <v>6.348831592498418</v>
+        <v>6.348831592498416</v>
       </c>
       <c r="P11" t="n">
-        <v>6.447698145636419</v>
+        <v>6.447698145636416</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.3383510633596</v>
+        <v>6.338351063359594</v>
       </c>
       <c r="R11" t="n">
-        <v>6.705316370678354</v>
+        <v>6.705316370678358</v>
       </c>
       <c r="S11" t="n">
-        <v>6.370840245199978</v>
+        <v>6.370840245199976</v>
       </c>
       <c r="T11" t="n">
         <v>6.408400846138901</v>
       </c>
       <c r="U11" t="n">
-        <v>6.329104046940561</v>
+        <v>6.329104046940563</v>
       </c>
       <c r="V11" t="n">
-        <v>6.515507511210843</v>
+        <v>6.515507511210838</v>
       </c>
       <c r="W11" t="n">
         <v>6.095314817551208</v>
@@ -7663,13 +7663,13 @@
         <v>5.911084325545763</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.209027439164501</v>
+        <v>6.209027439164506</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3217161215971</v>
+        <v>6.321716121597103</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.012484882369667</v>
+        <v>6.012484882369664</v>
       </c>
       <c r="AB11" t="n">
         <v>6.359339287881715</v>
@@ -7841,19 +7841,19 @@
         <v>6.302567109091473</v>
       </c>
       <c r="C2" t="n">
-        <v>6.28007882599715</v>
+        <v>6.280078825997149</v>
       </c>
       <c r="D2" t="n">
-        <v>6.286646995949542</v>
+        <v>6.286646995949539</v>
       </c>
       <c r="E2" t="n">
-        <v>4.124455495865583</v>
+        <v>4.124455495865579</v>
       </c>
       <c r="F2" t="n">
         <v>6.249967613292323</v>
       </c>
       <c r="G2" t="n">
-        <v>6.325632373915908</v>
+        <v>6.325632373915905</v>
       </c>
       <c r="H2" t="n">
         <v>6.302567109091473</v>
@@ -7871,10 +7871,10 @@
         <v>6.302567109091473</v>
       </c>
       <c r="M2" t="n">
-        <v>6.298927358260072</v>
+        <v>6.29892735826007</v>
       </c>
       <c r="N2" t="n">
-        <v>6.329376505530426</v>
+        <v>6.329376505530425</v>
       </c>
       <c r="O2" t="n">
         <v>6.301747705332031</v>
@@ -7883,7 +7883,7 @@
         <v>6.301024652065128</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.302558007320499</v>
+        <v>6.302558007320498</v>
       </c>
       <c r="R2" t="n">
         <v>6.304568577233433</v>
@@ -7898,7 +7898,7 @@
         <v>6.30536719892872</v>
       </c>
       <c r="V2" t="n">
-        <v>6.525848887278472</v>
+        <v>6.525848887278462</v>
       </c>
       <c r="W2" t="n">
         <v>6.302567109091473</v>
@@ -7907,10 +7907,10 @@
         <v>6.305430476442289</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.299461275144095</v>
+        <v>6.299461275144096</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.276978756981038</v>
+        <v>6.276978756981033</v>
       </c>
       <c r="AA2" t="n">
         <v>6.302567109091473</v>
@@ -7926,16 +7926,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="C3" t="n">
-        <v>12.66150158687358</v>
+        <v>12.66150158687359</v>
       </c>
       <c r="D3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="E3" t="n">
-        <v>10.53554684855111</v>
+        <v>10.5355468485511</v>
       </c>
       <c r="F3" t="n">
         <v>12.66184020919415</v>
@@ -7944,31 +7944,31 @@
         <v>12.66219655400746</v>
       </c>
       <c r="H3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="I3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="J3" t="n">
         <v>12.66267152204858</v>
       </c>
       <c r="K3" t="n">
-        <v>12.66213247289858</v>
+        <v>12.66213247289859</v>
       </c>
       <c r="L3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="M3" t="n">
         <v>12.66075616989707</v>
       </c>
       <c r="N3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="O3" t="n">
-        <v>12.66162466129584</v>
+        <v>12.66162466129585</v>
       </c>
       <c r="P3" t="n">
-        <v>12.66083342307486</v>
+        <v>12.66083342307487</v>
       </c>
       <c r="Q3" t="n">
         <v>12.66251137562627</v>
@@ -7977,19 +7977,19 @@
         <v>12.6647115444802</v>
       </c>
       <c r="S3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="T3" t="n">
         <v>12.66123004860307</v>
       </c>
       <c r="U3" t="n">
-        <v>12.66558547638232</v>
+        <v>12.66558547638233</v>
       </c>
       <c r="V3" t="n">
-        <v>12.87406987398979</v>
+        <v>12.87406987398978</v>
       </c>
       <c r="W3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="X3" t="n">
         <v>12.66565472161439</v>
@@ -8001,10 +8001,10 @@
         <v>12.66243135526142</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.66252133577614</v>
+        <v>12.66252133577615</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.67290277333821</v>
+        <v>12.67290277333822</v>
       </c>
     </row>
     <row r="4">
@@ -8014,85 +8014,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-15.07880946868964</v>
+        <v>-15.07880946868965</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.479534711449294</v>
+        <v>-2.479534711449304</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.112794942416588</v>
+        <v>-1.112794942416595</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.8908926018786</v>
+        <v>-16.89089260187861</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.50247875871684</v>
+        <v>-10.50247875871685</v>
       </c>
       <c r="G4" t="n">
-        <v>7.771966599074329</v>
+        <v>7.771966599074317</v>
       </c>
       <c r="H4" t="n">
-        <v>5.55428968532231</v>
+        <v>5.554289685322304</v>
       </c>
       <c r="I4" t="n">
-        <v>1.89310291428676</v>
+        <v>1.893102914286752</v>
       </c>
       <c r="J4" t="n">
-        <v>2.741711416227945</v>
+        <v>2.741711416227941</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4981043365698954</v>
+        <v>0.4981043365698858</v>
       </c>
       <c r="L4" t="n">
-        <v>-16.83273453313422</v>
+        <v>-16.83273453313424</v>
       </c>
       <c r="M4" t="n">
-        <v>2.360116646986777</v>
+        <v>2.360116646986766</v>
       </c>
       <c r="N4" t="n">
-        <v>3.062933130959039</v>
+        <v>3.062933130959032</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.03169585032496</v>
+        <v>-5.031695850324975</v>
       </c>
       <c r="P4" t="n">
-        <v>-9.831869090591235</v>
+        <v>-9.831869090591221</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.458468134974496</v>
+        <v>2.458468134974492</v>
       </c>
       <c r="R4" t="n">
         <v>-33.55296660464131</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.988027214283562</v>
+        <v>-4.988027214283564</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.496691438579497</v>
+        <v>-2.496691438579503</v>
       </c>
       <c r="U4" t="n">
-        <v>3.062933130959037</v>
+        <v>3.062933130959032</v>
       </c>
       <c r="V4" t="n">
-        <v>6.029377195518501</v>
+        <v>6.029377195518508</v>
       </c>
       <c r="W4" t="n">
         <v>20.57547276706428</v>
       </c>
       <c r="X4" t="n">
-        <v>52.56197602129531</v>
+        <v>52.56197602129533</v>
       </c>
       <c r="Y4" t="n">
         <v>10.2059704022025</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.912078172052705</v>
+        <v>-2.912078172052711</v>
       </c>
       <c r="AA4" t="n">
-        <v>37.25056085949003</v>
+        <v>37.25056085949</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.287002053199477</v>
+        <v>2.287002053199478</v>
       </c>
     </row>
     <row r="5">
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="H5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="I5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5818409380965115</v>
+        <v>0.5818409380965083</v>
       </c>
       <c r="K5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="L5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="M5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5831661254386222</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="R5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="T5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5767534374404267</v>
+        <v>0.5767534374404311</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5743103060537456</v>
+        <v>0.5743103060537476</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5767534374404267</v>
+        <v>0.5767534374404311</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.583166125438622</v>
+        <v>0.5831661254386276</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5831661254386221</v>
+        <v>0.5831661254386269</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6325998833021508</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6325998833021508</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6325998833021508</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="J6" t="n">
-        <v>0.890162435322118</v>
+        <v>0.631274695960039</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6325998833021508</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6393570315051846</v>
+        <v>0.6393570315051952</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6393570315052107</v>
+        <v>0.9184536279450183</v>
       </c>
       <c r="P6" t="n">
-        <v>0.918397500840301</v>
+        <v>0.9183975008403032</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6325998833021508</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.8914876226642249</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6237440639172732</v>
+        <v>0.6237440639172723</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9185845879944604</v>
+        <v>0.9185845879944587</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64773097589379</v>
+        <v>0.647730975893788</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8914876226642287</v>
+        <v>0.6325998833021511</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6394019003486811</v>
+        <v>0.6394019003486799</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9962723321022373</v>
+        <v>0.9962723321022356</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9957067474792696</v>
+        <v>0.9957067474792689</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9957067474792696</v>
+        <v>0.9957067474792685</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9846561733513225</v>
+        <v>0.9846561733513224</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9887417000594709</v>
+        <v>0.9887417000594707</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9975975194443486</v>
+        <v>0.9975975194443477</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.080421181593091</v>
+        <v>1.08042118159309</v>
       </c>
       <c r="C8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="D8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="E8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.267393200940945</v>
       </c>
       <c r="F8" t="n">
-        <v>1.142723251367937</v>
+        <v>1.142723251367939</v>
       </c>
       <c r="G8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.563261058929249</v>
       </c>
       <c r="H8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="I8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="J8" t="n">
-        <v>1.479010908854466</v>
+        <v>1.47901090885446</v>
       </c>
       <c r="K8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="L8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="M8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096194135</v>
       </c>
       <c r="N8" t="n">
-        <v>1.170335133037711</v>
+        <v>1.170335133037717</v>
       </c>
       <c r="O8" t="n">
-        <v>1.255526089348383</v>
+        <v>1.255526089348388</v>
       </c>
       <c r="P8" t="n">
-        <v>1.234643727460676</v>
+        <v>1.23464372746067</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.001828773288275</v>
+        <v>1.00182877328827</v>
       </c>
       <c r="R8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="S8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="T8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2262078803245</v>
+        <v>1.276579040237917</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4714802768117</v>
+        <v>1.352731743409554</v>
       </c>
       <c r="W8" t="n">
-        <v>1.480414690819661</v>
+        <v>1.480414690819656</v>
       </c>
       <c r="X8" t="n">
-        <v>1.038481769783616</v>
+        <v>1.038481769783615</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.863312011336897</v>
+        <v>1.863312011336885</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.072992556743747</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.480336096196577</v>
+        <v>1.480336096196575</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.898080664740343</v>
+        <v>1.898080664740339</v>
       </c>
     </row>
     <row r="9">
@@ -8457,82 +8457,82 @@
         <v>1.758906709223369</v>
       </c>
       <c r="C9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="D9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="E9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.037130137049834</v>
       </c>
       <c r="F9" t="n">
-        <v>2.120609765680261</v>
+        <v>1.286785567850186</v>
       </c>
       <c r="G9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609715550459</v>
       </c>
       <c r="H9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="I9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="J9" t="n">
-        <v>2.119284578338152</v>
+        <v>2.119284578338151</v>
       </c>
       <c r="K9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="L9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="M9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="N9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="O9" t="n">
-        <v>2.240477618237558</v>
+        <v>2.240477618237559</v>
       </c>
       <c r="P9" t="n">
         <v>2.266546830485138</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.120609715550458</v>
+        <v>2.120609715550459</v>
       </c>
       <c r="R9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="S9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="T9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="U9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="V9" t="n">
-        <v>2.111753946295383</v>
+        <v>2.529151472634567</v>
       </c>
       <c r="W9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="X9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.120609765680261</v>
+        <v>1.902534966621471</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.120609765680261</v>
+        <v>2.120609765680263</v>
       </c>
     </row>
     <row r="10">
@@ -8548,7 +8548,7 @@
         <v>12.73615021189682</v>
       </c>
       <c r="D10" t="n">
-        <v>12.70406939687971</v>
+        <v>12.7040693968797</v>
       </c>
       <c r="E10" t="n">
         <v>10.98205878755787</v>
@@ -8584,7 +8584,7 @@
         <v>12.8141725052889</v>
       </c>
       <c r="P10" t="n">
-        <v>12.93870054632157</v>
+        <v>12.93870054632158</v>
       </c>
       <c r="Q10" t="n">
         <v>12.61766214185667</v>
@@ -8611,7 +8611,7 @@
         <v>11.38280403219609</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.43793290447937</v>
+        <v>12.43793290447938</v>
       </c>
       <c r="Z10" t="n">
         <v>12.76153888010957</v>
@@ -8630,85 +8630,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.486212106684654</v>
+        <v>6.486212106684651</v>
       </c>
       <c r="C11" t="n">
-        <v>6.31404418827378</v>
+        <v>6.314044188273779</v>
       </c>
       <c r="D11" t="n">
-        <v>6.305551496157483</v>
+        <v>6.305551496157482</v>
       </c>
       <c r="E11" t="n">
-        <v>4.32761985106278</v>
+        <v>4.327619851062777</v>
       </c>
       <c r="F11" t="n">
-        <v>6.364411249453915</v>
+        <v>6.364411249453912</v>
       </c>
       <c r="G11" t="n">
-        <v>6.238543968471472</v>
+        <v>6.238543968471471</v>
       </c>
       <c r="H11" t="n">
         <v>6.253617447651948</v>
       </c>
       <c r="I11" t="n">
-        <v>6.289528897672194</v>
+        <v>6.289528897672193</v>
       </c>
       <c r="J11" t="n">
-        <v>6.278918659564888</v>
+        <v>6.278918659564892</v>
       </c>
       <c r="K11" t="n">
-        <v>6.304302110831022</v>
+        <v>6.304302110831017</v>
       </c>
       <c r="L11" t="n">
-        <v>6.525353841006405</v>
+        <v>6.525353841006406</v>
       </c>
       <c r="M11" t="n">
-        <v>6.280873100064457</v>
+        <v>6.280873100064455</v>
       </c>
       <c r="N11" t="n">
-        <v>6.233995439991737</v>
+        <v>6.233995439991735</v>
       </c>
       <c r="O11" t="n">
-        <v>6.371157460489999</v>
+        <v>6.371157460489996</v>
       </c>
       <c r="P11" t="n">
         <v>6.427455078652359</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.282151463029305</v>
+        <v>6.282151463029303</v>
       </c>
       <c r="R11" t="n">
-        <v>6.646055019176607</v>
+        <v>6.646055019176602</v>
       </c>
       <c r="S11" t="n">
-        <v>6.370643661919227</v>
+        <v>6.370643661919225</v>
       </c>
       <c r="T11" t="n">
-        <v>6.334429150598529</v>
+        <v>6.334429150598528</v>
       </c>
       <c r="U11" t="n">
-        <v>6.276476071104119</v>
+        <v>6.276476071104114</v>
       </c>
       <c r="V11" t="n">
-        <v>6.461347626857064</v>
+        <v>6.461347626857054</v>
       </c>
       <c r="W11" t="n">
-        <v>6.081281842663044</v>
+        <v>6.081281842663041</v>
       </c>
       <c r="X11" t="n">
         <v>5.721729324554386</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.198819250487984</v>
+        <v>6.198819250487982</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.322072996623889</v>
+        <v>6.322072996623885</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.914484085897782</v>
+        <v>5.914484085897779</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.295473235506676</v>
+        <v>6.295473235506673</v>
       </c>
     </row>
   </sheetData>
@@ -8874,85 +8874,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="C2" t="n">
-        <v>6.554754096686525</v>
+        <v>6.554754096686522</v>
       </c>
       <c r="D2" t="n">
         <v>6.60540309174794</v>
       </c>
       <c r="E2" t="n">
-        <v>4.390413785197127</v>
+        <v>4.390413785197126</v>
       </c>
       <c r="F2" t="n">
-        <v>6.555983323321569</v>
+        <v>6.555983323321565</v>
       </c>
       <c r="G2" t="n">
-        <v>6.79136920943474</v>
+        <v>6.791369209434734</v>
       </c>
       <c r="H2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="I2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="J2" t="n">
-        <v>6.670281820088594</v>
+        <v>6.670281820088593</v>
       </c>
       <c r="K2" t="n">
-        <v>6.676486536307731</v>
+        <v>6.676486536307728</v>
       </c>
       <c r="L2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="M2" t="n">
-        <v>6.744482418690371</v>
+        <v>6.744482418690365</v>
       </c>
       <c r="N2" t="n">
-        <v>6.617920909287045</v>
+        <v>6.617920909287043</v>
       </c>
       <c r="O2" t="n">
-        <v>6.676040539681259</v>
+        <v>6.676040539681255</v>
       </c>
       <c r="P2" t="n">
-        <v>6.676521409758761</v>
+        <v>6.676521409758758</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.676672858389581</v>
+        <v>6.676672858389577</v>
       </c>
       <c r="R2" t="n">
-        <v>6.676645833457862</v>
+        <v>6.676645833457859</v>
       </c>
       <c r="S2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="T2" t="n">
-        <v>6.676402955317025</v>
+        <v>6.676402955317021</v>
       </c>
       <c r="U2" t="n">
-        <v>6.677311927790918</v>
+        <v>6.677311927790915</v>
       </c>
       <c r="V2" t="n">
-        <v>6.762911951373025</v>
+        <v>6.762911951373024</v>
       </c>
       <c r="W2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="X2" t="n">
-        <v>6.677205216120282</v>
+        <v>6.677205216120278</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.675209198086479</v>
+        <v>6.675209198086476</v>
       </c>
       <c r="Z2" t="n">
         <v>6.594186243829816</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.676681960160555</v>
+        <v>6.676681960160551</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.686168781628158</v>
+        <v>6.686168781628155</v>
       </c>
     </row>
     <row r="3">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="C3" t="n">
-        <v>12.89677542590333</v>
+        <v>12.89677542590332</v>
       </c>
       <c r="D3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="E3" t="n">
         <v>10.69599244250043</v>
       </c>
       <c r="F3" t="n">
-        <v>12.89738663969362</v>
+        <v>12.89738663969361</v>
       </c>
       <c r="G3" t="n">
-        <v>12.8976384512536</v>
+        <v>12.89763845125359</v>
       </c>
       <c r="H3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="I3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="J3" t="n">
         <v>12.89134936213895</v>
       </c>
       <c r="K3" t="n">
-        <v>12.89753638233869</v>
+        <v>12.89753638233868</v>
       </c>
       <c r="L3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="M3" t="n">
         <v>12.89749845762612</v>
       </c>
       <c r="N3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="O3" t="n">
-        <v>12.89704832760824</v>
+        <v>12.89704832760823</v>
       </c>
       <c r="P3" t="n">
-        <v>12.89757454403647</v>
+        <v>12.89757454403646</v>
       </c>
       <c r="Q3" t="n">
         <v>12.89774027487342</v>
       </c>
       <c r="R3" t="n">
-        <v>12.89771070127348</v>
+        <v>12.89771070127347</v>
       </c>
       <c r="S3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="T3" t="n">
         <v>12.89744491928141</v>
@@ -9025,19 +9025,19 @@
         <v>13.09205046585258</v>
       </c>
       <c r="W3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="X3" t="n">
         <v>12.89832283438172</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.89613858983468</v>
+        <v>12.89613858983467</v>
       </c>
       <c r="Z3" t="n">
         <v>12.89769584814842</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.8977502350233</v>
+        <v>12.89775023502329</v>
       </c>
       <c r="AB3" t="n">
         <v>12.90813167258536</v>
@@ -9053,82 +9053,82 @@
         <v>17.81556862269282</v>
       </c>
       <c r="C4" t="n">
-        <v>9.00921924752091</v>
+        <v>9.009219247520912</v>
       </c>
       <c r="D4" t="n">
-        <v>23.45217582211287</v>
+        <v>23.45217582211285</v>
       </c>
       <c r="E4" t="n">
-        <v>9.450846202740435</v>
+        <v>9.450846202740445</v>
       </c>
       <c r="F4" t="n">
-        <v>9.410873332013187</v>
+        <v>9.41087333201315</v>
       </c>
       <c r="G4" t="n">
-        <v>65.89118949762532</v>
+        <v>65.89118949762536</v>
       </c>
       <c r="H4" t="n">
-        <v>35.47252585587281</v>
+        <v>35.47252585587276</v>
       </c>
       <c r="I4" t="n">
-        <v>11.09704467490719</v>
+        <v>11.09704467490721</v>
       </c>
       <c r="J4" t="n">
-        <v>38.92899935168003</v>
+        <v>38.92899935168005</v>
       </c>
       <c r="K4" t="n">
-        <v>18.68664915930543</v>
+        <v>18.68664915930542</v>
       </c>
       <c r="L4" t="n">
-        <v>35.08840823693059</v>
+        <v>35.08840823693058</v>
       </c>
       <c r="M4" t="n">
-        <v>58.25739155888088</v>
+        <v>58.25739155888091</v>
       </c>
       <c r="N4" t="n">
-        <v>38.26182806751067</v>
+        <v>38.2618280675109</v>
       </c>
       <c r="O4" t="n">
-        <v>18.27274470149166</v>
+        <v>18.27274470149169</v>
       </c>
       <c r="P4" t="n">
-        <v>29.83224516038749</v>
+        <v>29.83224516038728</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.85163186878087</v>
+        <v>14.85163186878085</v>
       </c>
       <c r="R4" t="n">
-        <v>5.325717169527986</v>
+        <v>5.325717169527973</v>
       </c>
       <c r="S4" t="n">
-        <v>27.89709454877729</v>
+        <v>27.89709454877719</v>
       </c>
       <c r="T4" t="n">
         <v>14.53490941773199</v>
       </c>
       <c r="U4" t="n">
-        <v>38.26182806751067</v>
+        <v>38.26182806751089</v>
       </c>
       <c r="V4" t="n">
-        <v>12.17960649891585</v>
+        <v>12.17960649891582</v>
       </c>
       <c r="W4" t="n">
-        <v>48.48487380498609</v>
+        <v>48.48487380498607</v>
       </c>
       <c r="X4" t="n">
-        <v>37.04386617411245</v>
+        <v>37.04386617411252</v>
       </c>
       <c r="Y4" t="n">
-        <v>33.19187555937146</v>
+        <v>33.1918755593713</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.01277939467453</v>
+        <v>18.01277939467455</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.41403353065967</v>
+        <v>35.41403353065959</v>
       </c>
       <c r="AB4" t="n">
-        <v>52.49224551545665</v>
+        <v>52.49224551545657</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="C5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="D5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="E5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="F5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="G5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="H5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="I5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="J5" t="n">
         <v>1.084813094521467</v>
       </c>
       <c r="K5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="L5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="M5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="N5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="O5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="P5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="R5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="S5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="T5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="U5" t="n">
         <v>1.057106875238479</v>
       </c>
       <c r="V5" t="n">
-        <v>1.070163454350768</v>
+        <v>1.070163454350769</v>
       </c>
       <c r="W5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="X5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="Y5" t="n">
         <v>1.057106875238479</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.087463503786493</v>
+        <v>1.087463503786494</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="C6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="D6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="E6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="F6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="H6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="I6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="J6" t="n">
-        <v>1.775787395683924</v>
+        <v>1.208662765999765</v>
       </c>
       <c r="K6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="M6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="N6" t="n">
-        <v>1.215738797033018</v>
+        <v>1.215738797033062</v>
       </c>
       <c r="O6" t="n">
-        <v>1.215738797032992</v>
+        <v>1.215738797033062</v>
       </c>
       <c r="P6" t="n">
-        <v>1.809614824087883</v>
+        <v>1.809614824087881</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="R6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="S6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="T6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="U6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="V6" t="n">
-        <v>1.194013125829065</v>
+        <v>1.761137755513225</v>
       </c>
       <c r="W6" t="n">
-        <v>1.242057893417693</v>
+        <v>1.242057893417719</v>
       </c>
       <c r="X6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.225515191911233</v>
+        <v>1.225515191911301</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.21131317526479</v>
+        <v>1.211313175264791</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.778437804948953</v>
+        <v>1.77843780494895</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2239803527282</v>
+        <v>1.223980352728199</v>
       </c>
     </row>
     <row r="7">
@@ -9371,10 +9371,10 @@
         <v>1.740996892222624</v>
       </c>
       <c r="U7" t="n">
-        <v>1.737943177354233</v>
+        <v>1.737943177354232</v>
       </c>
       <c r="V7" t="n">
-        <v>1.723696842786899</v>
+        <v>1.7236968427869</v>
       </c>
       <c r="W7" t="n">
         <v>1.740996892222624</v>
@@ -9405,82 +9405,82 @@
         <v>2.014811089652385</v>
       </c>
       <c r="C8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="D8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="E8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.360648081415296</v>
       </c>
       <c r="F8" t="n">
-        <v>2.130049511181263</v>
+        <v>2.130049511181264</v>
       </c>
       <c r="G8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.9079067048259</v>
       </c>
       <c r="H8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="I8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="J8" t="n">
-        <v>2.751872277230506</v>
+        <v>2.751872277230509</v>
       </c>
       <c r="K8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="L8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="M8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495139</v>
       </c>
       <c r="N8" t="n">
-        <v>2.181122447739574</v>
+        <v>2.181122447739576</v>
       </c>
       <c r="O8" t="n">
-        <v>2.338697811805021</v>
+        <v>2.338697811805022</v>
       </c>
       <c r="P8" t="n">
-        <v>2.300072282548773</v>
+        <v>2.300072282548774</v>
       </c>
       <c r="Q8" t="n">
         <v>1.869440877933448</v>
       </c>
       <c r="R8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="S8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="T8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="U8" t="n">
-        <v>2.298603879789622</v>
+        <v>2.39269251644828</v>
       </c>
       <c r="V8" t="n">
-        <v>2.737222637059811</v>
+        <v>2.534180473077675</v>
       </c>
       <c r="W8" t="n">
-        <v>2.754668060446551</v>
+        <v>2.754668060446548</v>
       </c>
       <c r="X8" t="n">
         <v>1.937236915261483</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.488655083560197</v>
+        <v>3.4886550835602</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.001070567021202</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.754522686495536</v>
+        <v>2.754522686495537</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.527213302542809</v>
+        <v>3.527213302542806</v>
       </c>
     </row>
     <row r="9">
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.601819027607421</v>
+        <v>3.601819027607422</v>
       </c>
       <c r="C9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="D9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="E9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.187073493839621</v>
       </c>
       <c r="F9" t="n">
-        <v>4.362676133154938</v>
+        <v>2.608692716319074</v>
       </c>
       <c r="G9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676233473483</v>
       </c>
       <c r="H9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="I9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="J9" t="n">
-        <v>4.360025723889914</v>
+        <v>4.360025723889916</v>
       </c>
       <c r="K9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="L9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="M9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="N9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="O9" t="n">
-        <v>4.61482331524001</v>
+        <v>4.614823315240012</v>
       </c>
       <c r="P9" t="n">
-        <v>4.669660979408875</v>
+        <v>4.66966097940888</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.36267623347348</v>
+        <v>4.362676233473483</v>
       </c>
       <c r="R9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="S9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="T9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="U9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="V9" t="n">
-        <v>4.345376083719215</v>
+        <v>5.223388048796004</v>
       </c>
       <c r="W9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="X9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.362676133154938</v>
+        <v>3.903946996398826</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.362676133154938</v>
+        <v>4.362676133154943</v>
       </c>
     </row>
     <row r="10">
@@ -9596,7 +9596,7 @@
         <v>11.32358676261711</v>
       </c>
       <c r="H10" t="n">
-        <v>12.21694973350018</v>
+        <v>12.21694973350017</v>
       </c>
       <c r="I10" t="n">
         <v>12.69183308143361</v>
@@ -9611,7 +9611,7 @@
         <v>12.1247550199186</v>
       </c>
       <c r="M10" t="n">
-        <v>11.62558244267024</v>
+        <v>11.62558244267023</v>
       </c>
       <c r="N10" t="n">
         <v>12.36140915585738</v>
@@ -9632,7 +9632,7 @@
         <v>12.23581068366185</v>
       </c>
       <c r="T10" t="n">
-        <v>12.61973651970241</v>
+        <v>12.6197365197024</v>
       </c>
       <c r="U10" t="n">
         <v>12.05933018862176</v>
@@ -9644,16 +9644,16 @@
         <v>11.86887257517221</v>
       </c>
       <c r="X10" t="n">
-        <v>12.14243723074618</v>
+        <v>12.14243723074617</v>
       </c>
       <c r="Y10" t="n">
         <v>12.18977762507977</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.49660152957937</v>
+        <v>12.49660152957936</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.15071468632043</v>
+        <v>12.15071468632042</v>
       </c>
       <c r="AB10" t="n">
         <v>11.89512149924867</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.494642268947603</v>
+        <v>6.494642268947602</v>
       </c>
       <c r="C11" t="n">
-        <v>6.477634758960893</v>
+        <v>6.47763475896089</v>
       </c>
       <c r="D11" t="n">
         <v>6.395758153446301</v>
@@ -9678,49 +9678,49 @@
         <v>4.306869855873567</v>
       </c>
       <c r="F11" t="n">
-        <v>6.47755251764243</v>
+        <v>6.477552517642428</v>
       </c>
       <c r="G11" t="n">
-        <v>6.075170674900037</v>
+        <v>6.075170674900035</v>
       </c>
       <c r="H11" t="n">
-        <v>6.366915562385064</v>
+        <v>6.366915562385062</v>
       </c>
       <c r="I11" t="n">
-        <v>6.582988999058216</v>
+        <v>6.582988999058212</v>
       </c>
       <c r="J11" t="n">
-        <v>6.266297680205918</v>
+        <v>6.266297680205914</v>
       </c>
       <c r="K11" t="n">
-        <v>6.492442065045123</v>
+        <v>6.492442065045121</v>
       </c>
       <c r="L11" t="n">
-        <v>6.324966673898328</v>
+        <v>6.324966673898329</v>
       </c>
       <c r="M11" t="n">
         <v>6.165756578529605</v>
       </c>
       <c r="N11" t="n">
-        <v>6.373884009048955</v>
+        <v>6.373884009048952</v>
       </c>
       <c r="O11" t="n">
-        <v>6.483912648865039</v>
+        <v>6.483912648865035</v>
       </c>
       <c r="P11" t="n">
-        <v>6.371517618565421</v>
+        <v>6.371517618565425</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.540590347891902</v>
+        <v>6.540590347891898</v>
       </c>
       <c r="R11" t="n">
-        <v>6.637775909654684</v>
+        <v>6.637775909654683</v>
       </c>
       <c r="S11" t="n">
-        <v>6.37549735481491</v>
+        <v>6.375497354814906</v>
       </c>
       <c r="T11" t="n">
-        <v>6.55004474850442</v>
+        <v>6.550044748504416</v>
       </c>
       <c r="U11" t="n">
         <v>6.295514467436479</v>
@@ -9732,19 +9732,19 @@
         <v>6.208539346089751</v>
       </c>
       <c r="X11" t="n">
-        <v>6.333274857601615</v>
+        <v>6.333274857601613</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.353812708084162</v>
+        <v>6.35381270808416</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.41168705066914</v>
+        <v>6.411687050669138</v>
       </c>
       <c r="AA11" t="n">
         <v>6.336778404839707</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.225245924488087</v>
+        <v>6.225245924488086</v>
       </c>
     </row>
   </sheetData>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="C2" t="n">
-        <v>6.437370962955276</v>
+        <v>6.437370962955282</v>
       </c>
       <c r="D2" t="n">
-        <v>6.453000865751891</v>
+        <v>6.453000865751886</v>
       </c>
       <c r="E2" t="n">
-        <v>4.28949639058963</v>
+        <v>4.289496390589633</v>
       </c>
       <c r="F2" t="n">
-        <v>6.384693766931315</v>
+        <v>6.38469376693132</v>
       </c>
       <c r="G2" t="n">
-        <v>6.65286687058735</v>
+        <v>6.652866870587347</v>
       </c>
       <c r="H2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="I2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="J2" t="n">
-        <v>6.505049330713772</v>
+        <v>6.505049330713769</v>
       </c>
       <c r="K2" t="n">
-        <v>6.509577759579254</v>
+        <v>6.509577759579257</v>
       </c>
       <c r="L2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="M2" t="n">
-        <v>6.440331192693417</v>
+        <v>6.44033119269342</v>
       </c>
       <c r="N2" t="n">
-        <v>6.448350228964903</v>
+        <v>6.448350228964899</v>
       </c>
       <c r="O2" t="n">
-        <v>6.509138684767586</v>
+        <v>6.509138684767588</v>
       </c>
       <c r="P2" t="n">
-        <v>6.50977395994336</v>
+        <v>6.509773959943363</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.509845852638787</v>
+        <v>6.50984585263879</v>
       </c>
       <c r="R2" t="n">
-        <v>6.510893230939241</v>
+        <v>6.510893230939244</v>
       </c>
       <c r="S2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="T2" t="n">
-        <v>6.509033286979893</v>
+        <v>6.509033286979895</v>
       </c>
       <c r="U2" t="n">
-        <v>6.510839829245746</v>
+        <v>6.510839829245748</v>
       </c>
       <c r="V2" t="n">
         <v>6.664795798845324</v>
       </c>
       <c r="W2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="X2" t="n">
-        <v>6.516100715654533</v>
+        <v>6.516100715654535</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.508084753736003</v>
+        <v>6.508084753736005</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.461503103414137</v>
+        <v>6.461503103414141</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.509854954409762</v>
+        <v>6.509854954409764</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.519341775877364</v>
+        <v>6.519341775877367</v>
       </c>
     </row>
     <row r="3">
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.163800582603433</v>
+        <v>-1.163800582603442</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447534452416964</v>
+        <v>1.44753445241695</v>
       </c>
       <c r="D4" t="n">
         <v>5.150248621464506</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.585014927232556</v>
+        <v>-1.585014927232576</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.08369906559697</v>
+        <v>-12.08369906559699</v>
       </c>
       <c r="G4" t="n">
-        <v>48.12532239302422</v>
+        <v>48.12532239302399</v>
       </c>
       <c r="H4" t="n">
-        <v>22.83577468961138</v>
+        <v>22.83577468961121</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.937088418178889</v>
+        <v>-1.937088418178901</v>
       </c>
       <c r="J4" t="n">
-        <v>17.24037104803309</v>
+        <v>17.24037104803305</v>
       </c>
       <c r="K4" t="n">
-        <v>1.634795697386883</v>
+        <v>1.634795697386885</v>
       </c>
       <c r="L4" t="n">
         <v>-15.79400171376825</v>
       </c>
       <c r="M4" t="n">
-        <v>2.157525720645344</v>
+        <v>2.157525720645335</v>
       </c>
       <c r="N4" t="n">
-        <v>6.931422677343932</v>
+        <v>6.931422677343864</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.520334986073355</v>
+        <v>-2.5203349860733</v>
       </c>
       <c r="P4" t="n">
-        <v>11.3712563716644</v>
+        <v>11.37125637166442</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.488756837759592</v>
+        <v>1.488756837759611</v>
       </c>
       <c r="R4" t="n">
-        <v>-29.56395658459864</v>
+        <v>-29.56395658459865</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.600583978791764</v>
+        <v>-6.600583978791756</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.840776717919773</v>
+        <v>-8.840776717919793</v>
       </c>
       <c r="U4" t="n">
-        <v>6.931422677343933</v>
+        <v>6.931422677343867</v>
       </c>
       <c r="V4" t="n">
-        <v>7.824814426187101</v>
+        <v>7.824814426187091</v>
       </c>
       <c r="W4" t="n">
-        <v>32.2661832279722</v>
+        <v>32.26618322797216</v>
       </c>
       <c r="X4" t="n">
-        <v>38.48145229171573</v>
+        <v>38.4814522917156</v>
       </c>
       <c r="Y4" t="n">
-        <v>49.91491884723814</v>
+        <v>49.91491884723805</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.514023060134707</v>
+        <v>6.514023060134695</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.34575537070553</v>
+        <v>17.34575537070556</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.64324130905388</v>
+        <v>29.64324130905382</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8285880030635731</v>
+        <v>0.8285880030635715</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348862</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8101736904700465</v>
+        <v>0.8101736904700396</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8157036686259788</v>
+        <v>0.8157036686259764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8101736904700465</v>
+        <v>0.8101736904700396</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8309088617348936</v>
+        <v>0.8309088617348859</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8309088617348981</v>
+        <v>0.8309088617348861</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.358737063105528</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="C6" t="n">
-        <v>1.358737063105528</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9134319853929016</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="G6" t="n">
-        <v>1.358737063105528</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="J6" t="n">
-        <v>1.356416204434217</v>
+        <v>0.9111111267215883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="L6" t="n">
-        <v>1.358737063105528</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9174239325602832</v>
+        <v>0.9174239325602331</v>
       </c>
       <c r="O6" t="n">
-        <v>1.388235097015464</v>
+        <v>0.9174239325601897</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9018391441607806</v>
+        <v>0.9018391441606952</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9134319853929016</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="R6" t="n">
-        <v>1.358737063105528</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9134319853929016</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9134319853929016</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="U6" t="n">
-        <v>1.358737063105528</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="V6" t="n">
-        <v>1.343531869996625</v>
+        <v>1.343531869996624</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9381939939695655</v>
+        <v>0.9381939939695539</v>
       </c>
       <c r="X6" t="n">
-        <v>1.358737063105528</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9251598613101014</v>
+        <v>0.9251598613104086</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9134319853929016</v>
+        <v>0.9134319853929048</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.358737063105528</v>
+        <v>1.358737063105532</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9231107520503483</v>
+        <v>0.9231107520503415</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="C7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="D7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="E7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="F7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="G7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="H7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="I7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="J7" t="n">
-        <v>1.342073444592059</v>
+        <v>1.342073444592065</v>
       </c>
       <c r="K7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="L7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="M7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="N7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263378</v>
       </c>
       <c r="O7" t="n">
         <v>1.342497701318797</v>
       </c>
       <c r="P7" t="n">
-        <v>1.342497701318797</v>
+        <v>1.342497701318796</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="R7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="S7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="T7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="U7" t="n">
-        <v>1.337858518349408</v>
+        <v>1.337858518349406</v>
       </c>
       <c r="V7" t="n">
         <v>1.32918911015447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="X7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.344394303263393</v>
+        <v>1.344394303263379</v>
       </c>
     </row>
     <row r="8">
@@ -10438,85 +10438,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.521876224802238</v>
+        <v>1.521876224802236</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08100180580218</v>
+        <v>1.783283927189895</v>
       </c>
       <c r="F8" t="n">
-        <v>1.608981455627053</v>
+        <v>1.608981455627057</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.1969401373455</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="J8" t="n">
-        <v>2.078680947130862</v>
+        <v>2.078680947130864</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="L8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="M8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805801598</v>
       </c>
       <c r="N8" t="n">
-        <v>1.647585940728229</v>
+        <v>1.64758594072824</v>
       </c>
       <c r="O8" t="n">
-        <v>1.766692383483384</v>
+        <v>1.766692383483379</v>
       </c>
       <c r="P8" t="n">
-        <v>1.737496516375045</v>
+        <v>1.737496516375055</v>
       </c>
       <c r="Q8" t="n">
         <v>1.411995286850449</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="U8" t="n">
-        <v>1.733569145316572</v>
+        <v>1.804504819071417</v>
       </c>
       <c r="V8" t="n">
-        <v>2.065796612693268</v>
+        <v>1.90901370177329</v>
       </c>
       <c r="W8" t="n">
-        <v>2.081111689507591</v>
+        <v>2.081111689507586</v>
       </c>
       <c r="X8" t="n">
-        <v>1.463240257046726</v>
+        <v>1.463240257046727</v>
       </c>
       <c r="Y8" t="n">
         <v>2.630777212614138</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.08100180580218</v>
+        <v>1.511490180123139</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08100180580218</v>
+        <v>2.081001805802177</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.66505522801652</v>
+        <v>2.665055228016525</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.695680883318069</v>
+        <v>2.695680883318072</v>
       </c>
       <c r="C9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="D9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="E9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.132575750936078</v>
       </c>
       <c r="F9" t="n">
-        <v>3.26366343635724</v>
+        <v>1.954308004796317</v>
       </c>
       <c r="G9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.26366391875412</v>
       </c>
       <c r="H9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="I9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="J9" t="n">
-        <v>3.261342577685931</v>
+        <v>3.261342577685922</v>
       </c>
       <c r="K9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="L9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="M9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="N9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="O9" t="n">
-        <v>3.451892752987301</v>
+        <v>3.451892752987297</v>
       </c>
       <c r="P9" t="n">
-        <v>3.492829294970105</v>
+        <v>3.492829294970098</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.263663918754117</v>
+        <v>3.26366391875412</v>
       </c>
       <c r="R9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="S9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="U9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="V9" t="n">
-        <v>3.248458243248327</v>
+        <v>3.903898436797224</v>
       </c>
       <c r="W9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="X9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.26366343635724</v>
+        <v>2.921220655408328</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.26366343635724</v>
+        <v>3.263663436357235</v>
       </c>
     </row>
     <row r="10">
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.85740303358429</v>
+        <v>12.85740303358428</v>
       </c>
       <c r="C10" t="n">
         <v>12.79317868158657</v>
@@ -10623,46 +10623,46 @@
         <v>12.70814450993973</v>
       </c>
       <c r="E10" t="n">
-        <v>10.69261305931792</v>
+        <v>10.69261305931791</v>
       </c>
       <c r="F10" t="n">
         <v>13.10353908630958</v>
       </c>
       <c r="G10" t="n">
-        <v>11.51692546134268</v>
+        <v>11.51692546134269</v>
       </c>
       <c r="H10" t="n">
-        <v>12.34232531057618</v>
+        <v>12.34232531057617</v>
       </c>
       <c r="I10" t="n">
-        <v>12.86720215947331</v>
+        <v>12.86720215947332</v>
       </c>
       <c r="J10" t="n">
         <v>12.36416674344303</v>
       </c>
       <c r="K10" t="n">
-        <v>12.79108560327115</v>
+        <v>12.79108560327114</v>
       </c>
       <c r="L10" t="n">
-        <v>13.24527668696923</v>
+        <v>13.24527668696924</v>
       </c>
       <c r="M10" t="n">
         <v>12.77813864144407</v>
       </c>
       <c r="N10" t="n">
-        <v>12.73508260988524</v>
+        <v>12.73508260988525</v>
       </c>
       <c r="O10" t="n">
         <v>12.89860269535443</v>
       </c>
       <c r="P10" t="n">
-        <v>12.53557402581586</v>
+        <v>12.53557402581587</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.79214247155761</v>
+        <v>12.7921424715576</v>
       </c>
       <c r="R10" t="n">
-        <v>13.46417237588951</v>
+        <v>13.4641723758895</v>
       </c>
       <c r="S10" t="n">
         <v>13.00896990307928</v>
@@ -10677,16 +10677,16 @@
         <v>12.82288504560979</v>
       </c>
       <c r="W10" t="n">
-        <v>12.07431355775998</v>
+        <v>12.07431355775997</v>
       </c>
       <c r="X10" t="n">
         <v>11.93373311433693</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.6476822901115</v>
+        <v>11.64768229011149</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.65559512726103</v>
+        <v>12.65559512726104</v>
       </c>
       <c r="AA10" t="n">
         <v>12.42162491299676</v>
@@ -10702,85 +10702,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.533088839000154</v>
+        <v>6.533088839000156</v>
       </c>
       <c r="C11" t="n">
-        <v>6.431848373606694</v>
+        <v>6.431848373606693</v>
       </c>
       <c r="D11" t="n">
-        <v>6.408321646425319</v>
+        <v>6.408321646425316</v>
       </c>
       <c r="E11" t="n">
-        <v>4.315537244406044</v>
+        <v>4.315537244406045</v>
       </c>
       <c r="F11" t="n">
-        <v>6.520153837915721</v>
+        <v>6.520153837915716</v>
       </c>
       <c r="G11" t="n">
-        <v>6.066274740860983</v>
+        <v>6.066274740860981</v>
       </c>
       <c r="H11" t="n">
-        <v>6.298726833576155</v>
+        <v>6.298726833576154</v>
       </c>
       <c r="I11" t="n">
-        <v>6.537547472507637</v>
+        <v>6.537547472507629</v>
       </c>
       <c r="J11" t="n">
-        <v>6.306045955540359</v>
+        <v>6.306045955540355</v>
       </c>
       <c r="K11" t="n">
-        <v>6.502775020388997</v>
+        <v>6.502775020388984</v>
       </c>
       <c r="L11" t="n">
         <v>6.709572587370303</v>
       </c>
       <c r="M11" t="n">
-        <v>6.427809396492827</v>
+        <v>6.427809396492822</v>
       </c>
       <c r="N11" t="n">
-        <v>6.415927930960171</v>
+        <v>6.415927930960168</v>
       </c>
       <c r="O11" t="n">
-        <v>6.551475185101795</v>
+        <v>6.551475185101794</v>
       </c>
       <c r="P11" t="n">
-        <v>6.386614948446777</v>
+        <v>6.386614948446771</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.503390505433901</v>
+        <v>6.503390505433905</v>
       </c>
       <c r="R11" t="n">
-        <v>6.809692131175725</v>
+        <v>6.809692131175723</v>
       </c>
       <c r="S11" t="n">
-        <v>6.602052247635331</v>
+        <v>6.602052247635334</v>
       </c>
       <c r="T11" t="n">
         <v>6.608017150720602</v>
       </c>
       <c r="U11" t="n">
-        <v>6.440471934739096</v>
+        <v>6.440471934739098</v>
       </c>
       <c r="V11" t="n">
-        <v>6.580903276128739</v>
+        <v>6.58090327612874</v>
       </c>
       <c r="W11" t="n">
-        <v>6.176780631942005</v>
+        <v>6.176780631942003</v>
       </c>
       <c r="X11" t="n">
-        <v>6.115952013696209</v>
+        <v>6.115952013696208</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.981773246605369</v>
+        <v>5.98177324660537</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.392955357184655</v>
+        <v>6.392955357184656</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.334808405390361</v>
+        <v>6.334808405390364</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.235280518620667</v>
+        <v>6.235280518620669</v>
       </c>
     </row>
   </sheetData>

--- a/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
@@ -886,7 +886,7 @@
         <v>0.8090728879632745</v>
       </c>
       <c r="N5" t="n">
-        <v>45.97326141195387</v>
+        <v>0.8090728879632733</v>
       </c>
       <c r="O5" t="n">
         <v>0.8090728879632733</v>
@@ -974,7 +974,7 @@
         <v>1.607913103221029</v>
       </c>
       <c r="N6" t="n">
-        <v>45.97326141195387</v>
+        <v>0.9905179081235741</v>
       </c>
       <c r="O6" t="n">
         <v>0.9905172360190946</v>
@@ -1062,7 +1062,7 @@
         <v>1.568489131524303</v>
       </c>
       <c r="N7" t="n">
-        <v>45.97326141195387</v>
+        <v>1.568489131524303</v>
       </c>
       <c r="O7" t="n">
         <v>1.566307755273997</v>
@@ -1150,7 +1150,7 @@
         <v>2.784346547661483</v>
       </c>
       <c r="N8" t="n">
-        <v>45.97326141195387</v>
+        <v>2.109767366161005</v>
       </c>
       <c r="O8" t="n">
         <v>2.295147582199739</v>
@@ -1238,7 +1238,7 @@
         <v>4.84501653793898</v>
       </c>
       <c r="N9" t="n">
-        <v>45.97326141195387</v>
+        <v>4.84501653793898</v>
       </c>
       <c r="O9" t="n">
         <v>5.153771767761627</v>
@@ -1804,7 +1804,7 @@
         <v>-0.03492416578028479</v>
       </c>
       <c r="D4" t="n">
-        <v>2.62380666634436</v>
+        <v>2.623806666344359</v>
       </c>
       <c r="E4" t="n">
         <v>-0.1342493417642536</v>
@@ -1922,7 +1922,7 @@
         <v>0.5643833248417544</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3301487230214006</v>
+        <v>0.5643833248417565</v>
       </c>
       <c r="O5" t="n">
         <v>0.5643833248417565</v>
@@ -2010,7 +2010,7 @@
         <v>0.6382803738325401</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3301487230214006</v>
+        <v>0.6403283769428707</v>
       </c>
       <c r="O6" t="n">
         <v>0.928224206244331</v>
@@ -2098,7 +2098,7 @@
         <v>1.008751426796727</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3301487230214006</v>
+        <v>1.008751426796727</v>
       </c>
       <c r="O7" t="n">
         <v>1.006856815514766</v>
@@ -2186,7 +2186,7 @@
         <v>1.540769892326772</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3301487230214006</v>
+        <v>1.206777482578628</v>
       </c>
       <c r="O8" t="n">
         <v>1.298561496776262</v>
@@ -2274,7 +2274,7 @@
         <v>2.189907461634078</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3301487230214006</v>
+        <v>2.189907461634078</v>
       </c>
       <c r="O9" t="n">
         <v>2.316131173292358</v>
@@ -2958,7 +2958,7 @@
         <v>0.7472213667773767</v>
       </c>
       <c r="N5" t="n">
-        <v>37.13632369250293</v>
+        <v>0.7472213667773753</v>
       </c>
       <c r="O5" t="n">
         <v>0.7472213667773753</v>
@@ -3046,7 +3046,7 @@
         <v>1.449488426692342</v>
       </c>
       <c r="N6" t="n">
-        <v>37.13632369250293</v>
+        <v>0.8963734149367729</v>
       </c>
       <c r="O6" t="n">
         <v>0.8970732650558478</v>
@@ -3134,7 +3134,7 @@
         <v>1.424293611574331</v>
       </c>
       <c r="N7" t="n">
-        <v>37.13632369250293</v>
+        <v>1.424293611574331</v>
       </c>
       <c r="O7" t="n">
         <v>1.422253776428277</v>
@@ -3222,7 +3222,7 @@
         <v>2.499195135387222</v>
       </c>
       <c r="N8" t="n">
-        <v>37.13632369250293</v>
+        <v>1.900770543811096</v>
       </c>
       <c r="O8" t="n">
         <v>2.065222817350493</v>
@@ -3310,7 +3310,7 @@
         <v>4.010791572654466</v>
       </c>
       <c r="N9" t="n">
-        <v>37.13632369250293</v>
+        <v>4.010791572654466</v>
       </c>
       <c r="O9" t="n">
         <v>4.261972037293019</v>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.622717660730844</v>
+        <v>6.622717660730848</v>
       </c>
       <c r="C2" t="n">
-        <v>6.580167203223123</v>
+        <v>6.580167203223128</v>
       </c>
       <c r="D2" t="n">
         <v>6.677143988231959</v>
@@ -3706,73 +3706,73 @@
         <v>4.410016639446291</v>
       </c>
       <c r="F2" t="n">
-        <v>6.58535763126684</v>
+        <v>6.585357631266841</v>
       </c>
       <c r="G2" t="n">
-        <v>6.747056976335273</v>
+        <v>6.747056976335277</v>
       </c>
       <c r="H2" t="n">
-        <v>6.651874090149456</v>
+        <v>6.65187409014946</v>
       </c>
       <c r="I2" t="n">
-        <v>6.605645415588801</v>
+        <v>6.605645415588803</v>
       </c>
       <c r="J2" t="n">
-        <v>6.67664965142043</v>
+        <v>6.676649651420435</v>
       </c>
       <c r="K2" t="n">
-        <v>6.62813051822854</v>
+        <v>6.628130518228544</v>
       </c>
       <c r="L2" t="n">
-        <v>6.6871846294656</v>
+        <v>6.687184629465602</v>
       </c>
       <c r="M2" t="n">
-        <v>6.723836465681245</v>
+        <v>6.723836465681249</v>
       </c>
       <c r="N2" t="n">
         <v>6.63041220021008</v>
       </c>
       <c r="O2" t="n">
-        <v>6.627243656643967</v>
+        <v>6.627243656643971</v>
       </c>
       <c r="P2" t="n">
-        <v>6.66665945301848</v>
+        <v>6.666659453018482</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.577889324659487</v>
+        <v>6.577889324659488</v>
       </c>
       <c r="R2" t="n">
-        <v>6.63120849968781</v>
+        <v>6.631208499687814</v>
       </c>
       <c r="S2" t="n">
-        <v>6.679730971529518</v>
+        <v>6.679730971529521</v>
       </c>
       <c r="T2" t="n">
-        <v>6.621962864927398</v>
+        <v>6.621962864927403</v>
       </c>
       <c r="U2" t="n">
-        <v>6.666334037351232</v>
+        <v>6.666334037351236</v>
       </c>
       <c r="V2" t="n">
-        <v>6.797273137838623</v>
+        <v>6.797273137838624</v>
       </c>
       <c r="W2" t="n">
-        <v>6.714463385430405</v>
+        <v>6.714463385430408</v>
       </c>
       <c r="X2" t="n">
-        <v>6.7048148455468</v>
+        <v>6.704814845546805</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.679575265854659</v>
+        <v>6.679575265854663</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.629527546314649</v>
+        <v>6.629527546314653</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.659888896911821</v>
+        <v>6.659888896911824</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.738351788372094</v>
+        <v>6.738351788372096</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>12.90099859071352</v>
       </c>
       <c r="E3" t="n">
-        <v>10.69695584227267</v>
+        <v>10.69695584227268</v>
       </c>
       <c r="F3" t="n">
         <v>12.90048541185741</v>
@@ -3821,7 +3821,7 @@
         <v>12.90099859071352</v>
       </c>
       <c r="O3" t="n">
-        <v>12.90021477566956</v>
+        <v>12.90021477566957</v>
       </c>
       <c r="P3" t="n">
         <v>12.90090995824454</v>
@@ -3830,7 +3830,7 @@
         <v>12.90098863056365</v>
       </c>
       <c r="R3" t="n">
-        <v>12.90213477783688</v>
+        <v>12.90213477783689</v>
       </c>
       <c r="S3" t="n">
         <v>12.90099859071352</v>
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.77222561343722</v>
+        <v>22.77222561343727</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45509280048092</v>
+        <v>13.45509280048091</v>
       </c>
       <c r="D4" t="n">
         <v>39.40803692377364</v>
       </c>
       <c r="E4" t="n">
-        <v>13.28178555024654</v>
+        <v>13.28178555024651</v>
       </c>
       <c r="F4" t="n">
-        <v>15.35163066955329</v>
+        <v>15.3516306695533</v>
       </c>
       <c r="G4" t="n">
-        <v>51.86877461192937</v>
+        <v>51.86877461192942</v>
       </c>
       <c r="H4" t="n">
-        <v>34.44810388411968</v>
+        <v>34.44810388411967</v>
       </c>
       <c r="I4" t="n">
-        <v>20.96643664172596</v>
+        <v>20.96643664172591</v>
       </c>
       <c r="J4" t="n">
-        <v>37.65994046255283</v>
+        <v>37.65994046255281</v>
       </c>
       <c r="K4" t="n">
-        <v>23.85944707944967</v>
+        <v>23.85944707944966</v>
       </c>
       <c r="L4" t="n">
-        <v>40.1162842072569</v>
+        <v>40.11628420725661</v>
       </c>
       <c r="M4" t="n">
-        <v>52.65057810354229</v>
+        <v>52.65057810354222</v>
       </c>
       <c r="N4" t="n">
-        <v>26.7017155632253</v>
+        <v>26.70171556322528</v>
       </c>
       <c r="O4" t="n">
-        <v>22.80747540650299</v>
+        <v>22.80747540650306</v>
       </c>
       <c r="P4" t="n">
-        <v>32.98449130381712</v>
+        <v>32.9844913038171</v>
       </c>
       <c r="Q4" t="n">
         <v>12.89228997225859</v>
       </c>
       <c r="R4" t="n">
-        <v>27.95559062047973</v>
+        <v>27.95559062047971</v>
       </c>
       <c r="S4" t="n">
-        <v>36.29575691777308</v>
+        <v>36.29575691777303</v>
       </c>
       <c r="T4" t="n">
-        <v>25.38700083008389</v>
+        <v>25.38700083008393</v>
       </c>
       <c r="U4" t="n">
-        <v>33.67784339022121</v>
+        <v>33.67784339022148</v>
       </c>
       <c r="V4" t="n">
-        <v>16.9676865014092</v>
+        <v>16.96768650140927</v>
       </c>
       <c r="W4" t="n">
-        <v>47.55723665337874</v>
+        <v>47.55723665337872</v>
       </c>
       <c r="X4" t="n">
-        <v>44.41876534389004</v>
+        <v>44.41876534389017</v>
       </c>
       <c r="Y4" t="n">
-        <v>38.78437380031696</v>
+        <v>38.78437380031702</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.1705493069677</v>
+        <v>23.17054930696766</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.72310121845565</v>
+        <v>33.72310121845564</v>
       </c>
       <c r="AB4" t="n">
-        <v>56.29104069142126</v>
+        <v>56.29104069142124</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7161028160130062</v>
+        <v>0.7161028160130041</v>
       </c>
       <c r="C5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7161028160130045</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7138032031309216</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7161028160130072</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.7161028160130066</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.7161028160130056</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7138032031309191</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7161028160130066</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7161028160130067</v>
-      </c>
       <c r="M5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="N5" t="n">
-        <v>26.7017155632253</v>
+        <v>0.7161028160130045</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7161028160130056</v>
+        <v>0.7161028160130045</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7161028160130056</v>
+        <v>0.7161028160130045</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7161028160130056</v>
+        <v>0.7161028160130045</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6921138192023621</v>
+        <v>0.6921138192023637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7010397262083365</v>
+        <v>0.7010397262083367</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7161028160130056</v>
+        <v>0.7161028160130045</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7161028160130062</v>
+        <v>0.7161028160130041</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6921138192023621</v>
+        <v>0.6921138192023637</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160130072</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7161028160130056</v>
+        <v>0.7161028160130045</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="D6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="E6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="J6" t="n">
-        <v>1.350474217820709</v>
+        <v>1.350474217820714</v>
       </c>
       <c r="K6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="L6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="N6" t="n">
-        <v>26.7017155632253</v>
+        <v>0.8617131476329383</v>
       </c>
       <c r="O6" t="n">
-        <v>1.378776491625379</v>
+        <v>1.378776491625371</v>
       </c>
       <c r="P6" t="n">
-        <v>1.378542312366355</v>
+        <v>1.378542312366353</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="S6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="V6" t="n">
         <v>1.337710740898131</v>
       </c>
       <c r="W6" t="n">
-        <v>1.378860021699625</v>
+        <v>1.378860021699622</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8580130905915354</v>
+        <v>0.8580130905915366</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8738086022515719</v>
+        <v>0.8738086022516096</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.352773830702795</v>
+        <v>1.352773830702804</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8708321132637145</v>
+        <v>0.8708321132637156</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305348</v>
       </c>
       <c r="C7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="D7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="E7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="F7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="G7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="H7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="I7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="J7" t="n">
-        <v>1.315225714423259</v>
+        <v>1.315225714423261</v>
       </c>
       <c r="K7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="L7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305348</v>
       </c>
       <c r="M7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="N7" t="n">
-        <v>26.7017155632253</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="O7" t="n">
-        <v>1.315626239373899</v>
+        <v>1.315626239373903</v>
       </c>
       <c r="P7" t="n">
-        <v>1.315626239373899</v>
+        <v>1.315626239373903</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="R7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="S7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="T7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="U7" t="n">
-        <v>1.314995085530786</v>
+        <v>1.314995085530784</v>
       </c>
       <c r="V7" t="n">
         <v>1.302462237500676</v>
       </c>
       <c r="W7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="X7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305348</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.317525327305346</v>
+        <v>1.317525327305349</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.575260874428943</v>
+        <v>1.57526087442894</v>
       </c>
       <c r="C8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="D8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="E8" t="n">
-        <v>1.890859609713221</v>
+        <v>1.890859609713223</v>
       </c>
       <c r="F8" t="n">
-        <v>1.680423424897122</v>
+        <v>1.680423424897123</v>
       </c>
       <c r="G8" t="n">
-        <v>2.390268676894457</v>
+        <v>2.390268676894459</v>
       </c>
       <c r="H8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="I8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="J8" t="n">
-        <v>2.247996176898271</v>
+        <v>2.247996176898272</v>
       </c>
       <c r="K8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="L8" t="n">
-        <v>2.250295789780355</v>
+        <v>2.250295789780366</v>
       </c>
       <c r="M8" t="n">
-        <v>2.250295789781437</v>
+        <v>2.250295789781446</v>
       </c>
       <c r="N8" t="n">
-        <v>26.7017155632253</v>
+        <v>1.727030799405245</v>
       </c>
       <c r="O8" t="n">
-        <v>1.870828562003741</v>
+        <v>1.87082856200375</v>
       </c>
       <c r="P8" t="n">
-        <v>1.835580255769399</v>
+        <v>1.835580255769401</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.442601106740384</v>
+        <v>1.442601106740383</v>
       </c>
       <c r="R8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="S8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="T8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="U8" t="n">
-        <v>1.920331128231838</v>
+        <v>1.920331128231836</v>
       </c>
       <c r="V8" t="n">
         <v>2.05019598441771</v>
       </c>
       <c r="W8" t="n">
-        <v>2.250428453113416</v>
+        <v>2.25042845311342</v>
       </c>
       <c r="X8" t="n">
-        <v>1.504469397820636</v>
+        <v>1.50446939782064</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.920630884272413</v>
+        <v>2.920630884272419</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.562721754343774</v>
+        <v>1.562721754343773</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.250295789780354</v>
+        <v>2.250295789780365</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.955426204025417</v>
+        <v>2.955426204025425</v>
       </c>
     </row>
     <row r="9">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.832795068223235</v>
+        <v>2.832795068223236</v>
       </c>
       <c r="C9" t="n">
         <v>3.474383645964847</v>
@@ -4319,10 +4319,10 @@
         <v>3.474383645964847</v>
       </c>
       <c r="E9" t="n">
-        <v>3.326307800637896</v>
+        <v>3.326307800637895</v>
       </c>
       <c r="F9" t="n">
-        <v>1.995346560273916</v>
+        <v>1.995346560273917</v>
       </c>
       <c r="G9" t="n">
         <v>3.474383881823786</v>
@@ -4334,7 +4334,7 @@
         <v>3.474383645964847</v>
       </c>
       <c r="J9" t="n">
-        <v>3.47208403308276</v>
+        <v>3.472084033082758</v>
       </c>
       <c r="K9" t="n">
         <v>3.474383645964847</v>
@@ -4346,13 +4346,13 @@
         <v>3.474383645964847</v>
       </c>
       <c r="N9" t="n">
-        <v>26.7017155632253</v>
+        <v>3.474383645964847</v>
       </c>
       <c r="O9" t="n">
-        <v>3.687005574562206</v>
+        <v>3.687005574562202</v>
       </c>
       <c r="P9" t="n">
-        <v>3.733247144758899</v>
+        <v>3.733247144758896</v>
       </c>
       <c r="Q9" t="n">
         <v>3.474383881823786</v>
@@ -4370,7 +4370,7 @@
         <v>3.474383645964847</v>
       </c>
       <c r="V9" t="n">
-        <v>4.199699485978994</v>
+        <v>4.199699485978992</v>
       </c>
       <c r="W9" t="n">
         <v>3.474383645964847</v>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.34815136677467</v>
+        <v>12.34815136677466</v>
       </c>
       <c r="C10" t="n">
         <v>12.59906673460962</v>
       </c>
       <c r="D10" t="n">
-        <v>12.03787519358929</v>
+        <v>12.0378751935893</v>
       </c>
       <c r="E10" t="n">
         <v>10.40220730351259</v>
@@ -4434,19 +4434,19 @@
         <v>11.76437623323751</v>
       </c>
       <c r="N10" t="n">
-        <v>12.30911143500694</v>
+        <v>12.30911143500695</v>
       </c>
       <c r="O10" t="n">
         <v>12.31554358827759</v>
       </c>
       <c r="P10" t="n">
-        <v>12.0845502971186</v>
+        <v>12.08455029711861</v>
       </c>
       <c r="Q10" t="n">
         <v>12.61847674019546</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3164814626442</v>
+        <v>12.31648146264421</v>
       </c>
       <c r="S10" t="n">
         <v>12.01172571714485</v>
@@ -4467,7 +4467,7 @@
         <v>11.91825976971146</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.00603202200461</v>
+        <v>12.0060320220046</v>
       </c>
       <c r="Z10" t="n">
         <v>12.30770828192569</v>
@@ -4486,82 +4486,82 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.371170412019094</v>
+        <v>6.371170412019096</v>
       </c>
       <c r="C11" t="n">
-        <v>6.443253057386964</v>
+        <v>6.443253057386966</v>
       </c>
       <c r="D11" t="n">
-        <v>6.284420091929366</v>
+        <v>6.284420091929372</v>
       </c>
       <c r="E11" t="n">
         <v>4.27590511500259</v>
       </c>
       <c r="F11" t="n">
-        <v>6.436742940260019</v>
+        <v>6.436742940260028</v>
       </c>
       <c r="G11" t="n">
-        <v>6.158744490935909</v>
+        <v>6.158744490935913</v>
       </c>
       <c r="H11" t="n">
-        <v>6.328696031762082</v>
+        <v>6.328696031762084</v>
       </c>
       <c r="I11" t="n">
-        <v>6.403858273608154</v>
+        <v>6.403858273608158</v>
       </c>
       <c r="J11" t="n">
-        <v>6.268981929986492</v>
+        <v>6.268981929986493</v>
       </c>
       <c r="K11" t="n">
-        <v>6.364925228395954</v>
+        <v>6.364925228395957</v>
       </c>
       <c r="L11" t="n">
-        <v>6.263808065159934</v>
+        <v>6.263808065159937</v>
       </c>
       <c r="M11" t="n">
-        <v>6.206979541062571</v>
+        <v>6.206979541062576</v>
       </c>
       <c r="N11" t="n">
-        <v>6.361101658131141</v>
+        <v>6.361101658131145</v>
       </c>
       <c r="O11" t="n">
-        <v>6.361216403144097</v>
+        <v>6.361216403144102</v>
       </c>
       <c r="P11" t="n">
-        <v>6.295213205622294</v>
+        <v>6.295213205622297</v>
       </c>
       <c r="Q11" t="n">
         <v>6.44934551422998</v>
       </c>
       <c r="R11" t="n">
-        <v>6.364734374908764</v>
+        <v>6.364734374908767</v>
       </c>
       <c r="S11" t="n">
-        <v>6.275108980111274</v>
+        <v>6.275108980111275</v>
       </c>
       <c r="T11" t="n">
-        <v>6.374275134293564</v>
+        <v>6.374275134293566</v>
       </c>
       <c r="U11" t="n">
-        <v>6.301328448954946</v>
+        <v>6.301328448954947</v>
       </c>
       <c r="V11" t="n">
-        <v>6.602485965388852</v>
+        <v>6.602485965388854</v>
       </c>
       <c r="W11" t="n">
-        <v>6.218538933656501</v>
+        <v>6.218538933656505</v>
       </c>
       <c r="X11" t="n">
-        <v>6.254555720458277</v>
+        <v>6.25455572045828</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.273244026713234</v>
+        <v>6.273244026713241</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.359620174792995</v>
+        <v>6.359620174792999</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.310803993346402</v>
+        <v>6.310803993346408</v>
       </c>
       <c r="AB11" t="n">
         <v>6.207902540382435</v>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5963264565979</v>
+        <v>6.596326456597893</v>
       </c>
       <c r="C2" t="n">
-        <v>6.571732165983308</v>
+        <v>6.571732165983317</v>
       </c>
       <c r="D2" t="n">
-        <v>6.618850860565925</v>
+        <v>6.618850860565926</v>
       </c>
       <c r="E2" t="n">
-        <v>4.378626444160855</v>
+        <v>4.378626444160853</v>
       </c>
       <c r="F2" t="n">
-        <v>6.577490958908339</v>
+        <v>6.577490958908343</v>
       </c>
       <c r="G2" t="n">
-        <v>6.700368830114634</v>
+        <v>6.700368830114636</v>
       </c>
       <c r="H2" t="n">
-        <v>6.623399730500364</v>
+        <v>6.623399730500369</v>
       </c>
       <c r="I2" t="n">
-        <v>6.588087460551088</v>
+        <v>6.58808746055109</v>
       </c>
       <c r="J2" t="n">
-        <v>6.648536294777308</v>
+        <v>6.648536294777313</v>
       </c>
       <c r="K2" t="n">
-        <v>6.627818768255552</v>
+        <v>6.627818768255553</v>
       </c>
       <c r="L2" t="n">
-        <v>6.647920723599571</v>
+        <v>6.64792072359957</v>
       </c>
       <c r="M2" t="n">
-        <v>6.678996935342046</v>
+        <v>6.678996935342052</v>
       </c>
       <c r="N2" t="n">
-        <v>6.601834879676969</v>
+        <v>6.601834879676971</v>
       </c>
       <c r="O2" t="n">
-        <v>6.590849551634865</v>
+        <v>6.590849551634873</v>
       </c>
       <c r="P2" t="n">
-        <v>6.641518048645198</v>
+        <v>6.641518048645201</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.575137932545289</v>
+        <v>6.575137932545292</v>
       </c>
       <c r="R2" t="n">
         <v>6.605356953597822</v>
       </c>
       <c r="S2" t="n">
-        <v>6.648763929751385</v>
+        <v>6.648763929751389</v>
       </c>
       <c r="T2" t="n">
-        <v>6.599272325496339</v>
+        <v>6.599272325496346</v>
       </c>
       <c r="U2" t="n">
-        <v>6.661274986456734</v>
+        <v>6.661274986456735</v>
       </c>
       <c r="V2" t="n">
         <v>6.847969271445885</v>
       </c>
       <c r="W2" t="n">
-        <v>6.701131836128306</v>
+        <v>6.701131836128301</v>
       </c>
       <c r="X2" t="n">
-        <v>6.692170172303851</v>
+        <v>6.692170172303856</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.71869528600503</v>
+        <v>6.718695286005032</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.60166545191605</v>
+        <v>6.601665451916053</v>
       </c>
       <c r="AA2" t="n">
         <v>6.648622516475537</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.70311696732301</v>
+        <v>6.703116967323012</v>
       </c>
     </row>
     <row r="3">
@@ -4875,7 +4875,7 @@
         <v>12.88339787805254</v>
       </c>
       <c r="U3" t="n">
-        <v>12.88775330583179</v>
+        <v>12.8877533058318</v>
       </c>
       <c r="V3" t="n">
         <v>13.1125487520498</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.72662841990043</v>
+        <v>19.72662841990049</v>
       </c>
       <c r="C4" t="n">
-        <v>15.23686007335154</v>
+        <v>15.23686007335153</v>
       </c>
       <c r="D4" t="n">
-        <v>27.21128155911682</v>
+        <v>27.2112815591168</v>
       </c>
       <c r="E4" t="n">
-        <v>9.201152240249494</v>
+        <v>9.201152240249492</v>
       </c>
       <c r="F4" t="n">
-        <v>17.40559476767046</v>
+        <v>17.40559476767038</v>
       </c>
       <c r="G4" t="n">
-        <v>43.18461036888817</v>
+        <v>43.18461036888811</v>
       </c>
       <c r="H4" t="n">
-        <v>31.15207111040305</v>
+        <v>31.15207111040304</v>
       </c>
       <c r="I4" t="n">
         <v>20.24912050044285</v>
       </c>
       <c r="J4" t="n">
-        <v>33.34869657613153</v>
+        <v>33.34869657613146</v>
       </c>
       <c r="K4" t="n">
-        <v>27.57746066473506</v>
+        <v>27.5774606647351</v>
       </c>
       <c r="L4" t="n">
-        <v>33.00787558207427</v>
+        <v>33.00787558207428</v>
       </c>
       <c r="M4" t="n">
-        <v>43.35924293516675</v>
+        <v>43.35924293516669</v>
       </c>
       <c r="N4" t="n">
-        <v>23.56899416128043</v>
+        <v>23.5689941612804</v>
       </c>
       <c r="O4" t="n">
-        <v>18.33970424845434</v>
+        <v>18.33970424845429</v>
       </c>
       <c r="P4" t="n">
-        <v>30.14495388793946</v>
+        <v>30.14495388793936</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.88814912587793</v>
+        <v>15.88814912587789</v>
       </c>
       <c r="R4" t="n">
         <v>25.06817879857045</v>
       </c>
       <c r="S4" t="n">
-        <v>32.33741152993396</v>
+        <v>32.33741152993395</v>
       </c>
       <c r="T4" t="n">
-        <v>23.78254166855601</v>
+        <v>23.78254166855605</v>
       </c>
       <c r="U4" t="n">
-        <v>34.65598936104849</v>
+        <v>34.65598936104851</v>
       </c>
       <c r="V4" t="n">
-        <v>25.2099835092711</v>
+        <v>25.20998350927103</v>
       </c>
       <c r="W4" t="n">
-        <v>48.36495585355676</v>
+        <v>48.36495585355667</v>
       </c>
       <c r="X4" t="n">
-        <v>44.75338634475148</v>
+        <v>44.75338634475133</v>
       </c>
       <c r="Y4" t="n">
-        <v>54.09122663083383</v>
+        <v>54.09122663083387</v>
       </c>
       <c r="Z4" t="n">
         <v>19.47237731209158</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.17137038044017</v>
+        <v>35.17137038044014</v>
       </c>
       <c r="AB4" t="n">
-        <v>50.22293132902752</v>
+        <v>50.22293132902743</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7258754116112299</v>
+        <v>0.7258754116112097</v>
       </c>
       <c r="C5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="D5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="E5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="F5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="G5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="H5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="I5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7241204449673484</v>
+        <v>0.7241204449673467</v>
       </c>
       <c r="K5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7258754116112295</v>
+        <v>0.7258754116112128</v>
       </c>
       <c r="M5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="N5" t="n">
-        <v>23.56899416128043</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="O5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="P5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="R5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="S5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="T5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7052122534911769</v>
+        <v>0.7052122534911551</v>
       </c>
       <c r="V5" t="n">
-        <v>0.714295674660406</v>
+        <v>0.714295674660405</v>
       </c>
       <c r="W5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7258754116112301</v>
+        <v>0.7258754116112318</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7052122534911769</v>
+        <v>0.7052122534911551</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.72587541161123</v>
+        <v>0.7258754116112147</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.725875411611231</v>
+        <v>0.7258754116112306</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="D6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="E6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="H6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="J6" t="n">
-        <v>1.345473227355676</v>
+        <v>1.345473227355674</v>
       </c>
       <c r="K6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="N6" t="n">
-        <v>23.56899416128043</v>
+        <v>0.8924657923995228</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8931048940012543</v>
+        <v>0.8931048940012511</v>
       </c>
       <c r="P6" t="n">
-        <v>1.375021814776566</v>
+        <v>1.375021814776545</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="R6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="T6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="U6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8742049815991145</v>
+        <v>0.8742049815991161</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9165771028192446</v>
+        <v>0.9165771028192403</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9071176514664413</v>
+        <v>0.9071176514663949</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8857847185499449</v>
+        <v>0.885784718549932</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.347228193999558</v>
+        <v>1.347228193999557</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8983698622506548</v>
+        <v>0.8983698622506395</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.310641902997842</v>
+        <v>1.310641902997822</v>
       </c>
       <c r="C7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="D7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="E7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="F7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="G7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="H7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="I7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="J7" t="n">
-        <v>1.308886936353961</v>
+        <v>1.308886936353958</v>
       </c>
       <c r="K7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="L7" t="n">
-        <v>1.310641902997841</v>
+        <v>1.310641902997822</v>
       </c>
       <c r="M7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="N7" t="n">
-        <v>23.56899416128043</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="O7" t="n">
-        <v>1.308743652850281</v>
+        <v>1.308743652850266</v>
       </c>
       <c r="P7" t="n">
-        <v>1.308743652850281</v>
+        <v>1.308743652850266</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="R7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="S7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="T7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="U7" t="n">
-        <v>1.30648065776902</v>
+        <v>1.306480657769011</v>
       </c>
       <c r="V7" t="n">
-        <v>1.299062166047019</v>
+        <v>1.299062166047014</v>
       </c>
       <c r="W7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="X7" t="n">
-        <v>1.310641902997841</v>
+        <v>1.310641902997822</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.310641902997843</v>
+        <v>1.310641902997824</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.546754056371732</v>
+        <v>1.546754056371717</v>
       </c>
       <c r="C8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="D8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="E8" t="n">
-        <v>1.847731420139699</v>
+        <v>1.847731420139683</v>
       </c>
       <c r="F8" t="n">
-        <v>1.647044531810973</v>
+        <v>1.647044531810972</v>
       </c>
       <c r="G8" t="n">
-        <v>2.324003368301736</v>
+        <v>2.324003368301728</v>
       </c>
       <c r="H8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="I8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="J8" t="n">
-        <v>2.188760317406959</v>
+        <v>2.188760317406955</v>
       </c>
       <c r="K8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="L8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050822</v>
       </c>
       <c r="M8" t="n">
-        <v>2.190515284052015</v>
+        <v>2.190515284051995</v>
       </c>
       <c r="N8" t="n">
-        <v>23.56899416128043</v>
+        <v>1.69149263361222</v>
       </c>
       <c r="O8" t="n">
-        <v>1.828628390737071</v>
+        <v>1.828628390737055</v>
       </c>
       <c r="P8" t="n">
-        <v>1.795013103017074</v>
+        <v>1.795013103017054</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.420240282079343</v>
+        <v>1.420240282079336</v>
       </c>
       <c r="R8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="S8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="T8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="U8" t="n">
-        <v>1.874550255187422</v>
+        <v>1.87455025518742</v>
       </c>
       <c r="V8" t="n">
-        <v>2.001051544480339</v>
+        <v>2.001051544480336</v>
       </c>
       <c r="W8" t="n">
-        <v>2.190641801273097</v>
+        <v>2.190641801273071</v>
       </c>
       <c r="X8" t="n">
-        <v>1.47924227758278</v>
+        <v>1.479242277582759</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.827592236949093</v>
+        <v>2.827592236949084</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.534795861084601</v>
+        <v>1.534795861084588</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.190515284050845</v>
+        <v>2.190515284050821</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.862977716521183</v>
+        <v>2.862977716521174</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.651038226097276</v>
+        <v>2.651038226097248</v>
       </c>
       <c r="C9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="D9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="E9" t="n">
-        <v>3.101480102267715</v>
+        <v>3.101480102267701</v>
       </c>
       <c r="F9" t="n">
-        <v>1.886677243410671</v>
+        <v>1.886677243410664</v>
       </c>
       <c r="G9" t="n">
-        <v>3.236632983732371</v>
+        <v>3.236632983732372</v>
       </c>
       <c r="H9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="I9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="J9" t="n">
-        <v>3.234877862738869</v>
+        <v>3.234877862738856</v>
       </c>
       <c r="K9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="L9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382734</v>
       </c>
       <c r="M9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="N9" t="n">
-        <v>23.56899416128043</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="O9" t="n">
-        <v>3.430698319641796</v>
+        <v>3.430698319641785</v>
       </c>
       <c r="P9" t="n">
-        <v>3.472904200601652</v>
+        <v>3.472904200601644</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.236632983732371</v>
+        <v>3.236632983732372</v>
       </c>
       <c r="R9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="S9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="T9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="U9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="V9" t="n">
-        <v>3.900816282132658</v>
+        <v>3.900816282132646</v>
       </c>
       <c r="W9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="X9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382734</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88357141799602</v>
+        <v>2.883571417996015</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.236632829382747</v>
+        <v>3.236632829382735</v>
       </c>
     </row>
     <row r="10">
@@ -5440,13 +5440,13 @@
         <v>12.53767793025691</v>
       </c>
       <c r="D10" t="n">
-        <v>12.26855849735829</v>
+        <v>12.2685584973583</v>
       </c>
       <c r="E10" t="n">
         <v>10.47034345598425</v>
       </c>
       <c r="F10" t="n">
-        <v>12.50834424733421</v>
+        <v>12.5083442473342</v>
       </c>
       <c r="G10" t="n">
         <v>11.77247133759648</v>
@@ -5464,7 +5464,7 @@
         <v>12.21260639350296</v>
       </c>
       <c r="L10" t="n">
-        <v>12.0909828429247</v>
+        <v>12.09098284292469</v>
       </c>
       <c r="M10" t="n">
         <v>11.9087511222989</v>
@@ -5485,10 +5485,10 @@
         <v>12.36358639487692</v>
       </c>
       <c r="S10" t="n">
-        <v>12.08343318119306</v>
+        <v>12.08343318119305</v>
       </c>
       <c r="T10" t="n">
-        <v>12.37536040424918</v>
+        <v>12.37536040424917</v>
       </c>
       <c r="U10" t="n">
         <v>12.03079701041895</v>
@@ -5497,10 +5497,10 @@
         <v>12.45855594753256</v>
       </c>
       <c r="W10" t="n">
-        <v>11.77825768591467</v>
+        <v>11.77825768591466</v>
       </c>
       <c r="X10" t="n">
-        <v>11.85800330539441</v>
+        <v>11.8580033053944</v>
       </c>
       <c r="Y10" t="n">
         <v>11.65485426750065</v>
@@ -5509,10 +5509,10 @@
         <v>12.36114859077075</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.08881443286369</v>
+        <v>12.08881443286368</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.84115863708428</v>
+        <v>11.84115863708427</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.372564915236243</v>
+        <v>6.372564915236239</v>
       </c>
       <c r="C11" t="n">
         <v>6.414304937213775</v>
       </c>
       <c r="D11" t="n">
-        <v>6.338509443194354</v>
+        <v>6.338509443194346</v>
       </c>
       <c r="E11" t="n">
-        <v>4.283324871404242</v>
+        <v>4.283324871404241</v>
       </c>
       <c r="F11" t="n">
         <v>6.406562736693088</v>
       </c>
       <c r="G11" t="n">
-        <v>6.19445395085523</v>
+        <v>6.194453950855237</v>
       </c>
       <c r="H11" t="n">
-        <v>6.332909341960351</v>
+        <v>6.332909341960355</v>
       </c>
       <c r="I11" t="n">
-        <v>6.390108447567171</v>
+        <v>6.390108447567173</v>
       </c>
       <c r="J11" t="n">
-        <v>6.280459344825414</v>
+        <v>6.280459344825416</v>
       </c>
       <c r="K11" t="n">
-        <v>6.322195899169558</v>
+        <v>6.322195899169556</v>
       </c>
       <c r="L11" t="n">
-        <v>6.286781817560682</v>
+        <v>6.286781817560681</v>
       </c>
       <c r="M11" t="n">
-        <v>6.235745171780616</v>
+        <v>6.235745171780618</v>
       </c>
       <c r="N11" t="n">
-        <v>6.365848793211411</v>
+        <v>6.365848793211412</v>
       </c>
       <c r="O11" t="n">
-        <v>6.379465054534459</v>
+        <v>6.379465054534468</v>
       </c>
       <c r="P11" t="n">
-        <v>6.290558870126866</v>
+        <v>6.290558870126865</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.410855881138969</v>
+        <v>6.410855881138974</v>
       </c>
       <c r="R11" t="n">
         <v>6.367256980493042</v>
       </c>
       <c r="S11" t="n">
-        <v>6.284189903565258</v>
+        <v>6.284189903565263</v>
       </c>
       <c r="T11" t="n">
-        <v>6.368113655896439</v>
+        <v>6.36811365589644</v>
       </c>
       <c r="U11" t="n">
         <v>6.271357141086209</v>
       </c>
       <c r="V11" t="n">
-        <v>6.550400461239134</v>
+        <v>6.550400461239136</v>
       </c>
       <c r="W11" t="n">
-        <v>6.197701987053905</v>
+        <v>6.197701987053902</v>
       </c>
       <c r="X11" t="n">
-        <v>6.223599133685038</v>
+        <v>6.223599133685035</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.160662915593676</v>
+        <v>6.160662915593672</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.363493763535221</v>
+        <v>6.363493763535215</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.286496976948583</v>
+        <v>6.286496976948579</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.223583664309805</v>
+        <v>6.223583664309799</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.5930537450806793</v>
       </c>
       <c r="N5" t="n">
-        <v>8.826612841522879</v>
+        <v>0.5930537450806728</v>
       </c>
       <c r="O5" t="n">
         <v>0.5930537450806728</v>
@@ -6154,7 +6154,7 @@
         <v>1.008397277871448</v>
       </c>
       <c r="N6" t="n">
-        <v>8.826612841522879</v>
+        <v>0.68085114656309</v>
       </c>
       <c r="O6" t="n">
         <v>1.041900119091942</v>
@@ -6242,7 +6242,7 @@
         <v>1.105821277833418</v>
       </c>
       <c r="N7" t="n">
-        <v>8.826612841522879</v>
+        <v>1.105821277833418</v>
       </c>
       <c r="O7" t="n">
         <v>1.103789454688766</v>
@@ -6330,7 +6330,7 @@
         <v>1.796449084257497</v>
       </c>
       <c r="N8" t="n">
-        <v>8.826612841522879</v>
+        <v>1.383684655052046</v>
       </c>
       <c r="O8" t="n">
         <v>1.497115904067843</v>
@@ -6418,7 +6418,7 @@
         <v>2.744215437878196</v>
       </c>
       <c r="N9" t="n">
-        <v>8.826612841522879</v>
+        <v>2.744215437878196</v>
       </c>
       <c r="O9" t="n">
         <v>2.910657060132398</v>
@@ -6835,7 +6835,7 @@
         <v>6.237339281611789</v>
       </c>
       <c r="M2" t="n">
-        <v>6.302850725837532</v>
+        <v>6.302850725837533</v>
       </c>
       <c r="N2" t="n">
         <v>6.334606236649558</v>
@@ -6844,10 +6844,10 @@
         <v>6.304506100184568</v>
       </c>
       <c r="P2" t="n">
-        <v>6.268642756132893</v>
+        <v>6.268642756132894</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.30962568292978</v>
+        <v>6.309625682929781</v>
       </c>
       <c r="R2" t="n">
         <v>6.171627221672797</v>
@@ -6859,7 +6859,7 @@
         <v>6.285278695688263</v>
       </c>
       <c r="U2" t="n">
-        <v>6.314961923209828</v>
+        <v>6.314961923209829</v>
       </c>
       <c r="V2" t="n">
         <v>6.529803224771103</v>
@@ -6868,7 +6868,7 @@
         <v>6.400258238494637</v>
       </c>
       <c r="X2" t="n">
-        <v>6.478749660843605</v>
+        <v>6.478749660843604</v>
       </c>
       <c r="Y2" t="n">
         <v>6.355353071739655</v>
@@ -6981,7 +6981,7 @@
         <v>-7.896554697736203</v>
       </c>
       <c r="C4" t="n">
-        <v>3.344880659684905</v>
+        <v>3.344880659684907</v>
       </c>
       <c r="D4" t="n">
         <v>3.859189808433794</v>
@@ -7056,7 +7056,7 @@
         <v>32.66467278415319</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8868079469252815</v>
+        <v>0.8868079469252813</v>
       </c>
     </row>
     <row r="5">
@@ -7090,7 +7090,7 @@
         <v>0.5279827888024152</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5265119885597164</v>
+        <v>0.5265119885597165</v>
       </c>
       <c r="K5" t="n">
         <v>0.5279827888024152</v>
@@ -7102,7 +7102,7 @@
         <v>0.5279827888024152</v>
       </c>
       <c r="N5" t="n">
-        <v>7.935130176629051</v>
+        <v>0.5279827888024234</v>
       </c>
       <c r="O5" t="n">
         <v>0.5279827888024234</v>
@@ -7190,7 +7190,7 @@
         <v>0.820978640241086</v>
       </c>
       <c r="N6" t="n">
-        <v>7.935130176629051</v>
+        <v>0.5708834477880163</v>
       </c>
       <c r="O6" t="n">
         <v>0.8494532192602461</v>
@@ -7278,7 +7278,7 @@
         <v>0.953079741687089</v>
       </c>
       <c r="N7" t="n">
-        <v>7.935130176629051</v>
+        <v>0.953079741687089</v>
       </c>
       <c r="O7" t="n">
         <v>0.9511870666198627</v>
@@ -7366,7 +7366,7 @@
         <v>1.446262624495868</v>
       </c>
       <c r="N8" t="n">
-        <v>7.935130176629051</v>
+        <v>1.1322622788005</v>
       </c>
       <c r="O8" t="n">
         <v>1.218552300256536</v>
@@ -7454,7 +7454,7 @@
         <v>2.181091764649232</v>
       </c>
       <c r="N9" t="n">
-        <v>7.935130176629051</v>
+        <v>2.181091764649232</v>
       </c>
       <c r="O9" t="n">
         <v>2.308701766460362</v>
@@ -8050,7 +8050,7 @@
         <v>2.262430068637599</v>
       </c>
       <c r="N4" t="n">
-        <v>9.389331545583371</v>
+        <v>9.389331545583373</v>
       </c>
       <c r="O4" t="n">
         <v>-5.249260499659616</v>
@@ -8138,7 +8138,7 @@
         <v>0.5091473516192405</v>
       </c>
       <c r="N5" t="n">
-        <v>9.389331545583373</v>
+        <v>0.5091473516192379</v>
       </c>
       <c r="O5" t="n">
         <v>0.5091473516192379</v>
@@ -8226,7 +8226,7 @@
         <v>0.7712313983082526</v>
       </c>
       <c r="N6" t="n">
-        <v>9.389331545583371</v>
+        <v>0.5459311886284801</v>
       </c>
       <c r="O6" t="n">
         <v>0.5465792848956221</v>
@@ -8314,7 +8314,7 @@
         <v>0.9165950567343237</v>
       </c>
       <c r="N7" t="n">
-        <v>9.389331545583371</v>
+        <v>0.9165950567343237</v>
       </c>
       <c r="O7" t="n">
         <v>0.9147033068049761</v>
@@ -8402,7 +8402,7 @@
         <v>1.359050257877954</v>
       </c>
       <c r="N8" t="n">
-        <v>9.389331545583371</v>
+        <v>1.069487320491215</v>
       </c>
       <c r="O8" t="n">
         <v>1.149061730031975</v>
@@ -8490,7 +8490,7 @@
         <v>2.003922936416411</v>
       </c>
       <c r="N9" t="n">
-        <v>9.389331545583371</v>
+        <v>2.003922936416411</v>
       </c>
       <c r="O9" t="n">
         <v>2.119248842823855</v>
@@ -9174,7 +9174,7 @@
         <v>0.7070533720713429</v>
       </c>
       <c r="N5" t="n">
-        <v>25.02471039617396</v>
+        <v>0.7070533720713422</v>
       </c>
       <c r="O5" t="n">
         <v>0.7070533720713422</v>
@@ -9262,7 +9262,7 @@
         <v>0.8289700810652644</v>
       </c>
       <c r="N6" t="n">
-        <v>25.02471039617396</v>
+        <v>0.8334697815989539</v>
       </c>
       <c r="O6" t="n">
         <v>1.374086831003744</v>
@@ -9350,7 +9350,7 @@
         <v>1.330192290472188</v>
       </c>
       <c r="N7" t="n">
-        <v>25.02471039617396</v>
+        <v>1.330192290472188</v>
       </c>
       <c r="O7" t="n">
         <v>1.328154413475839</v>
@@ -9438,7 +9438,7 @@
         <v>2.281589106037755</v>
       </c>
       <c r="N8" t="n">
-        <v>25.02471039617396</v>
+        <v>1.742525661576498</v>
       </c>
       <c r="O8" t="n">
         <v>1.890664976509315</v>
@@ -9526,7 +9526,7 @@
         <v>3.74244805161532</v>
       </c>
       <c r="N9" t="n">
-        <v>25.02471039617396</v>
+        <v>3.74244805161532</v>
       </c>
       <c r="O9" t="n">
         <v>3.975834820163398</v>
@@ -10210,7 +10210,7 @@
         <v>0.6141578754143058</v>
       </c>
       <c r="N5" t="n">
-        <v>3.64348666611799</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="O5" t="n">
         <v>0.6141578754143059</v>
@@ -10298,7 +10298,7 @@
         <v>0.682025714528617</v>
       </c>
       <c r="N6" t="n">
-        <v>3.64348666611799</v>
+        <v>0.6852236840603814</v>
       </c>
       <c r="O6" t="n">
         <v>1.106041514433886</v>
@@ -10386,7 +10386,7 @@
         <v>1.109070054124197</v>
       </c>
       <c r="N7" t="n">
-        <v>3.64348666611799</v>
+        <v>1.109070054124197</v>
       </c>
       <c r="O7" t="n">
         <v>1.107173749370278</v>
@@ -10474,7 +10474,7 @@
         <v>1.788848023305292</v>
       </c>
       <c r="N8" t="n">
-        <v>3.64348666611799</v>
+        <v>1.38525394475865</v>
       </c>
       <c r="O8" t="n">
         <v>1.496165101806745</v>
@@ -10562,7 +10562,7 @@
         <v>2.865620692622612</v>
       </c>
       <c r="N9" t="n">
-        <v>3.64348666611799</v>
+        <v>2.865620692622612</v>
       </c>
       <c r="O9" t="n">
         <v>3.039138586683871</v>

--- a/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
+++ b/Results/GWP 20a/hydrogen climate change GWP 20a results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.732899213069638</v>
+        <v>6.732899213069632</v>
       </c>
       <c r="C2" t="n">
-        <v>6.640826539014186</v>
+        <v>6.640826539014179</v>
       </c>
       <c r="D2" t="n">
-        <v>6.700549001210273</v>
+        <v>6.700549001210267</v>
       </c>
       <c r="E2" t="n">
-        <v>4.434856121367461</v>
+        <v>4.434856121367456</v>
       </c>
       <c r="F2" t="n">
-        <v>6.677341068214601</v>
+        <v>6.677341068214595</v>
       </c>
       <c r="G2" t="n">
-        <v>6.825797480611488</v>
+        <v>6.825797480611484</v>
       </c>
       <c r="H2" t="n">
-        <v>6.752405939373601</v>
+        <v>6.752405939373596</v>
       </c>
       <c r="I2" t="n">
-        <v>6.677070760397854</v>
+        <v>6.677070760397847</v>
       </c>
       <c r="J2" t="n">
-        <v>6.747940058467891</v>
+        <v>6.747940058467887</v>
       </c>
       <c r="K2" t="n">
-        <v>6.7306087499311</v>
+        <v>6.730608749931096</v>
       </c>
       <c r="L2" t="n">
-        <v>6.79030764046196</v>
+        <v>6.790307640461956</v>
       </c>
       <c r="M2" t="n">
-        <v>6.825156861082673</v>
+        <v>6.825156861082665</v>
       </c>
       <c r="N2" t="n">
         <v>6.740975101705941</v>
       </c>
       <c r="O2" t="n">
-        <v>6.732335375007882</v>
+        <v>6.732335375007874</v>
       </c>
       <c r="P2" t="n">
-        <v>6.713185863621995</v>
+        <v>6.713185863621987</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.699104616072797</v>
+        <v>6.699104616072792</v>
       </c>
       <c r="R2" t="n">
-        <v>6.692923322291401</v>
+        <v>6.692923322291395</v>
       </c>
       <c r="S2" t="n">
-        <v>6.759191867781928</v>
+        <v>6.759191867781922</v>
       </c>
       <c r="T2" t="n">
-        <v>6.721734600935057</v>
+        <v>6.721734600935051</v>
       </c>
       <c r="U2" t="n">
-        <v>6.789569121136029</v>
+        <v>6.789569121136021</v>
       </c>
       <c r="V2" t="n">
-        <v>6.859662464456816</v>
+        <v>6.859662464456819</v>
       </c>
       <c r="W2" t="n">
-        <v>6.777037532429607</v>
+        <v>6.777037532429601</v>
       </c>
       <c r="X2" t="n">
-        <v>6.717452739448929</v>
+        <v>6.717452739448923</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.711420000929362</v>
+        <v>6.711420000929356</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.706496297778695</v>
+        <v>6.70649629777869</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.760247243159646</v>
+        <v>6.760247243159641</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.807552498446533</v>
+        <v>6.807552498446528</v>
       </c>
     </row>
     <row r="3">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.74699192178046</v>
+        <v>39.74699192178007</v>
       </c>
       <c r="C4" t="n">
         <v>16.57684703300913</v>
       </c>
       <c r="D4" t="n">
-        <v>34.96526716301928</v>
+        <v>34.96526716301909</v>
       </c>
       <c r="E4" t="n">
-        <v>14.57578379524714</v>
+        <v>14.57578379524712</v>
       </c>
       <c r="F4" t="n">
-        <v>28.47615051989947</v>
+        <v>28.47615051989949</v>
       </c>
       <c r="G4" t="n">
-        <v>66.65693703257524</v>
+        <v>66.65693703257537</v>
       </c>
       <c r="H4" t="n">
-        <v>52.69682006657587</v>
+        <v>52.69682006657595</v>
       </c>
       <c r="I4" t="n">
-        <v>28.11651282705245</v>
+        <v>28.11651282705239</v>
       </c>
       <c r="J4" t="n">
-        <v>47.59665212791205</v>
+        <v>47.59665212791211</v>
       </c>
       <c r="K4" t="n">
-        <v>43.78567157070948</v>
+        <v>43.78567157070945</v>
       </c>
       <c r="L4" t="n">
-        <v>59.13199745555513</v>
+        <v>59.13199745555526</v>
       </c>
       <c r="M4" t="n">
-        <v>73.56797081770125</v>
+        <v>73.56797081770108</v>
       </c>
       <c r="N4" t="n">
-        <v>45.97326141195387</v>
+        <v>45.97326141195391</v>
       </c>
       <c r="O4" t="n">
-        <v>38.6758404150026</v>
+        <v>38.67584041500258</v>
       </c>
       <c r="P4" t="n">
-        <v>35.09719699247102</v>
+        <v>35.09719699247099</v>
       </c>
       <c r="Q4" t="n">
         <v>33.83001624477777</v>
       </c>
       <c r="R4" t="n">
-        <v>33.38801132869056</v>
+        <v>33.38801132869059</v>
       </c>
       <c r="S4" t="n">
-        <v>48.23983447488662</v>
+        <v>48.23983447488675</v>
       </c>
       <c r="T4" t="n">
-        <v>41.56198974982847</v>
+        <v>41.56198974982845</v>
       </c>
       <c r="U4" t="n">
-        <v>57.7746143051404</v>
+        <v>57.77461430514042</v>
       </c>
       <c r="V4" t="n">
-        <v>22.16823138378435</v>
+        <v>22.16823138378437</v>
       </c>
       <c r="W4" t="n">
-        <v>55.70322363172581</v>
+        <v>55.70322363172587</v>
       </c>
       <c r="X4" t="n">
-        <v>39.57919823499586</v>
+        <v>39.57919823499577</v>
       </c>
       <c r="Y4" t="n">
-        <v>36.59730756649894</v>
+        <v>36.5973075664989</v>
       </c>
       <c r="Z4" t="n">
-        <v>33.56715277695966</v>
+        <v>33.56715277695963</v>
       </c>
       <c r="AA4" t="n">
-        <v>51.15536349684987</v>
+        <v>51.15536349685004</v>
       </c>
       <c r="AB4" t="n">
-        <v>70.70290832741748</v>
+        <v>70.70290832741752</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8066698894803811</v>
+        <v>0.806669889480378</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7857743239137011</v>
+        <v>0.7857743239136952</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7933607276942477</v>
+        <v>0.7933607276942481</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632657</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7857743239137011</v>
+        <v>0.7857743239136952</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8090728879632745</v>
+        <v>0.8090728879632787</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8090728879632733</v>
+        <v>0.8090728879632656</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="C6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="D6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="E6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="G6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="H6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9806587166218905</v>
+        <v>0.9806587166218901</v>
       </c>
       <c r="K6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="L6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="M6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9905179081235741</v>
+        <v>0.9905179081235457</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9905172360190946</v>
+        <v>0.9905172360190521</v>
       </c>
       <c r="P6" t="n">
-        <v>1.640386800579965</v>
+        <v>1.64038680057996</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="R6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="V6" t="n">
-        <v>1.592200942952005</v>
+        <v>1.592200942952006</v>
       </c>
       <c r="W6" t="n">
-        <v>1.640385202144282</v>
+        <v>1.640385202144286</v>
       </c>
       <c r="X6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.004595251928655</v>
+        <v>1.004595251928687</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9830617151047845</v>
+        <v>0.9830617151047901</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.607913103221029</v>
+        <v>1.607913103221027</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9994627417893076</v>
+        <v>0.9994627417893128</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="C7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="D7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="E7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="F7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="G7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="H7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="I7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="J7" t="n">
-        <v>1.566086133041404</v>
+        <v>1.566086133041402</v>
       </c>
       <c r="K7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="L7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="M7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="N7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="O7" t="n">
-        <v>1.566307755273997</v>
+        <v>1.566307755273994</v>
       </c>
       <c r="P7" t="n">
-        <v>1.566307755273997</v>
+        <v>1.566307755273994</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="T7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="U7" t="n">
-        <v>1.567294615543899</v>
+        <v>1.567294615543898</v>
       </c>
       <c r="V7" t="n">
         <v>1.552776971255275</v>
       </c>
       <c r="W7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="X7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.568489131524303</v>
+        <v>1.568489131524305</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.914109652326335</v>
+        <v>1.914109652326331</v>
       </c>
       <c r="C8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="D8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="E8" t="n">
-        <v>2.320971071398901</v>
+        <v>2.320971071398902</v>
       </c>
       <c r="F8" t="n">
-        <v>2.049682389874815</v>
+        <v>2.049682389874818</v>
       </c>
       <c r="G8" t="n">
-        <v>2.964795836932435</v>
+        <v>2.964795836932439</v>
       </c>
       <c r="H8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="I8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78194354917836</v>
+        <v>2.781943549178361</v>
       </c>
       <c r="K8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="L8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="M8" t="n">
-        <v>2.784346547661483</v>
+        <v>2.784346547661475</v>
       </c>
       <c r="N8" t="n">
-        <v>2.109767366161005</v>
+        <v>2.109767366160998</v>
       </c>
       <c r="O8" t="n">
         <v>2.295147582199739</v>
       </c>
       <c r="P8" t="n">
-        <v>2.249706411867672</v>
+        <v>2.249706411867664</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.743088240365542</v>
+        <v>1.74308824036554</v>
       </c>
       <c r="R8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="S8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="T8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="U8" t="n">
-        <v>2.360360326094583</v>
+        <v>2.360360326094584</v>
       </c>
       <c r="V8" t="n">
-        <v>2.531629065686359</v>
+        <v>2.53162906568636</v>
       </c>
       <c r="W8" t="n">
-        <v>2.784517573545354</v>
+        <v>2.784517573545353</v>
       </c>
       <c r="X8" t="n">
-        <v>1.822847180641692</v>
+        <v>1.822847180641694</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.650911622082678</v>
+        <v>3.650911622082692</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.897944555265434</v>
+        <v>1.897944555265435</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.784346547661255</v>
+        <v>2.784346547661247</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.693381752306864</v>
+        <v>3.693381752306869</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.913344538527346</v>
+        <v>3.91334453852736</v>
       </c>
       <c r="C9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="D9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="E9" t="n">
-        <v>4.629990642407114</v>
+        <v>4.629990642407115</v>
       </c>
       <c r="F9" t="n">
-        <v>2.697257959594859</v>
+        <v>2.697257959594862</v>
       </c>
       <c r="G9" t="n">
-        <v>4.845016800172965</v>
+        <v>4.845016800172966</v>
       </c>
       <c r="H9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="I9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="J9" t="n">
-        <v>4.84261353945608</v>
+        <v>4.842613539456096</v>
       </c>
       <c r="K9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="L9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="M9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="N9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="O9" t="n">
-        <v>5.153771767761627</v>
+        <v>5.15377176776163</v>
       </c>
       <c r="P9" t="n">
-        <v>5.220920675869034</v>
+        <v>5.220920675869045</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.845016800172965</v>
+        <v>4.845016800172966</v>
       </c>
       <c r="R9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="S9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="T9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="U9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="V9" t="n">
-        <v>5.904433090817255</v>
+        <v>5.904433090817267</v>
       </c>
       <c r="W9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="X9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.283301273930654</v>
+        <v>4.283301273930664</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.84501653793898</v>
+        <v>4.845016537938985</v>
       </c>
     </row>
     <row r="10">
@@ -1293,10 +1293,10 @@
         <v>12.09913353877366</v>
       </c>
       <c r="C10" t="n">
-        <v>12.65136647669724</v>
+        <v>12.65136647669723</v>
       </c>
       <c r="D10" t="n">
-        <v>12.3018986058325</v>
+        <v>12.30189860583251</v>
       </c>
       <c r="E10" t="n">
         <v>10.44209795542156</v>
@@ -1308,16 +1308,16 @@
         <v>11.54725190188282</v>
       </c>
       <c r="H10" t="n">
-        <v>12.00463671062536</v>
+        <v>12.00463671062535</v>
       </c>
       <c r="I10" t="n">
-        <v>12.44039904766836</v>
+        <v>12.44039904766835</v>
       </c>
       <c r="J10" t="n">
         <v>11.97848526125413</v>
       </c>
       <c r="K10" t="n">
-        <v>12.12463899190338</v>
+        <v>12.12463899190337</v>
       </c>
       <c r="L10" t="n">
         <v>11.76515134930407</v>
@@ -1332,22 +1332,22 @@
         <v>12.10155329008503</v>
       </c>
       <c r="P10" t="n">
-        <v>12.2149391714846</v>
+        <v>12.21493917148459</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.30869601951713</v>
+        <v>12.30869601951712</v>
       </c>
       <c r="R10" t="n">
         <v>12.34898639711846</v>
       </c>
       <c r="S10" t="n">
-        <v>11.9458571524565</v>
+        <v>11.94585715245649</v>
       </c>
       <c r="T10" t="n">
         <v>12.17830042463602</v>
       </c>
       <c r="U10" t="n">
-        <v>11.76832810992823</v>
+        <v>11.76832810992822</v>
       </c>
       <c r="V10" t="n">
         <v>12.68896629379642</v>
@@ -1356,7 +1356,7 @@
         <v>11.84546604280255</v>
       </c>
       <c r="X10" t="n">
-        <v>12.20215516188545</v>
+        <v>12.20215516188546</v>
       </c>
       <c r="Y10" t="n">
         <v>12.2339147210953</v>
@@ -1365,10 +1365,10 @@
         <v>12.25698956600793</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.94538789678758</v>
+        <v>11.94538789678757</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.67541569371579</v>
+        <v>11.67541569371578</v>
       </c>
     </row>
     <row r="11">
@@ -1378,85 +1378,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.341208989348066</v>
+        <v>6.341208989348067</v>
       </c>
       <c r="C11" t="n">
-        <v>6.500404061909794</v>
+        <v>6.500404061909791</v>
       </c>
       <c r="D11" t="n">
-        <v>6.4011175291744</v>
+        <v>6.401117529174393</v>
       </c>
       <c r="E11" t="n">
-        <v>4.306568062072314</v>
+        <v>4.306568062072308</v>
       </c>
       <c r="F11" t="n">
-        <v>6.440924359840269</v>
+        <v>6.440924359840264</v>
       </c>
       <c r="G11" t="n">
-        <v>6.182999353362163</v>
+        <v>6.182999353362158</v>
       </c>
       <c r="H11" t="n">
-        <v>6.317719357701029</v>
+        <v>6.317719357701033</v>
       </c>
       <c r="I11" t="n">
-        <v>6.440657430772015</v>
+        <v>6.440657430772005</v>
       </c>
       <c r="J11" t="n">
-        <v>6.30371354320574</v>
+        <v>6.303713543205736</v>
       </c>
       <c r="K11" t="n">
-        <v>6.350523588664609</v>
+        <v>6.350523588664604</v>
       </c>
       <c r="L11" t="n">
-        <v>6.246654456193645</v>
+        <v>6.246654456193638</v>
       </c>
       <c r="M11" t="n">
-        <v>6.196019059581934</v>
+        <v>6.196019059581928</v>
       </c>
       <c r="N11" t="n">
-        <v>6.332076056836021</v>
+        <v>6.332076056836009</v>
       </c>
       <c r="O11" t="n">
-        <v>6.341746145844278</v>
+        <v>6.341746145844274</v>
       </c>
       <c r="P11" t="n">
-        <v>6.374187571834556</v>
+        <v>6.37418757183455</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.402765988925506</v>
+        <v>6.402765988925496</v>
       </c>
       <c r="R11" t="n">
-        <v>6.414916945350527</v>
+        <v>6.414916945350522</v>
       </c>
       <c r="S11" t="n">
-        <v>6.297760399823189</v>
+        <v>6.297760399823177</v>
       </c>
       <c r="T11" t="n">
-        <v>6.36606556257076</v>
+        <v>6.366065562570748</v>
       </c>
       <c r="U11" t="n">
-        <v>6.24736137307543</v>
+        <v>6.247361373075419</v>
       </c>
       <c r="V11" t="n">
-        <v>6.647105886140349</v>
+        <v>6.647105886140351</v>
       </c>
       <c r="W11" t="n">
-        <v>6.269927789650837</v>
+        <v>6.269927789650829</v>
       </c>
       <c r="X11" t="n">
-        <v>6.37263768255366</v>
+        <v>6.372637682553654</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.381055644686282</v>
+        <v>6.38105564468628</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.38663106950603</v>
+        <v>6.386631069506023</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.298602262376119</v>
+        <v>6.298602262376115</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.223069304914979</v>
+        <v>6.223069304914982</v>
       </c>
     </row>
   </sheetData>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.331342233069892</v>
+        <v>6.331342233069893</v>
       </c>
       <c r="C2" t="n">
-        <v>6.337109085671808</v>
+        <v>6.33710908567181</v>
       </c>
       <c r="D2" t="n">
-        <v>6.348892431476584</v>
+        <v>6.348892431476581</v>
       </c>
       <c r="E2" t="n">
-        <v>4.241209597485457</v>
+        <v>4.241209597485459</v>
       </c>
       <c r="F2" t="n">
-        <v>6.29130881376145</v>
+        <v>6.291308813761452</v>
       </c>
       <c r="G2" t="n">
-        <v>6.366239946802694</v>
+        <v>6.366239946802699</v>
       </c>
       <c r="H2" t="n">
         <v>6.369108590566881</v>
       </c>
       <c r="I2" t="n">
-        <v>6.343370859839913</v>
+        <v>6.343370859839916</v>
       </c>
       <c r="J2" t="n">
-        <v>6.354547500112049</v>
+        <v>6.354547500112051</v>
       </c>
       <c r="K2" t="n">
-        <v>6.344865065417348</v>
+        <v>6.344865065417349</v>
       </c>
       <c r="L2" t="n">
-        <v>6.246458760069938</v>
+        <v>6.24645876006994</v>
       </c>
       <c r="M2" t="n">
-        <v>6.331837379974644</v>
+        <v>6.331837379974645</v>
       </c>
       <c r="N2" t="n">
-        <v>6.340004168484268</v>
+        <v>6.34000416848427</v>
       </c>
       <c r="O2" t="n">
-        <v>6.305684605148427</v>
+        <v>6.305684605148429</v>
       </c>
       <c r="P2" t="n">
-        <v>6.332531258243883</v>
+        <v>6.332531258243888</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.345842274206981</v>
+        <v>6.345842274206984</v>
       </c>
       <c r="R2" t="n">
-        <v>6.202064137843244</v>
+        <v>6.202064137843246</v>
       </c>
       <c r="S2" t="n">
-        <v>6.302230609656692</v>
+        <v>6.302230609656698</v>
       </c>
       <c r="T2" t="n">
-        <v>6.315796894509026</v>
+        <v>6.315796894509027</v>
       </c>
       <c r="U2" t="n">
-        <v>6.36712515461377</v>
+        <v>6.367125154613777</v>
       </c>
       <c r="V2" t="n">
-        <v>6.601834429773365</v>
+        <v>6.601834429773363</v>
       </c>
       <c r="W2" t="n">
-        <v>6.488635613805315</v>
+        <v>6.488635613805318</v>
       </c>
       <c r="X2" t="n">
-        <v>6.532455358089845</v>
+        <v>6.532455358089852</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.442527238431135</v>
+        <v>6.442527238431138</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.371322063874536</v>
+        <v>6.371322063874542</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.494999877676443</v>
+        <v>6.494999877676449</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.358982521015434</v>
+        <v>6.358982521015432</v>
       </c>
     </row>
     <row r="3">
@@ -1719,7 +1719,7 @@
         <v>12.71045279179484</v>
       </c>
       <c r="E3" t="n">
-        <v>10.58109900704067</v>
+        <v>10.58109900704068</v>
       </c>
       <c r="F3" t="n">
         <v>12.70977166521285</v>
@@ -1734,7 +1734,7 @@
         <v>12.71045279179484</v>
       </c>
       <c r="J3" t="n">
-        <v>12.71080903696803</v>
+        <v>12.71080903696804</v>
       </c>
       <c r="K3" t="n">
         <v>12.71006392891728</v>
@@ -1798,82 +1798,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.585359953736435</v>
+        <v>-1.58535995373644</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.03492416578028479</v>
+        <v>-0.03492416578027768</v>
       </c>
       <c r="D4" t="n">
-        <v>2.623806666344359</v>
+        <v>2.623806666344367</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1342493417642536</v>
+        <v>-0.1342493417642493</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.83153727463611</v>
+        <v>-11.83153727463609</v>
       </c>
       <c r="G4" t="n">
-        <v>6.339409963964994</v>
+        <v>6.339409963965013</v>
       </c>
       <c r="H4" t="n">
-        <v>8.182937299631789</v>
+        <v>8.18293729963178</v>
       </c>
       <c r="I4" t="n">
-        <v>1.248031330056057</v>
+        <v>1.248031330056059</v>
       </c>
       <c r="J4" t="n">
-        <v>3.661949362196092</v>
+        <v>3.661949362196107</v>
       </c>
       <c r="K4" t="n">
         <v>1.712739601317598</v>
       </c>
       <c r="L4" t="n">
-        <v>-20.73979159194195</v>
+        <v>-20.73979159194198</v>
       </c>
       <c r="M4" t="n">
         <v>-1.206813518911573</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3301487230214006</v>
+        <v>0.3301487230214008</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.993514779312712</v>
+        <v>-6.993514779312718</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9148238913459399</v>
+        <v>-0.9148238913459414</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.811096057068146</v>
+        <v>1.811096057068142</v>
       </c>
       <c r="R4" t="n">
-        <v>-37.01471211360391</v>
+        <v>-37.01471211360395</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.069060546463691</v>
+        <v>-8.069060546463694</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.687516460393132</v>
+        <v>-5.687516460393128</v>
       </c>
       <c r="U4" t="n">
-        <v>5.894359209068426</v>
+        <v>5.894359209068429</v>
       </c>
       <c r="V4" t="n">
-        <v>9.378634787469608</v>
+        <v>9.378634787469599</v>
       </c>
       <c r="W4" t="n">
-        <v>37.73644760288658</v>
+        <v>37.73644760288649</v>
       </c>
       <c r="X4" t="n">
-        <v>46.62982903961732</v>
+        <v>46.62982903961733</v>
       </c>
       <c r="Y4" t="n">
-        <v>27.41959810956</v>
+        <v>27.41959810956003</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.204576635220034</v>
+        <v>7.204576635220028</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.90564690279287</v>
+        <v>39.90564690279301</v>
       </c>
       <c r="AB4" t="n">
         <v>2.928793923720373</v>
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417558</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5631378802222979</v>
+        <v>0.5631378802223013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5471764399077702</v>
+        <v>0.5471764399077712</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5560371491817454</v>
+        <v>0.5560371491817406</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5471764399077702</v>
+        <v>0.5471764399077712</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5643833248417544</v>
+        <v>0.564383324841754</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5643833248417565</v>
+        <v>0.5643833248417559</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="C6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="E6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8979385168564005</v>
+        <v>0.8979385168564042</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6403283769428707</v>
+        <v>0.6403283769428705</v>
       </c>
       <c r="O6" t="n">
-        <v>0.928224206244331</v>
+        <v>0.9282242062443316</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6282924054276721</v>
+        <v>0.6282924054276702</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="S6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6299341981725306</v>
+        <v>0.6299341981725219</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6624266693170257</v>
+        <v>0.6624266693170038</v>
       </c>
       <c r="X6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6517069671959244</v>
+        <v>0.6517069671959276</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6382803738325401</v>
+        <v>0.6382803738325332</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.899183961475853</v>
+        <v>0.8991839614758528</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6404802444158614</v>
+        <v>0.6404802444158595</v>
       </c>
     </row>
     <row r="7">
@@ -2086,7 +2086,7 @@
         <v>1.008751426796727</v>
       </c>
       <c r="J7" t="n">
-        <v>1.007505982177276</v>
+        <v>1.007505982177274</v>
       </c>
       <c r="K7" t="n">
         <v>1.008751426796727</v>
@@ -2119,10 +2119,10 @@
         <v>1.008751426796727</v>
       </c>
       <c r="U7" t="n">
-        <v>1.002854470213527</v>
+        <v>1.002854470213521</v>
       </c>
       <c r="V7" t="n">
-        <v>1.000405251136719</v>
+        <v>1.000405251136713</v>
       </c>
       <c r="W7" t="n">
         <v>1.008751426796727</v>
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.109904953482062</v>
+        <v>1.109904953482058</v>
       </c>
       <c r="C8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="D8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="E8" t="n">
-        <v>1.311347022111277</v>
+        <v>1.311347022111287</v>
       </c>
       <c r="F8" t="n">
-        <v>1.177028675323181</v>
+        <v>1.177028675323188</v>
       </c>
       <c r="G8" t="n">
-        <v>1.630112544215611</v>
+        <v>1.630112544215607</v>
       </c>
       <c r="H8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="I8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="J8" t="n">
-        <v>1.539524447706191</v>
+        <v>1.539524447706197</v>
       </c>
       <c r="K8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="L8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="M8" t="n">
-        <v>1.540769892326772</v>
+        <v>1.54076989232678</v>
       </c>
       <c r="N8" t="n">
-        <v>1.206777482578628</v>
+        <v>1.206777482578633</v>
       </c>
       <c r="O8" t="n">
-        <v>1.298561496776262</v>
+        <v>1.298561496776261</v>
       </c>
       <c r="P8" t="n">
-        <v>1.276063017083302</v>
+        <v>1.276063017083308</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.025230158985954</v>
+        <v>1.025230158985959</v>
       </c>
       <c r="R8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="S8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="T8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="U8" t="n">
-        <v>1.327368746996149</v>
+        <v>1.327368746996161</v>
       </c>
       <c r="V8" t="n">
-        <v>1.411240726532879</v>
+        <v>1.411240726532875</v>
       </c>
       <c r="W8" t="n">
-        <v>1.540854569612265</v>
+        <v>1.54085456961227</v>
       </c>
       <c r="X8" t="n">
-        <v>1.064719786762363</v>
+        <v>1.064719786762365</v>
       </c>
       <c r="Y8" t="n">
         <v>1.963862954514781</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.101901416033216</v>
+        <v>1.101901416033218</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.540769892325643</v>
+        <v>1.540769892325648</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.990844349281486</v>
+        <v>1.990844349281481</v>
       </c>
     </row>
     <row r="9">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.809026545165904</v>
+        <v>1.809026545165898</v>
       </c>
       <c r="C9" t="n">
         <v>2.189907461634078</v>
@@ -2247,13 +2247,13 @@
         <v>2.189907461634078</v>
       </c>
       <c r="E9" t="n">
-        <v>2.10200185838161</v>
+        <v>2.102001858381609</v>
       </c>
       <c r="F9" t="n">
-        <v>1.311872727638203</v>
+        <v>1.311872727638205</v>
       </c>
       <c r="G9" t="n">
-        <v>2.189907667929707</v>
+        <v>2.189907667929711</v>
       </c>
       <c r="H9" t="n">
         <v>2.189907461634078</v>
@@ -2262,7 +2262,7 @@
         <v>2.189907461634078</v>
       </c>
       <c r="J9" t="n">
-        <v>2.188662017014621</v>
+        <v>2.188662017014623</v>
       </c>
       <c r="K9" t="n">
         <v>2.189907461634078</v>
@@ -2280,10 +2280,10 @@
         <v>2.316131173292358</v>
       </c>
       <c r="P9" t="n">
-        <v>2.343582620078089</v>
+        <v>2.343582620078092</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.189907667929707</v>
+        <v>2.189907667929711</v>
       </c>
       <c r="R9" t="n">
         <v>2.189907461634078</v>
@@ -2298,7 +2298,7 @@
         <v>2.189907461634078</v>
       </c>
       <c r="V9" t="n">
-        <v>2.621089977398319</v>
+        <v>2.621089977398313</v>
       </c>
       <c r="W9" t="n">
         <v>2.189907461634078</v>
@@ -2310,7 +2310,7 @@
         <v>2.189907461634078</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.960270220174045</v>
+        <v>1.960270220174047</v>
       </c>
       <c r="AA9" t="n">
         <v>2.189907461634078</v>
@@ -2332,7 +2332,7 @@
         <v>12.72628974352976</v>
       </c>
       <c r="D10" t="n">
-        <v>12.66372782122354</v>
+        <v>12.66372782122355</v>
       </c>
       <c r="E10" t="n">
         <v>10.60250188827619</v>
@@ -2344,19 +2344,19 @@
         <v>12.5577777980477</v>
       </c>
       <c r="H10" t="n">
-        <v>12.54642936752907</v>
+        <v>12.54642936752908</v>
       </c>
       <c r="I10" t="n">
-        <v>12.69609875751576</v>
+        <v>12.69609875751577</v>
       </c>
       <c r="J10" t="n">
-        <v>12.63184913538071</v>
+        <v>12.63184913538072</v>
       </c>
       <c r="K10" t="n">
         <v>12.68481125135724</v>
       </c>
       <c r="L10" t="n">
-        <v>13.26885986454658</v>
+        <v>13.26885986454659</v>
       </c>
       <c r="M10" t="n">
         <v>12.75225120422816</v>
@@ -2377,10 +2377,10 @@
         <v>13.53444474972118</v>
       </c>
       <c r="S10" t="n">
-        <v>12.93987725891738</v>
+        <v>12.93987725891739</v>
       </c>
       <c r="T10" t="n">
-        <v>12.84929414233895</v>
+        <v>12.84929414233896</v>
       </c>
       <c r="U10" t="n">
         <v>12.57497857098227</v>
@@ -2392,19 +2392,19 @@
         <v>11.8386074626563</v>
       </c>
       <c r="X10" t="n">
-        <v>11.60734381359523</v>
+        <v>11.60734381359524</v>
       </c>
       <c r="Y10" t="n">
         <v>12.09000778057388</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.52917125297595</v>
+        <v>12.52917125297596</v>
       </c>
       <c r="AA10" t="n">
         <v>11.80178544582563</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.67058688473453</v>
+        <v>12.67058688473454</v>
       </c>
     </row>
     <row r="11">
@@ -2414,85 +2414,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.357251415870731</v>
+        <v>6.357251415870734</v>
       </c>
       <c r="C11" t="n">
-        <v>6.344778938180972</v>
+        <v>6.344778938180978</v>
       </c>
       <c r="D11" t="n">
-        <v>6.327632420962995</v>
+        <v>6.327632420962999</v>
       </c>
       <c r="E11" t="n">
-        <v>4.250947976654551</v>
+        <v>4.250947976654553</v>
       </c>
       <c r="F11" t="n">
-        <v>6.421225944844962</v>
+        <v>6.421225944844965</v>
       </c>
       <c r="G11" t="n">
-        <v>6.296920114841179</v>
+        <v>6.296920114841178</v>
       </c>
       <c r="H11" t="n">
-        <v>6.294477409814311</v>
+        <v>6.294477409814316</v>
       </c>
       <c r="I11" t="n">
-        <v>6.336839728499331</v>
+        <v>6.336839728499334</v>
       </c>
       <c r="J11" t="n">
         <v>6.318620493259544</v>
       </c>
       <c r="K11" t="n">
-        <v>6.333375016652018</v>
+        <v>6.33337501665202</v>
       </c>
       <c r="L11" t="n">
-        <v>6.500535757709737</v>
+        <v>6.500535757709738</v>
       </c>
       <c r="M11" t="n">
-        <v>6.351658946935671</v>
+        <v>6.35165894693568</v>
       </c>
       <c r="N11" t="n">
-        <v>6.342442138172541</v>
+        <v>6.342442138172545</v>
       </c>
       <c r="O11" t="n">
-        <v>6.398929279481413</v>
+        <v>6.398929279481415</v>
       </c>
       <c r="P11" t="n">
-        <v>6.35108264798624</v>
+        <v>6.351082647986248</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.332652852080946</v>
+        <v>6.332652852080948</v>
       </c>
       <c r="R11" t="n">
-        <v>6.575986552666166</v>
+        <v>6.575986552666171</v>
       </c>
       <c r="S11" t="n">
-        <v>6.406619473329845</v>
+        <v>6.406619473329854</v>
       </c>
       <c r="T11" t="n">
-        <v>6.37955769124656</v>
+        <v>6.37955769124657</v>
       </c>
       <c r="U11" t="n">
-        <v>6.304089758672676</v>
+        <v>6.30408975867268</v>
       </c>
       <c r="V11" t="n">
-        <v>6.496577198242901</v>
+        <v>6.496577198242899</v>
       </c>
       <c r="W11" t="n">
-        <v>6.091943210641071</v>
+        <v>6.091943210641077</v>
       </c>
       <c r="X11" t="n">
-        <v>6.029111557067387</v>
+        <v>6.029111557067394</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.161769208389447</v>
+        <v>6.161769208389452</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.288879327422916</v>
+        <v>6.288879327422913</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.081553339509431</v>
+        <v>6.081553339509438</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.336119819083465</v>
+        <v>6.336119819083466</v>
       </c>
     </row>
   </sheetData>
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.67060644902623</v>
+        <v>6.670606449026232</v>
       </c>
       <c r="C2" t="n">
         <v>6.596261127478778</v>
       </c>
       <c r="D2" t="n">
-        <v>6.68476202560687</v>
+        <v>6.684762025606868</v>
       </c>
       <c r="E2" t="n">
-        <v>4.419090178852513</v>
+        <v>4.419090178852517</v>
       </c>
       <c r="F2" t="n">
-        <v>6.626502272377137</v>
+        <v>6.626502272377135</v>
       </c>
       <c r="G2" t="n">
-        <v>6.783391667522451</v>
+        <v>6.783391667522452</v>
       </c>
       <c r="H2" t="n">
-        <v>6.690709029801123</v>
+        <v>6.690709029801122</v>
       </c>
       <c r="I2" t="n">
-        <v>6.632399112059062</v>
+        <v>6.63239911205906</v>
       </c>
       <c r="J2" t="n">
         <v>6.707500873254821</v>
       </c>
       <c r="K2" t="n">
-        <v>6.677393804446935</v>
+        <v>6.677393804446934</v>
       </c>
       <c r="L2" t="n">
-        <v>6.735644509547616</v>
+        <v>6.73564450954762</v>
       </c>
       <c r="M2" t="n">
-        <v>6.772882605417719</v>
+        <v>6.77288260541772</v>
       </c>
       <c r="N2" t="n">
-        <v>6.684881832998166</v>
+        <v>6.684881832998165</v>
       </c>
       <c r="O2" t="n">
-        <v>6.674299264947981</v>
+        <v>6.67429926494798</v>
       </c>
       <c r="P2" t="n">
-        <v>6.691749567580485</v>
+        <v>6.691749567580484</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.644746408731065</v>
+        <v>6.644746408731062</v>
       </c>
       <c r="R2" t="n">
-        <v>6.666350536026977</v>
+        <v>6.666350536026975</v>
       </c>
       <c r="S2" t="n">
-        <v>6.716280551717989</v>
+        <v>6.716280551717985</v>
       </c>
       <c r="T2" t="n">
-        <v>6.659097433598432</v>
+        <v>6.659097433598431</v>
       </c>
       <c r="U2" t="n">
-        <v>6.72218835192807</v>
+        <v>6.722188351928068</v>
       </c>
       <c r="V2" t="n">
-        <v>6.790249447502271</v>
+        <v>6.79024944750228</v>
       </c>
       <c r="W2" t="n">
-        <v>6.751858819891109</v>
+        <v>6.751858819891106</v>
       </c>
       <c r="X2" t="n">
-        <v>6.690973465594809</v>
+        <v>6.690973465594808</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.666655896579437</v>
+        <v>6.666655896579438</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.6510851618724</v>
+        <v>6.651085161872399</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.69165528897584</v>
+        <v>6.691655288975836</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.775494156197731</v>
+        <v>6.775494156197729</v>
       </c>
     </row>
     <row r="3">
@@ -2770,7 +2770,7 @@
         <v>12.92476355675892</v>
       </c>
       <c r="J3" t="n">
-        <v>12.91893832414734</v>
+        <v>12.91893832414735</v>
       </c>
       <c r="K3" t="n">
         <v>12.92454970407431</v>
@@ -2800,7 +2800,7 @@
         <v>12.92476355675892</v>
       </c>
       <c r="T3" t="n">
-        <v>12.92445824101703</v>
+        <v>12.92445824101704</v>
       </c>
       <c r="U3" t="n">
         <v>12.92545293073404</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.09733201548247</v>
+        <v>30.09733201548287</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77614453528912</v>
+        <v>12.77614453528911</v>
       </c>
       <c r="D4" t="n">
-        <v>38.15357290435762</v>
+        <v>38.15357290435772</v>
       </c>
       <c r="E4" t="n">
-        <v>13.49676799984922</v>
+        <v>13.4967679998494</v>
       </c>
       <c r="F4" t="n">
-        <v>21.63917972659558</v>
+        <v>21.63917972659556</v>
       </c>
       <c r="G4" t="n">
-        <v>59.84792787208122</v>
+        <v>59.84792787208129</v>
       </c>
       <c r="H4" t="n">
-        <v>41.2009283384452</v>
+        <v>41.20092833844517</v>
       </c>
       <c r="I4" t="n">
-        <v>23.49086562726522</v>
+        <v>23.49086562726524</v>
       </c>
       <c r="J4" t="n">
-        <v>43.03102013195648</v>
+        <v>43.03102013195656</v>
       </c>
       <c r="K4" t="n">
-        <v>33.48277520919562</v>
+        <v>33.48277520919559</v>
       </c>
       <c r="L4" t="n">
-        <v>49.9857394508772</v>
+        <v>49.98573945087788</v>
       </c>
       <c r="M4" t="n">
-        <v>63.55611418313489</v>
+        <v>63.55611418313492</v>
       </c>
       <c r="N4" t="n">
-        <v>37.13632369250293</v>
+        <v>37.13632369250289</v>
       </c>
       <c r="O4" t="n">
-        <v>30.38225346185614</v>
+        <v>30.38225346185624</v>
       </c>
       <c r="P4" t="n">
-        <v>36.23710056968849</v>
+        <v>36.23710056968847</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.08449019485895</v>
+        <v>26.08449019485896</v>
       </c>
       <c r="R4" t="n">
-        <v>33.67215235177517</v>
+        <v>33.6721523517752</v>
       </c>
       <c r="S4" t="n">
-        <v>42.62453126718632</v>
+        <v>42.62453126718616</v>
       </c>
       <c r="T4" t="n">
-        <v>30.86942792474191</v>
+        <v>30.86942792474197</v>
       </c>
       <c r="U4" t="n">
-        <v>45.18398362231091</v>
+        <v>45.18398362231079</v>
       </c>
       <c r="V4" t="n">
-        <v>13.76582393000871</v>
+        <v>13.7658239300087</v>
       </c>
       <c r="W4" t="n">
-        <v>54.76660423444824</v>
+        <v>54.76660423444825</v>
       </c>
       <c r="X4" t="n">
-        <v>39.04674329832226</v>
+        <v>39.04674329832245</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.61517527396047</v>
+        <v>31.61517527396041</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.90282286527184</v>
+        <v>25.90282286527235</v>
       </c>
       <c r="AA4" t="n">
-        <v>38.30280102806631</v>
+        <v>38.30280102806637</v>
       </c>
       <c r="AB4" t="n">
-        <v>64.22316571788861</v>
+        <v>64.22316571788846</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7472213667773762</v>
+        <v>0.7472213667773793</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7446797531752506</v>
+        <v>0.7446797531752579</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7226825278581525</v>
+        <v>0.7226825278581577</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7306157853051543</v>
+        <v>0.7306157853051691</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7472213667773752</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7226825278581551</v>
+        <v>0.7226825278581577</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7472213667773767</v>
+        <v>0.7472213667773788</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7472213667773753</v>
+        <v>0.7472213667773766</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="C6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="E6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="G6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="H6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="I6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="J6" t="n">
-        <v>1.446946813090217</v>
+        <v>1.446946813090227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="L6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="M6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8963734149367729</v>
+        <v>0.8963734149367282</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8970732650558478</v>
+        <v>0.8970732650558558</v>
       </c>
       <c r="P6" t="n">
-        <v>1.477781799414284</v>
+        <v>1.477781799414294</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="R6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8755826415303583</v>
+        <v>0.8755826415303724</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9247467047090678</v>
+        <v>0.9247467047090688</v>
       </c>
       <c r="X6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9084302770140438</v>
+        <v>0.9084302770140337</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8921882230025772</v>
+        <v>0.8921882230025817</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.449488426692342</v>
+        <v>1.449488426692351</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9071132424379007</v>
+        <v>0.9071132424379047</v>
       </c>
     </row>
     <row r="7">
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="C7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="D7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="E7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="F7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="G7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="H7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="I7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="J7" t="n">
-        <v>1.421751997972207</v>
+        <v>1.421751997972216</v>
       </c>
       <c r="K7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="L7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="M7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="N7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="O7" t="n">
-        <v>1.422253776428277</v>
+        <v>1.422253776428281</v>
       </c>
       <c r="P7" t="n">
-        <v>1.422253776428277</v>
+        <v>1.422253776428281</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="R7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="S7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="T7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="U7" t="n">
-        <v>1.423358582866441</v>
+        <v>1.423358582866446</v>
       </c>
       <c r="V7" t="n">
-        <v>1.407688030102132</v>
+        <v>1.407688030102127</v>
       </c>
       <c r="W7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="X7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.424293611574331</v>
+        <v>1.424293611574337</v>
       </c>
     </row>
     <row r="8">
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.727201019719365</v>
+        <v>1.72720101971937</v>
       </c>
       <c r="C8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="D8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="E8" t="n">
-        <v>2.088131041295326</v>
+        <v>2.088131041295335</v>
       </c>
       <c r="F8" t="n">
-        <v>1.847468680394585</v>
+        <v>1.847468680394589</v>
       </c>
       <c r="G8" t="n">
-        <v>2.659273144306003</v>
+        <v>2.65927314430601</v>
       </c>
       <c r="H8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="I8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="J8" t="n">
-        <v>2.496653521784524</v>
+        <v>2.496653521784532</v>
       </c>
       <c r="K8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="L8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="M8" t="n">
-        <v>2.499195135387222</v>
+        <v>2.499195135387229</v>
       </c>
       <c r="N8" t="n">
-        <v>1.900770543811096</v>
+        <v>1.900770543811101</v>
       </c>
       <c r="O8" t="n">
-        <v>2.065222817350493</v>
+        <v>2.065222817350494</v>
       </c>
       <c r="P8" t="n">
-        <v>2.024911591409301</v>
+        <v>2.024911591409305</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57548655621899</v>
+        <v>1.575486556218991</v>
       </c>
       <c r="R8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="S8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="T8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="U8" t="n">
-        <v>2.123251308787129</v>
+        <v>2.12325130878714</v>
       </c>
       <c r="V8" t="n">
-        <v>2.272536282735195</v>
+        <v>2.272536282735202</v>
       </c>
       <c r="W8" t="n">
-        <v>2.499346853846916</v>
+        <v>2.499346853846923</v>
       </c>
       <c r="X8" t="n">
-        <v>1.64624135058656</v>
+        <v>1.646241350586565</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.268236018182447</v>
+        <v>3.268236018182458</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.712860832720274</v>
+        <v>1.712860832720275</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.499195135386645</v>
+        <v>2.499195135386652</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.305607541833556</v>
+        <v>3.305607541833561</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.252852074046326</v>
+        <v>3.252852074046333</v>
       </c>
       <c r="C9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="D9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="E9" t="n">
-        <v>3.835862405458067</v>
+        <v>3.835862405458077</v>
       </c>
       <c r="F9" t="n">
-        <v>2.263533865839394</v>
+        <v>2.263533865839399</v>
       </c>
       <c r="G9" t="n">
-        <v>4.010791803416937</v>
+        <v>4.010791803416947</v>
       </c>
       <c r="H9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="I9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="J9" t="n">
-        <v>4.008249959052343</v>
+        <v>4.008249959052351</v>
       </c>
       <c r="K9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="L9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="M9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="N9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="O9" t="n">
-        <v>4.261972037293019</v>
+        <v>4.261972037293026</v>
       </c>
       <c r="P9" t="n">
-        <v>4.316599428634007</v>
+        <v>4.316599428634023</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.010791803416937</v>
+        <v>4.010791803416947</v>
       </c>
       <c r="R9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="S9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="T9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="U9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="V9" t="n">
-        <v>4.86883117522821</v>
+        <v>4.868831175228227</v>
       </c>
       <c r="W9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="X9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.553821545236917</v>
+        <v>3.553821545236927</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.010791572654466</v>
+        <v>4.010791572654477</v>
       </c>
     </row>
     <row r="10">
@@ -3365,25 +3365,25 @@
         <v>12.22691139833956</v>
       </c>
       <c r="C10" t="n">
-        <v>12.66666169508883</v>
+        <v>12.66666169508884</v>
       </c>
       <c r="D10" t="n">
-        <v>12.15475629841756</v>
+        <v>12.15475629841757</v>
       </c>
       <c r="E10" t="n">
         <v>10.42887033650583</v>
       </c>
       <c r="F10" t="n">
-        <v>12.49581031463383</v>
+        <v>12.49581031463384</v>
       </c>
       <c r="G10" t="n">
-        <v>11.55597483652468</v>
+        <v>11.55597483652469</v>
       </c>
       <c r="H10" t="n">
         <v>12.12535448073459</v>
       </c>
       <c r="I10" t="n">
-        <v>12.46234238993072</v>
+        <v>12.46234238993073</v>
       </c>
       <c r="J10" t="n">
         <v>11.97209127994699</v>
@@ -3392,7 +3392,7 @@
         <v>12.19552418169352</v>
       </c>
       <c r="L10" t="n">
-        <v>11.84680106186614</v>
+        <v>11.84680106186613</v>
       </c>
       <c r="M10" t="n">
         <v>11.64187671837851</v>
@@ -3404,10 +3404,10 @@
         <v>12.19963552159024</v>
       </c>
       <c r="P10" t="n">
-        <v>12.09836373810692</v>
+        <v>12.09836373810693</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.38771406349715</v>
+        <v>12.38771406349716</v>
       </c>
       <c r="R10" t="n">
         <v>12.26496401396609</v>
@@ -3422,7 +3422,7 @@
         <v>11.92977156024411</v>
       </c>
       <c r="V10" t="n">
-        <v>12.79789513360466</v>
+        <v>12.79789513360467</v>
       </c>
       <c r="W10" t="n">
         <v>11.75290443276666</v>
@@ -3434,10 +3434,10 @@
         <v>12.24656170486317</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.34334247083816</v>
+        <v>12.34334247083817</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.10888851390977</v>
+        <v>12.10888851390978</v>
       </c>
       <c r="AB10" t="n">
         <v>11.6895253209159</v>
@@ -3450,61 +3450,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.353081493022549</v>
+        <v>6.353081493022551</v>
       </c>
       <c r="C11" t="n">
-        <v>6.479267499153183</v>
+        <v>6.479267499153182</v>
       </c>
       <c r="D11" t="n">
-        <v>6.334406269194021</v>
+        <v>6.334406269194016</v>
       </c>
       <c r="E11" t="n">
-        <v>4.291798263310522</v>
+        <v>4.291798263310526</v>
       </c>
       <c r="F11" t="n">
-        <v>6.431492617251066</v>
+        <v>6.431492617251063</v>
       </c>
       <c r="G11" t="n">
-        <v>6.16063929971649</v>
+        <v>6.160639299716488</v>
       </c>
       <c r="H11" t="n">
-        <v>6.326975352644482</v>
+        <v>6.326975352644485</v>
       </c>
       <c r="I11" t="n">
         <v>6.421996007503401</v>
       </c>
       <c r="J11" t="n">
-        <v>6.276682450721166</v>
+        <v>6.276682450721165</v>
       </c>
       <c r="K11" t="n">
-        <v>6.345684868497178</v>
+        <v>6.345684868497184</v>
       </c>
       <c r="L11" t="n">
-        <v>6.245168139108759</v>
+        <v>6.245168139108753</v>
       </c>
       <c r="M11" t="n">
-        <v>6.189279565154936</v>
+        <v>6.189279565154939</v>
       </c>
       <c r="N11" t="n">
-        <v>6.332721710318794</v>
+        <v>6.332721710318792</v>
       </c>
       <c r="O11" t="n">
         <v>6.344683068210993</v>
       </c>
       <c r="P11" t="n">
-        <v>6.315814956472764</v>
+        <v>6.315814956472763</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.400391709721708</v>
+        <v>6.400391709721704</v>
       </c>
       <c r="R11" t="n">
-        <v>6.366157629382006</v>
+        <v>6.366157629382011</v>
       </c>
       <c r="S11" t="n">
         <v>6.276483829361925</v>
       </c>
       <c r="T11" t="n">
-        <v>6.37657895105759</v>
+        <v>6.376578951057588</v>
       </c>
       <c r="U11" t="n">
         <v>6.269150155306889</v>
@@ -3513,22 +3513,22 @@
         <v>6.647319270921313</v>
       </c>
       <c r="W11" t="n">
-        <v>6.218659183981186</v>
+        <v>6.218659183981187</v>
       </c>
       <c r="X11" t="n">
-        <v>6.325105538472648</v>
+        <v>6.325105538472651</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.358805196362631</v>
+        <v>6.358805196362633</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.386561461100782</v>
+        <v>6.386561461100781</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.320429544439989</v>
+        <v>6.320429544439985</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.208733235244049</v>
+        <v>6.208733235244046</v>
       </c>
     </row>
   </sheetData>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.622717660730848</v>
+        <v>6.62271766073084</v>
       </c>
       <c r="C2" t="n">
-        <v>6.580167203223128</v>
+        <v>6.580167203223139</v>
       </c>
       <c r="D2" t="n">
-        <v>6.677143988231959</v>
+        <v>6.677143988231972</v>
       </c>
       <c r="E2" t="n">
-        <v>4.410016639446291</v>
+        <v>4.410016639446289</v>
       </c>
       <c r="F2" t="n">
-        <v>6.585357631266841</v>
+        <v>6.585357631266842</v>
       </c>
       <c r="G2" t="n">
-        <v>6.747056976335277</v>
+        <v>6.747056976335288</v>
       </c>
       <c r="H2" t="n">
-        <v>6.65187409014946</v>
+        <v>6.651874090149466</v>
       </c>
       <c r="I2" t="n">
-        <v>6.605645415588803</v>
+        <v>6.60564541558881</v>
       </c>
       <c r="J2" t="n">
-        <v>6.676649651420435</v>
+        <v>6.676649651420432</v>
       </c>
       <c r="K2" t="n">
-        <v>6.628130518228544</v>
+        <v>6.628130518228554</v>
       </c>
       <c r="L2" t="n">
-        <v>6.687184629465602</v>
+        <v>6.687184629465615</v>
       </c>
       <c r="M2" t="n">
-        <v>6.723836465681249</v>
+        <v>6.723836465681262</v>
       </c>
       <c r="N2" t="n">
-        <v>6.63041220021008</v>
+        <v>6.630412200210093</v>
       </c>
       <c r="O2" t="n">
-        <v>6.627243656643971</v>
+        <v>6.627243656643968</v>
       </c>
       <c r="P2" t="n">
-        <v>6.666659453018482</v>
+        <v>6.666659453018489</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.577889324659488</v>
+        <v>6.577889324659499</v>
       </c>
       <c r="R2" t="n">
-        <v>6.631208499687814</v>
+        <v>6.631208499687813</v>
       </c>
       <c r="S2" t="n">
-        <v>6.679730971529521</v>
+        <v>6.679730971529523</v>
       </c>
       <c r="T2" t="n">
         <v>6.621962864927403</v>
       </c>
       <c r="U2" t="n">
-        <v>6.666334037351236</v>
+        <v>6.666334037351248</v>
       </c>
       <c r="V2" t="n">
-        <v>6.797273137838624</v>
+        <v>6.797273137838622</v>
       </c>
       <c r="W2" t="n">
-        <v>6.714463385430408</v>
+        <v>6.714463385430419</v>
       </c>
       <c r="X2" t="n">
-        <v>6.704814845546805</v>
+        <v>6.704814845546816</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.679575265854663</v>
+        <v>6.679575265854664</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.629527546314653</v>
+        <v>6.629527546314665</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.659888896911824</v>
+        <v>6.659888896911828</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.738351788372096</v>
+        <v>6.738351788372107</v>
       </c>
     </row>
     <row r="3">
@@ -3782,28 +3782,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="C3" t="n">
-        <v>12.89997483768421</v>
+        <v>12.89997483768422</v>
       </c>
       <c r="D3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="E3" t="n">
-        <v>10.69695584227268</v>
+        <v>10.69695584227267</v>
       </c>
       <c r="F3" t="n">
-        <v>12.90048541185741</v>
+        <v>12.90048541185742</v>
       </c>
       <c r="G3" t="n">
-        <v>12.90078858580698</v>
+        <v>12.90078858580699</v>
       </c>
       <c r="H3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="I3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="J3" t="n">
         <v>12.89635637073534</v>
@@ -3812,55 +3812,55 @@
         <v>12.90069525579868</v>
       </c>
       <c r="L3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="M3" t="n">
-        <v>12.90031756200334</v>
+        <v>12.90031756200335</v>
       </c>
       <c r="N3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="O3" t="n">
         <v>12.90021477566957</v>
       </c>
       <c r="P3" t="n">
-        <v>12.90090995824454</v>
+        <v>12.90090995824455</v>
       </c>
       <c r="Q3" t="n">
         <v>12.90098863056365</v>
       </c>
       <c r="R3" t="n">
-        <v>12.90213477783689</v>
+        <v>12.9021347778369</v>
       </c>
       <c r="S3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="T3" t="n">
-        <v>12.90009943866056</v>
+        <v>12.90009943866057</v>
       </c>
       <c r="U3" t="n">
-        <v>12.90207633974599</v>
+        <v>12.902076339746</v>
       </c>
       <c r="V3" t="n">
         <v>13.09976782566588</v>
       </c>
       <c r="W3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="X3" t="n">
-        <v>12.90783333345804</v>
+        <v>12.90783333345805</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.89906145766499</v>
+        <v>12.899061457665</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.90090714150603</v>
+        <v>12.90090714150604</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.90099859071352</v>
+        <v>12.90099859071353</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.91138002827559</v>
+        <v>12.9113800282756</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.77222561343727</v>
+        <v>22.77222561343717</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45509280048091</v>
+        <v>13.4550928004809</v>
       </c>
       <c r="D4" t="n">
-        <v>39.40803692377364</v>
+        <v>39.4080369237737</v>
       </c>
       <c r="E4" t="n">
-        <v>13.28178555024651</v>
+        <v>13.28178555024654</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3516306695533</v>
+        <v>15.35163066955327</v>
       </c>
       <c r="G4" t="n">
-        <v>51.86877461192942</v>
+        <v>51.8687746119293</v>
       </c>
       <c r="H4" t="n">
-        <v>34.44810388411967</v>
+        <v>34.44810388411958</v>
       </c>
       <c r="I4" t="n">
-        <v>20.96643664172591</v>
+        <v>20.96643664172593</v>
       </c>
       <c r="J4" t="n">
-        <v>37.65994046255281</v>
+        <v>37.65994046255282</v>
       </c>
       <c r="K4" t="n">
         <v>23.85944707944966</v>
       </c>
       <c r="L4" t="n">
-        <v>40.11628420725661</v>
+        <v>40.1162842072569</v>
       </c>
       <c r="M4" t="n">
-        <v>52.65057810354222</v>
+        <v>52.65057810354223</v>
       </c>
       <c r="N4" t="n">
-        <v>26.70171556322528</v>
+        <v>26.70171556322524</v>
       </c>
       <c r="O4" t="n">
-        <v>22.80747540650306</v>
+        <v>22.80747540650299</v>
       </c>
       <c r="P4" t="n">
-        <v>32.9844913038171</v>
+        <v>32.98449130381711</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.89228997225859</v>
+        <v>12.8922899722586</v>
       </c>
       <c r="R4" t="n">
-        <v>27.95559062047971</v>
+        <v>27.95559062047969</v>
       </c>
       <c r="S4" t="n">
-        <v>36.29575691777303</v>
+        <v>36.29575691777302</v>
       </c>
       <c r="T4" t="n">
-        <v>25.38700083008393</v>
+        <v>25.38700083008389</v>
       </c>
       <c r="U4" t="n">
-        <v>33.67784339022148</v>
+        <v>33.67784339022125</v>
       </c>
       <c r="V4" t="n">
-        <v>16.96768650140927</v>
+        <v>16.9676865014092</v>
       </c>
       <c r="W4" t="n">
-        <v>47.55723665337872</v>
+        <v>47.55723665337879</v>
       </c>
       <c r="X4" t="n">
-        <v>44.41876534389017</v>
+        <v>44.41876534389001</v>
       </c>
       <c r="Y4" t="n">
-        <v>38.78437380031702</v>
+        <v>38.78437380031699</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.17054930696766</v>
+        <v>23.17054930696769</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.72310121845564</v>
+        <v>33.7231012184557</v>
       </c>
       <c r="AB4" t="n">
-        <v>56.29104069142124</v>
+        <v>56.29104069142129</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7161028160130041</v>
+        <v>0.7161028160129974</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7138032031309216</v>
+        <v>0.7138032031309316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7161028160130066</v>
+        <v>0.7161028160129973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6921138192023637</v>
+        <v>0.6921138192023736</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7010397262083367</v>
+        <v>0.7010397262083368</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7161028160130041</v>
+        <v>0.7161028160129999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6921138192023637</v>
+        <v>0.6921138192023769</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7161028160130072</v>
+        <v>0.7161028160129939</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7161028160130045</v>
+        <v>0.716102816013003</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="D6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="E6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="J6" t="n">
-        <v>1.350474217820714</v>
+        <v>1.350474217820727</v>
       </c>
       <c r="K6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="L6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8617131476329383</v>
+        <v>0.8617131476329118</v>
       </c>
       <c r="O6" t="n">
-        <v>1.378776491625371</v>
+        <v>1.378776491625387</v>
       </c>
       <c r="P6" t="n">
-        <v>1.378542312366353</v>
+        <v>1.378542312366358</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="S6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="V6" t="n">
         <v>1.337710740898131</v>
       </c>
       <c r="W6" t="n">
-        <v>1.378860021699622</v>
+        <v>1.37886002169964</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8580130905915366</v>
+        <v>0.8580130905915364</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8738086022516096</v>
+        <v>0.8738086022515779</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.352773830702804</v>
+        <v>1.352773830702813</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8708321132637156</v>
+        <v>0.8708321132637036</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.317525327305348</v>
+        <v>1.317525327305335</v>
       </c>
       <c r="C7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="D7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="E7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="F7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="G7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="H7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="I7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="J7" t="n">
-        <v>1.315225714423261</v>
+        <v>1.315225714423269</v>
       </c>
       <c r="K7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="L7" t="n">
-        <v>1.317525327305348</v>
+        <v>1.317525327305335</v>
       </c>
       <c r="M7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="N7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="O7" t="n">
-        <v>1.315626239373903</v>
+        <v>1.315626239373907</v>
       </c>
       <c r="P7" t="n">
-        <v>1.315626239373903</v>
+        <v>1.315626239373907</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="R7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="S7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="T7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="U7" t="n">
-        <v>1.314995085530784</v>
+        <v>1.314995085530781</v>
       </c>
       <c r="V7" t="n">
         <v>1.302462237500676</v>
       </c>
       <c r="W7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="X7" t="n">
-        <v>1.317525327305348</v>
+        <v>1.317525327305335</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.317525327305349</v>
+        <v>1.317525327305334</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.57526087442894</v>
+        <v>1.575260874428958</v>
       </c>
       <c r="C8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="D8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="E8" t="n">
-        <v>1.890859609713223</v>
+        <v>1.890859609713238</v>
       </c>
       <c r="F8" t="n">
-        <v>1.680423424897123</v>
+        <v>1.680423424897124</v>
       </c>
       <c r="G8" t="n">
-        <v>2.390268676894459</v>
+        <v>2.39026867689446</v>
       </c>
       <c r="H8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="I8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="J8" t="n">
-        <v>2.247996176898272</v>
+        <v>2.247996176898275</v>
       </c>
       <c r="K8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="L8" t="n">
-        <v>2.250295789780366</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="M8" t="n">
-        <v>2.250295789781446</v>
+        <v>2.250295789781456</v>
       </c>
       <c r="N8" t="n">
-        <v>1.727030799405245</v>
+        <v>1.727030799405252</v>
       </c>
       <c r="O8" t="n">
-        <v>1.87082856200375</v>
+        <v>1.870828562003761</v>
       </c>
       <c r="P8" t="n">
-        <v>1.835580255769401</v>
+        <v>1.835580255769427</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.442601106740383</v>
+        <v>1.44260110674039</v>
       </c>
       <c r="R8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="S8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="T8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="U8" t="n">
-        <v>1.920331128231836</v>
+        <v>1.920331128231851</v>
       </c>
       <c r="V8" t="n">
-        <v>2.05019598441771</v>
+        <v>2.050195984417709</v>
       </c>
       <c r="W8" t="n">
-        <v>2.25042845311342</v>
+        <v>2.250428453113427</v>
       </c>
       <c r="X8" t="n">
-        <v>1.50446939782064</v>
+        <v>1.50446939782065</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.920630884272419</v>
+        <v>2.9206308842724</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.562721754343773</v>
+        <v>1.562721754343787</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.250295789780365</v>
+        <v>2.25029578978038</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.955426204025425</v>
+        <v>2.955426204025421</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.832795068223236</v>
+        <v>2.832795068223241</v>
       </c>
       <c r="C9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="D9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="E9" t="n">
-        <v>3.326307800637895</v>
+        <v>3.326307800637891</v>
       </c>
       <c r="F9" t="n">
-        <v>1.995346560273917</v>
+        <v>1.995346560273931</v>
       </c>
       <c r="G9" t="n">
-        <v>3.474383881823786</v>
+        <v>3.474383881823803</v>
       </c>
       <c r="H9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="I9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="J9" t="n">
-        <v>3.472084033082758</v>
+        <v>3.472084033082762</v>
       </c>
       <c r="K9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="L9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964856</v>
       </c>
       <c r="M9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="N9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="O9" t="n">
-        <v>3.687005574562202</v>
+        <v>3.687005574562193</v>
       </c>
       <c r="P9" t="n">
         <v>3.733247144758896</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.474383881823786</v>
+        <v>3.474383881823803</v>
       </c>
       <c r="R9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="S9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="T9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="U9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="V9" t="n">
-        <v>4.199699485978992</v>
+        <v>4.199699485978996</v>
       </c>
       <c r="W9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="X9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964856</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.087562879525995</v>
+        <v>3.087562879526018</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.474383645964847</v>
+        <v>3.474383645964853</v>
       </c>
     </row>
     <row r="10">
@@ -4398,79 +4398,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.34815136677466</v>
+        <v>12.34815136677468</v>
       </c>
       <c r="C10" t="n">
-        <v>12.59906673460962</v>
+        <v>12.59906673460963</v>
       </c>
       <c r="D10" t="n">
-        <v>12.0378751935893</v>
+        <v>12.03787519358929</v>
       </c>
       <c r="E10" t="n">
-        <v>10.40220730351259</v>
+        <v>10.4022073035126</v>
       </c>
       <c r="F10" t="n">
-        <v>12.57386200500074</v>
+        <v>12.57386200500075</v>
       </c>
       <c r="G10" t="n">
         <v>11.60780316844582</v>
       </c>
       <c r="H10" t="n">
-        <v>12.19072211847053</v>
+        <v>12.19072211847054</v>
       </c>
       <c r="I10" t="n">
-        <v>12.45751347274114</v>
+        <v>12.45751347274115</v>
       </c>
       <c r="J10" t="n">
-        <v>12.00038963192796</v>
+        <v>12.00038963192797</v>
       </c>
       <c r="K10" t="n">
-        <v>12.32222614291758</v>
+        <v>12.32222614291759</v>
       </c>
       <c r="L10" t="n">
-        <v>11.97050716432796</v>
+        <v>11.97050716432797</v>
       </c>
       <c r="M10" t="n">
-        <v>11.76437623323751</v>
+        <v>11.76437623323752</v>
       </c>
       <c r="N10" t="n">
-        <v>12.30911143500695</v>
+        <v>12.30911143500696</v>
       </c>
       <c r="O10" t="n">
-        <v>12.31554358827759</v>
+        <v>12.3155435882776</v>
       </c>
       <c r="P10" t="n">
-        <v>12.08455029711861</v>
+        <v>12.08455029711862</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.61847674019546</v>
+        <v>12.61847674019547</v>
       </c>
       <c r="R10" t="n">
-        <v>12.31648146264421</v>
+        <v>12.31648146264422</v>
       </c>
       <c r="S10" t="n">
-        <v>12.01172571714485</v>
+        <v>12.01172571714487</v>
       </c>
       <c r="T10" t="n">
-        <v>12.35573461262525</v>
+        <v>12.35573461262526</v>
       </c>
       <c r="U10" t="n">
-        <v>12.09987187398261</v>
+        <v>12.09987187398262</v>
       </c>
       <c r="V10" t="n">
-        <v>12.6716671483607</v>
+        <v>12.67166714836071</v>
       </c>
       <c r="W10" t="n">
-        <v>11.81106237455248</v>
+        <v>11.81106237455249</v>
       </c>
       <c r="X10" t="n">
         <v>11.91825976971146</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.0060320220046</v>
+        <v>12.00603202200462</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.30770828192569</v>
+        <v>12.30770828192568</v>
       </c>
       <c r="AA10" t="n">
         <v>12.13378439599077</v>
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.371170412019096</v>
+        <v>6.371170412019093</v>
       </c>
       <c r="C11" t="n">
-        <v>6.443253057386966</v>
+        <v>6.443253057386976</v>
       </c>
       <c r="D11" t="n">
-        <v>6.284420091929372</v>
+        <v>6.284420091929361</v>
       </c>
       <c r="E11" t="n">
-        <v>4.27590511500259</v>
+        <v>4.275905115002597</v>
       </c>
       <c r="F11" t="n">
-        <v>6.436742940260028</v>
+        <v>6.436742940260023</v>
       </c>
       <c r="G11" t="n">
-        <v>6.158744490935913</v>
+        <v>6.158744490935919</v>
       </c>
       <c r="H11" t="n">
-        <v>6.328696031762084</v>
+        <v>6.328696031762091</v>
       </c>
       <c r="I11" t="n">
-        <v>6.403858273608158</v>
+        <v>6.403858273608153</v>
       </c>
       <c r="J11" t="n">
-        <v>6.268981929986493</v>
+        <v>6.268981929986499</v>
       </c>
       <c r="K11" t="n">
-        <v>6.364925228395957</v>
+        <v>6.36492522839597</v>
       </c>
       <c r="L11" t="n">
-        <v>6.263808065159937</v>
+        <v>6.263808065159947</v>
       </c>
       <c r="M11" t="n">
-        <v>6.206979541062576</v>
+        <v>6.206979541062577</v>
       </c>
       <c r="N11" t="n">
-        <v>6.361101658131145</v>
+        <v>6.361101658131156</v>
       </c>
       <c r="O11" t="n">
-        <v>6.361216403144102</v>
+        <v>6.361216403144099</v>
       </c>
       <c r="P11" t="n">
-        <v>6.295213205622297</v>
+        <v>6.295213205622304</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.44934551422998</v>
+        <v>6.449345514229982</v>
       </c>
       <c r="R11" t="n">
-        <v>6.364734374908767</v>
+        <v>6.364734374908761</v>
       </c>
       <c r="S11" t="n">
-        <v>6.275108980111275</v>
+        <v>6.275108980111279</v>
       </c>
       <c r="T11" t="n">
-        <v>6.374275134293566</v>
+        <v>6.374275134293562</v>
       </c>
       <c r="U11" t="n">
-        <v>6.301328448954947</v>
+        <v>6.30132844895495</v>
       </c>
       <c r="V11" t="n">
         <v>6.602485965388854</v>
       </c>
       <c r="W11" t="n">
-        <v>6.218538933656505</v>
+        <v>6.218538933656504</v>
       </c>
       <c r="X11" t="n">
-        <v>6.25455572045828</v>
+        <v>6.25455572045829</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.273244026713241</v>
+        <v>6.273244026713239</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.359620174792999</v>
+        <v>6.359620174793002</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.310803993346408</v>
+        <v>6.31080399334641</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.207902540382435</v>
+        <v>6.207902540382437</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.596326456597893</v>
+        <v>6.59632645659791</v>
       </c>
       <c r="C2" t="n">
-        <v>6.571732165983317</v>
+        <v>6.571732165983319</v>
       </c>
       <c r="D2" t="n">
         <v>6.618850860565926</v>
       </c>
       <c r="E2" t="n">
-        <v>4.378626444160853</v>
+        <v>4.378626444160854</v>
       </c>
       <c r="F2" t="n">
-        <v>6.577490958908343</v>
+        <v>6.577490958908348</v>
       </c>
       <c r="G2" t="n">
-        <v>6.700368830114636</v>
+        <v>6.70036883011464</v>
       </c>
       <c r="H2" t="n">
-        <v>6.623399730500369</v>
+        <v>6.623399730500362</v>
       </c>
       <c r="I2" t="n">
-        <v>6.58808746055109</v>
+        <v>6.588087460551098</v>
       </c>
       <c r="J2" t="n">
-        <v>6.648536294777313</v>
+        <v>6.648536294777339</v>
       </c>
       <c r="K2" t="n">
-        <v>6.627818768255553</v>
+        <v>6.627818768255562</v>
       </c>
       <c r="L2" t="n">
-        <v>6.64792072359957</v>
+        <v>6.647920723599562</v>
       </c>
       <c r="M2" t="n">
-        <v>6.678996935342052</v>
+        <v>6.678996935342057</v>
       </c>
       <c r="N2" t="n">
-        <v>6.601834879676971</v>
+        <v>6.601834879676979</v>
       </c>
       <c r="O2" t="n">
-        <v>6.590849551634873</v>
+        <v>6.590849551634878</v>
       </c>
       <c r="P2" t="n">
-        <v>6.641518048645201</v>
+        <v>6.641518048645207</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.575137932545292</v>
+        <v>6.575137932545303</v>
       </c>
       <c r="R2" t="n">
-        <v>6.605356953597822</v>
+        <v>6.605356953597834</v>
       </c>
       <c r="S2" t="n">
-        <v>6.648763929751389</v>
+        <v>6.648763929751393</v>
       </c>
       <c r="T2" t="n">
-        <v>6.599272325496346</v>
+        <v>6.59927232549634</v>
       </c>
       <c r="U2" t="n">
-        <v>6.661274986456735</v>
+        <v>6.661274986456724</v>
       </c>
       <c r="V2" t="n">
-        <v>6.847969271445885</v>
+        <v>6.847969271445888</v>
       </c>
       <c r="W2" t="n">
-        <v>6.701131836128301</v>
+        <v>6.701131836128313</v>
       </c>
       <c r="X2" t="n">
-        <v>6.692170172303856</v>
+        <v>6.69217017230386</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.718695286005032</v>
+        <v>6.718695286005039</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.601665451916053</v>
+        <v>6.60166545191606</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.648622516475537</v>
+        <v>6.64862251647555</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.703116967323012</v>
+        <v>6.703116967323014</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="C3" t="n">
-        <v>12.88366941632306</v>
+        <v>12.88366941632307</v>
       </c>
       <c r="D3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="E3" t="n">
         <v>10.67979599504133</v>
       </c>
       <c r="F3" t="n">
-        <v>12.88400803864362</v>
+        <v>12.88400803864363</v>
       </c>
       <c r="G3" t="n">
-        <v>12.88436438345693</v>
+        <v>12.88436438345694</v>
       </c>
       <c r="H3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="I3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="J3" t="n">
-        <v>12.88265420525769</v>
+        <v>12.8826542052577</v>
       </c>
       <c r="K3" t="n">
-        <v>12.88430030234806</v>
+        <v>12.88430030234807</v>
       </c>
       <c r="L3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="M3" t="n">
-        <v>12.88292399934654</v>
+        <v>12.88292399934655</v>
       </c>
       <c r="N3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="O3" t="n">
-        <v>12.88379249074532</v>
+        <v>12.88379249074533</v>
       </c>
       <c r="P3" t="n">
-        <v>12.88300125252434</v>
+        <v>12.88300125252435</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.88467920507574</v>
+        <v>12.88467920507575</v>
       </c>
       <c r="R3" t="n">
-        <v>12.88687937392967</v>
+        <v>12.88687937392968</v>
       </c>
       <c r="S3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="T3" t="n">
-        <v>12.88339787805254</v>
+        <v>12.88339787805255</v>
       </c>
       <c r="U3" t="n">
-        <v>12.8877533058318</v>
+        <v>12.88775330583181</v>
       </c>
       <c r="V3" t="n">
         <v>13.1125487520498</v>
       </c>
       <c r="W3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="X3" t="n">
-        <v>12.88782255106386</v>
+        <v>12.88782255106387</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.88129044770097</v>
+        <v>12.88129044770098</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.88459918471089</v>
+        <v>12.8845991847109</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.88468916522562</v>
+        <v>12.88468916522563</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.89507060278768</v>
+        <v>12.89507060278769</v>
       </c>
     </row>
     <row r="4">
@@ -4912,61 +4912,61 @@
         <v>15.23686007335153</v>
       </c>
       <c r="D4" t="n">
-        <v>27.2112815591168</v>
+        <v>27.21128155911665</v>
       </c>
       <c r="E4" t="n">
-        <v>9.201152240249492</v>
+        <v>9.201152240249487</v>
       </c>
       <c r="F4" t="n">
-        <v>17.40559476767038</v>
+        <v>17.40559476767045</v>
       </c>
       <c r="G4" t="n">
-        <v>43.18461036888811</v>
+        <v>43.1846103688881</v>
       </c>
       <c r="H4" t="n">
-        <v>31.15207111040304</v>
+        <v>31.1520711104031</v>
       </c>
       <c r="I4" t="n">
-        <v>20.24912050044285</v>
+        <v>20.24912050044283</v>
       </c>
       <c r="J4" t="n">
-        <v>33.34869657613146</v>
+        <v>33.34869657613149</v>
       </c>
       <c r="K4" t="n">
-        <v>27.5774606647351</v>
+        <v>27.57746066473506</v>
       </c>
       <c r="L4" t="n">
-        <v>33.00787558207428</v>
+        <v>33.00787558207437</v>
       </c>
       <c r="M4" t="n">
-        <v>43.35924293516669</v>
+        <v>43.3592429351667</v>
       </c>
       <c r="N4" t="n">
-        <v>23.5689941612804</v>
+        <v>23.56899416128041</v>
       </c>
       <c r="O4" t="n">
-        <v>18.33970424845429</v>
+        <v>18.33970424845423</v>
       </c>
       <c r="P4" t="n">
-        <v>30.14495388793936</v>
+        <v>30.14495388793951</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.88814912587789</v>
+        <v>15.88814912587795</v>
       </c>
       <c r="R4" t="n">
-        <v>25.06817879857045</v>
+        <v>25.06817879857044</v>
       </c>
       <c r="S4" t="n">
-        <v>32.33741152993395</v>
+        <v>32.33741152993389</v>
       </c>
       <c r="T4" t="n">
-        <v>23.78254166855605</v>
+        <v>23.78254166855601</v>
       </c>
       <c r="U4" t="n">
-        <v>34.65598936104851</v>
+        <v>34.65598936104847</v>
       </c>
       <c r="V4" t="n">
-        <v>25.20998350927103</v>
+        <v>25.20998350927105</v>
       </c>
       <c r="W4" t="n">
         <v>48.36495585355667</v>
@@ -4975,16 +4975,16 @@
         <v>44.75338634475133</v>
       </c>
       <c r="Y4" t="n">
-        <v>54.09122663083387</v>
+        <v>54.09122663083384</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.47237731209158</v>
+        <v>19.47237731209157</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.17137038044014</v>
+        <v>35.17137038044017</v>
       </c>
       <c r="AB4" t="n">
-        <v>50.22293132902743</v>
+        <v>50.22293132902751</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7258754116112097</v>
+        <v>0.7258754116112253</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7241204449673467</v>
+        <v>0.7241204449673447</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7258754116112128</v>
+        <v>0.7258754116112255</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7052122534911551</v>
+        <v>0.7052122534911743</v>
       </c>
       <c r="V5" t="n">
-        <v>0.714295674660405</v>
+        <v>0.7142956746604027</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7258754116112318</v>
+        <v>0.725875411611223</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7052122534911551</v>
+        <v>0.7052122534911724</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7258754116112147</v>
+        <v>0.7258754116112254</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7258754116112306</v>
+        <v>0.725875411611223</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="C6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="D6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="E6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="H6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="I6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="J6" t="n">
-        <v>1.345473227355674</v>
+        <v>1.34547322735567</v>
       </c>
       <c r="K6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="M6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8924657923995228</v>
+        <v>0.8924657923995524</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8931048940012511</v>
+        <v>0.8931048940012912</v>
       </c>
       <c r="P6" t="n">
-        <v>1.375021814776545</v>
+        <v>1.375021814776561</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="R6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="S6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="T6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="U6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8742049815991161</v>
+        <v>0.8742049815991149</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9165771028192403</v>
+        <v>0.9165771028192413</v>
       </c>
       <c r="X6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9071176514663949</v>
+        <v>0.907117651466452</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.885784718549932</v>
+        <v>0.8857847185499389</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.347228193999557</v>
+        <v>1.347228193999549</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8983698622506395</v>
+        <v>0.89836986225065</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.310641902997822</v>
+        <v>1.310641902997836</v>
       </c>
       <c r="C7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="D7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="E7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="F7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="G7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="H7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="I7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="J7" t="n">
-        <v>1.308886936353958</v>
+        <v>1.308886936353954</v>
       </c>
       <c r="K7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="L7" t="n">
-        <v>1.310641902997822</v>
+        <v>1.310641902997836</v>
       </c>
       <c r="M7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="N7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="O7" t="n">
-        <v>1.308743652850266</v>
+        <v>1.308743652850275</v>
       </c>
       <c r="P7" t="n">
-        <v>1.308743652850266</v>
+        <v>1.308743652850275</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="R7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="S7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="T7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="U7" t="n">
-        <v>1.306480657769011</v>
+        <v>1.306480657769013</v>
       </c>
       <c r="V7" t="n">
-        <v>1.299062166047014</v>
+        <v>1.299062166047012</v>
       </c>
       <c r="W7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="X7" t="n">
-        <v>1.310641902997822</v>
+        <v>1.310641902997836</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.310641902997824</v>
+        <v>1.310641902997834</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.546754056371717</v>
+        <v>1.546754056371718</v>
       </c>
       <c r="C8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="D8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="E8" t="n">
-        <v>1.847731420139683</v>
+        <v>1.847731420139686</v>
       </c>
       <c r="F8" t="n">
-        <v>1.647044531810972</v>
+        <v>1.647044531810963</v>
       </c>
       <c r="G8" t="n">
-        <v>2.324003368301728</v>
+        <v>2.324003368301723</v>
       </c>
       <c r="H8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="I8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="J8" t="n">
-        <v>2.188760317406955</v>
+        <v>2.188760317406948</v>
       </c>
       <c r="K8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="L8" t="n">
-        <v>2.190515284050822</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="M8" t="n">
-        <v>2.190515284051995</v>
+        <v>2.190515284052003</v>
       </c>
       <c r="N8" t="n">
-        <v>1.69149263361222</v>
+        <v>1.691492633612211</v>
       </c>
       <c r="O8" t="n">
-        <v>1.828628390737055</v>
+        <v>1.828628390737057</v>
       </c>
       <c r="P8" t="n">
-        <v>1.795013103017054</v>
+        <v>1.795013103017058</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.420240282079336</v>
+        <v>1.420240282079331</v>
       </c>
       <c r="R8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="S8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="T8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87455025518742</v>
+        <v>1.874550255187411</v>
       </c>
       <c r="V8" t="n">
-        <v>2.001051544480336</v>
+        <v>2.001051544480333</v>
       </c>
       <c r="W8" t="n">
-        <v>2.190641801273071</v>
+        <v>2.190641801273081</v>
       </c>
       <c r="X8" t="n">
-        <v>1.479242277582759</v>
+        <v>1.47924227758277</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.827592236949084</v>
+        <v>2.827592236949077</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.534795861084588</v>
+        <v>1.534795861084591</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.190515284050821</v>
+        <v>2.19051528405083</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.862977716521174</v>
+        <v>2.862977716521165</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.651038226097248</v>
+        <v>2.651038226097268</v>
       </c>
       <c r="C9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="D9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="E9" t="n">
-        <v>3.101480102267701</v>
+        <v>3.101480102267702</v>
       </c>
       <c r="F9" t="n">
-        <v>1.886677243410664</v>
+        <v>1.886677243410661</v>
       </c>
       <c r="G9" t="n">
-        <v>3.236632983732372</v>
+        <v>3.236632983732361</v>
       </c>
       <c r="H9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="I9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="J9" t="n">
-        <v>3.234877862738856</v>
+        <v>3.234877862738864</v>
       </c>
       <c r="K9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="L9" t="n">
-        <v>3.236632829382734</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="M9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="N9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="O9" t="n">
-        <v>3.430698319641785</v>
+        <v>3.430698319641786</v>
       </c>
       <c r="P9" t="n">
-        <v>3.472904200601644</v>
+        <v>3.472904200601643</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.236632983732372</v>
+        <v>3.236632983732361</v>
       </c>
       <c r="R9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="S9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="T9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="U9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="V9" t="n">
-        <v>3.900816282132646</v>
+        <v>3.900816282132644</v>
       </c>
       <c r="W9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="X9" t="n">
-        <v>3.236632829382734</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.883571417996015</v>
+        <v>2.88357141799601</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.236632829382735</v>
+        <v>3.23663282938274</v>
       </c>
     </row>
     <row r="10">
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.39290900225579</v>
+        <v>12.3929090022558</v>
       </c>
       <c r="C10" t="n">
-        <v>12.53767793025691</v>
+        <v>12.53767793025692</v>
       </c>
       <c r="D10" t="n">
         <v>12.2685584973583</v>
@@ -5446,73 +5446,73 @@
         <v>10.47034345598425</v>
       </c>
       <c r="F10" t="n">
-        <v>12.5083442473342</v>
+        <v>12.50834424733421</v>
       </c>
       <c r="G10" t="n">
-        <v>11.77247133759648</v>
+        <v>11.77247133759649</v>
       </c>
       <c r="H10" t="n">
-        <v>12.24625322244456</v>
+        <v>12.24625322244457</v>
       </c>
       <c r="I10" t="n">
-        <v>12.44957350291227</v>
+        <v>12.44957350291229</v>
       </c>
       <c r="J10" t="n">
-        <v>12.0736995415954</v>
+        <v>12.07369954159541</v>
       </c>
       <c r="K10" t="n">
         <v>12.21260639350296</v>
       </c>
       <c r="L10" t="n">
-        <v>12.09098284292469</v>
+        <v>12.0909828429247</v>
       </c>
       <c r="M10" t="n">
-        <v>11.9087511222989</v>
+        <v>11.90875112229891</v>
       </c>
       <c r="N10" t="n">
-        <v>12.36604205833486</v>
+        <v>12.36604205833487</v>
       </c>
       <c r="O10" t="n">
-        <v>12.41921443233219</v>
+        <v>12.4192144323322</v>
       </c>
       <c r="P10" t="n">
         <v>12.111667801042</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52362228027097</v>
+        <v>12.52362228027098</v>
       </c>
       <c r="R10" t="n">
-        <v>12.36358639487692</v>
+        <v>12.36358639487693</v>
       </c>
       <c r="S10" t="n">
-        <v>12.08343318119305</v>
+        <v>12.08343318119307</v>
       </c>
       <c r="T10" t="n">
-        <v>12.37536040424917</v>
+        <v>12.37536040424918</v>
       </c>
       <c r="U10" t="n">
-        <v>12.03079701041895</v>
+        <v>12.03079701041896</v>
       </c>
       <c r="V10" t="n">
         <v>12.45855594753256</v>
       </c>
       <c r="W10" t="n">
-        <v>11.77825768591466</v>
+        <v>11.77825768591467</v>
       </c>
       <c r="X10" t="n">
-        <v>11.8580033053944</v>
+        <v>11.85800330539441</v>
       </c>
       <c r="Y10" t="n">
         <v>11.65485426750065</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.36114859077075</v>
+        <v>12.36114859077076</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.08881443286368</v>
+        <v>12.08881443286369</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.84115863708427</v>
+        <v>11.84115863708428</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.372564915236239</v>
+        <v>6.372564915236254</v>
       </c>
       <c r="C11" t="n">
-        <v>6.414304937213775</v>
+        <v>6.414304937213785</v>
       </c>
       <c r="D11" t="n">
-        <v>6.338509443194346</v>
+        <v>6.338509443194356</v>
       </c>
       <c r="E11" t="n">
         <v>4.283324871404241</v>
       </c>
       <c r="F11" t="n">
-        <v>6.406562736693088</v>
+        <v>6.406562736693078</v>
       </c>
       <c r="G11" t="n">
-        <v>6.194453950855237</v>
+        <v>6.194453950855244</v>
       </c>
       <c r="H11" t="n">
-        <v>6.332909341960355</v>
+        <v>6.33290934196035</v>
       </c>
       <c r="I11" t="n">
-        <v>6.390108447567173</v>
+        <v>6.390108447567183</v>
       </c>
       <c r="J11" t="n">
-        <v>6.280459344825416</v>
+        <v>6.280459344825445</v>
       </c>
       <c r="K11" t="n">
-        <v>6.322195899169556</v>
+        <v>6.322195899169561</v>
       </c>
       <c r="L11" t="n">
-        <v>6.286781817560681</v>
+        <v>6.286781817560672</v>
       </c>
       <c r="M11" t="n">
-        <v>6.235745171780618</v>
+        <v>6.235745171780623</v>
       </c>
       <c r="N11" t="n">
-        <v>6.365848793211412</v>
+        <v>6.365848793211421</v>
       </c>
       <c r="O11" t="n">
-        <v>6.379465054534468</v>
+        <v>6.379465054534481</v>
       </c>
       <c r="P11" t="n">
-        <v>6.290558870126865</v>
+        <v>6.290558870126879</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.410855881138974</v>
+        <v>6.410855881138981</v>
       </c>
       <c r="R11" t="n">
-        <v>6.367256980493042</v>
+        <v>6.367256980493051</v>
       </c>
       <c r="S11" t="n">
-        <v>6.284189903565263</v>
+        <v>6.284189903565271</v>
       </c>
       <c r="T11" t="n">
-        <v>6.36811365589644</v>
+        <v>6.368113655896449</v>
       </c>
       <c r="U11" t="n">
-        <v>6.271357141086209</v>
+        <v>6.271357141086205</v>
       </c>
       <c r="V11" t="n">
-        <v>6.550400461239136</v>
+        <v>6.550400461239138</v>
       </c>
       <c r="W11" t="n">
-        <v>6.197701987053902</v>
+        <v>6.197701987053921</v>
       </c>
       <c r="X11" t="n">
-        <v>6.223599133685035</v>
+        <v>6.22359913368504</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.160662915593672</v>
+        <v>6.160662915593687</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.363493763535215</v>
+        <v>6.36349376353523</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.286496976948579</v>
+        <v>6.286496976948588</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.223583664309799</v>
+        <v>6.223583664309809</v>
       </c>
     </row>
   </sheetData>
@@ -5766,85 +5766,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.395927924062299</v>
+        <v>6.395927924062295</v>
       </c>
       <c r="C2" t="n">
-        <v>6.399434142393853</v>
+        <v>6.399434142393852</v>
       </c>
       <c r="D2" t="n">
-        <v>6.420963942976591</v>
+        <v>6.420963942976585</v>
       </c>
       <c r="E2" t="n">
-        <v>4.269045744120932</v>
+        <v>4.269045744120927</v>
       </c>
       <c r="F2" t="n">
-        <v>6.385628709067801</v>
+        <v>6.385628709067789</v>
       </c>
       <c r="G2" t="n">
-        <v>6.444941453402353</v>
+        <v>6.444941453402342</v>
       </c>
       <c r="H2" t="n">
-        <v>6.412112864948399</v>
+        <v>6.412112864948392</v>
       </c>
       <c r="I2" t="n">
-        <v>6.408081867116492</v>
+        <v>6.408081867116479</v>
       </c>
       <c r="J2" t="n">
-        <v>6.423339012894782</v>
+        <v>6.423339012894774</v>
       </c>
       <c r="K2" t="n">
-        <v>6.425582467662346</v>
+        <v>6.425582467662335</v>
       </c>
       <c r="L2" t="n">
-        <v>6.395650685744487</v>
+        <v>6.395650685744478</v>
       </c>
       <c r="M2" t="n">
-        <v>6.443225911987397</v>
+        <v>6.443225911987388</v>
       </c>
       <c r="N2" t="n">
-        <v>6.409180810467869</v>
+        <v>6.409180810467859</v>
       </c>
       <c r="O2" t="n">
-        <v>6.392087469009142</v>
+        <v>6.392087469009133</v>
       </c>
       <c r="P2" t="n">
-        <v>6.397073345479948</v>
+        <v>6.39707334547994</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.395795334023428</v>
+        <v>6.395795334023417</v>
       </c>
       <c r="R2" t="n">
-        <v>6.343796714397777</v>
+        <v>6.34379671439777</v>
       </c>
       <c r="S2" t="n">
-        <v>6.415787896833627</v>
+        <v>6.415787896833616</v>
       </c>
       <c r="T2" t="n">
-        <v>6.395624510370304</v>
+        <v>6.395624510370292</v>
       </c>
       <c r="U2" t="n">
-        <v>6.463502643323165</v>
+        <v>6.463502643323157</v>
       </c>
       <c r="V2" t="n">
-        <v>6.597139911777487</v>
+        <v>6.597139911777485</v>
       </c>
       <c r="W2" t="n">
-        <v>6.554196406118434</v>
+        <v>6.554196406118431</v>
       </c>
       <c r="X2" t="n">
-        <v>6.45306327146133</v>
+        <v>6.453063271461321</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.410220803131383</v>
+        <v>6.410220803131375</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.399355918390306</v>
+        <v>6.399355918390297</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.46653679441181</v>
+        <v>6.466536794411801</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.4445150567257</v>
+        <v>6.444515056725694</v>
       </c>
     </row>
     <row r="3">
@@ -5908,13 +5908,13 @@
         <v>12.74842598235482</v>
       </c>
       <c r="T3" t="n">
-        <v>12.74812066661294</v>
+        <v>12.74812066661293</v>
       </c>
       <c r="U3" t="n">
-        <v>12.74911535632994</v>
+        <v>12.74911535632993</v>
       </c>
       <c r="V3" t="n">
-        <v>12.95299548618227</v>
+        <v>12.95299548618226</v>
       </c>
       <c r="W3" t="n">
         <v>12.74842598235482</v>
@@ -5923,7 +5923,7 @@
         <v>12.74899858171324</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.7468143371662</v>
+        <v>12.74681433716619</v>
       </c>
       <c r="Z3" t="n">
         <v>12.74837159547995</v>
@@ -5932,7 +5932,7 @@
         <v>12.74842598235482</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.75880741991689</v>
+        <v>12.75880741991688</v>
       </c>
     </row>
     <row r="4">
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.949917358649642</v>
+        <v>4.949917358649654</v>
       </c>
       <c r="C4" t="n">
-        <v>6.569334620197953</v>
+        <v>6.569334620197948</v>
       </c>
       <c r="D4" t="n">
-        <v>12.4999950003239</v>
+        <v>12.49999500032388</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8509913251991312</v>
+        <v>0.8509913251991272</v>
       </c>
       <c r="F4" t="n">
-        <v>2.721229797168055</v>
+        <v>2.721229797168038</v>
       </c>
       <c r="G4" t="n">
-        <v>16.11302201561399</v>
+        <v>16.11302201561404</v>
       </c>
       <c r="H4" t="n">
-        <v>10.47363728803878</v>
+        <v>10.47363728803877</v>
       </c>
       <c r="I4" t="n">
-        <v>9.012642334139187</v>
+        <v>9.012642334139194</v>
       </c>
       <c r="J4" t="n">
-        <v>12.20005176912783</v>
+        <v>12.20005176912786</v>
       </c>
       <c r="K4" t="n">
         <v>12.69790100443196</v>
       </c>
       <c r="L4" t="n">
-        <v>4.841137231711455</v>
+        <v>4.841137231711486</v>
       </c>
       <c r="M4" t="n">
         <v>17.37545692187287</v>
       </c>
       <c r="N4" t="n">
-        <v>8.826612841522879</v>
+        <v>8.826612841522941</v>
       </c>
       <c r="O4" t="n">
-        <v>4.100496025130144</v>
+        <v>4.100496025130107</v>
       </c>
       <c r="P4" t="n">
-        <v>5.351331628488274</v>
+        <v>5.351331628488306</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.201776336642007</v>
+        <v>5.201776336641981</v>
       </c>
       <c r="R4" t="n">
-        <v>-9.504462300867377</v>
+        <v>-9.504462300867331</v>
       </c>
       <c r="S4" t="n">
-        <v>9.009942496870035</v>
+        <v>9.009942496870067</v>
       </c>
       <c r="T4" t="n">
-        <v>5.360305045769336</v>
+        <v>5.360305045769346</v>
       </c>
       <c r="U4" t="n">
-        <v>22.26289195850283</v>
+        <v>22.26289195850275</v>
       </c>
       <c r="V4" t="n">
-        <v>4.902364147361292</v>
+        <v>4.90236414736128</v>
       </c>
       <c r="W4" t="n">
-        <v>48.38673782934029</v>
+        <v>48.38673782934038</v>
       </c>
       <c r="X4" t="n">
-        <v>21.05533275934471</v>
+        <v>21.05533275934472</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.519228632709105</v>
+        <v>9.519228632709067</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.692101319537284</v>
+        <v>5.692101319537275</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.4687802072451</v>
+        <v>24.46878020724507</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.80887866722529</v>
+        <v>16.8088786672253</v>
       </c>
     </row>
     <row r="5">
@@ -6030,85 +6030,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="J5" t="n">
-        <v>0.591355320609905</v>
+        <v>0.5913553206099028</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5643994835713396</v>
+        <v>0.5643994835713237</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5818289883642034</v>
+        <v>0.5818289883642038</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5643994835713396</v>
+        <v>0.5643994835713237</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5930537450806793</v>
+        <v>0.593053745080675</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5930537450806728</v>
+        <v>0.5930537450806785</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="D6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="E6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="H6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="I6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6777655829009939</v>
+        <v>0.6777655829009919</v>
       </c>
       <c r="K6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="M6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="N6" t="n">
-        <v>0.68085114656309</v>
+        <v>0.6808511465631056</v>
       </c>
       <c r="O6" t="n">
-        <v>1.041900119091942</v>
+        <v>1.041900119091934</v>
       </c>
       <c r="P6" t="n">
         <v>1.041588787739655</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="R6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9971725211549652</v>
+        <v>0.997172521154967</v>
       </c>
       <c r="W6" t="n">
-        <v>1.042002730182497</v>
+        <v>1.042002730182494</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6927160688083162</v>
+        <v>0.6927160688083448</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6794640073717765</v>
+        <v>0.6794640073717668</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.008397277871448</v>
+        <v>1.00839727787144</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6852472560845584</v>
+        <v>0.6852472560845507</v>
       </c>
     </row>
     <row r="7">
@@ -6206,85 +6206,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="C7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="D7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="E7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="F7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="G7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="H7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="I7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="J7" t="n">
-        <v>1.104122853362642</v>
+        <v>1.104122853362645</v>
       </c>
       <c r="K7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="L7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="M7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="N7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="O7" t="n">
-        <v>1.103789454688766</v>
+        <v>1.103789454688769</v>
       </c>
       <c r="P7" t="n">
-        <v>1.103789454688766</v>
+        <v>1.103789454688769</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="R7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="S7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="T7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="U7" t="n">
-        <v>1.09941267959367</v>
+        <v>1.099412679593669</v>
       </c>
       <c r="V7" t="n">
         <v>1.094596521116944</v>
       </c>
       <c r="W7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="X7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.105821277833418</v>
+        <v>1.10582127783342</v>
       </c>
     </row>
     <row r="8">
@@ -6294,85 +6294,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.263964766246354</v>
+        <v>1.263964766246349</v>
       </c>
       <c r="C8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="D8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="E8" t="n">
-        <v>1.51291689225412</v>
+        <v>1.512916892254113</v>
       </c>
       <c r="F8" t="n">
-        <v>1.346919599688</v>
+        <v>1.346919599687992</v>
       </c>
       <c r="G8" t="n">
-        <v>1.906863176389743</v>
+        <v>1.906863176389732</v>
       </c>
       <c r="H8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="I8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="J8" t="n">
-        <v>1.79475065978567</v>
+        <v>1.794750659785671</v>
       </c>
       <c r="K8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="L8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="M8" t="n">
-        <v>1.796449084257497</v>
+        <v>1.796449084257494</v>
       </c>
       <c r="N8" t="n">
-        <v>1.383684655052046</v>
+        <v>1.383684655052027</v>
       </c>
       <c r="O8" t="n">
-        <v>1.497115904067843</v>
+        <v>1.497115904067841</v>
       </c>
       <c r="P8" t="n">
-        <v>1.469311164061377</v>
+        <v>1.469311164061371</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.159319444443007</v>
+        <v>1.159319444442994</v>
       </c>
       <c r="R8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="S8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="T8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="U8" t="n">
-        <v>1.533158702243316</v>
+        <v>1.533158702243317</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63594717541669</v>
+        <v>1.635947175416695</v>
       </c>
       <c r="W8" t="n">
-        <v>1.796553732475512</v>
+        <v>1.796553732475505</v>
       </c>
       <c r="X8" t="n">
-        <v>1.208122690125217</v>
+        <v>1.208122690125207</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.320083578978271</v>
+        <v>2.320083578978272</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.254073596672243</v>
+        <v>1.254073596672246</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.796449084256448</v>
+        <v>1.796449084256447</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.352673479853832</v>
+        <v>2.352673479853822</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.241975873759177</v>
+        <v>2.241975873759164</v>
       </c>
       <c r="C9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="D9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="E9" t="n">
-        <v>2.628300646110279</v>
+        <v>2.628300646110274</v>
       </c>
       <c r="F9" t="n">
-        <v>1.586416081803396</v>
+        <v>1.586416081803379</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74421550422326</v>
+        <v>2.744215504223258</v>
       </c>
       <c r="H9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="I9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="J9" t="n">
-        <v>2.742517013407418</v>
+        <v>2.742517013407411</v>
       </c>
       <c r="K9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="L9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="M9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="N9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="O9" t="n">
-        <v>2.910657060132398</v>
+        <v>2.910657060132378</v>
       </c>
       <c r="P9" t="n">
-        <v>2.946855242886437</v>
+        <v>2.946855242886431</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74421550422326</v>
+        <v>2.744215504223258</v>
       </c>
       <c r="R9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="S9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="T9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="U9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="V9" t="n">
-        <v>3.312564109415889</v>
+        <v>3.312564109415886</v>
       </c>
       <c r="W9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="X9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.441409667943889</v>
+        <v>2.441409667943886</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.744215437878196</v>
+        <v>2.744215437878188</v>
       </c>
     </row>
     <row r="10">
@@ -6473,7 +6473,7 @@
         <v>12.64467090812248</v>
       </c>
       <c r="C10" t="n">
-        <v>12.6194001681807</v>
+        <v>12.61940016818069</v>
       </c>
       <c r="D10" t="n">
         <v>12.49963047848354</v>
@@ -6482,10 +6482,10 @@
         <v>10.60000930581777</v>
       </c>
       <c r="F10" t="n">
-        <v>12.70451488620366</v>
+        <v>12.70451488620365</v>
       </c>
       <c r="G10" t="n">
-        <v>12.35258197107829</v>
+        <v>12.35258197107828</v>
       </c>
       <c r="H10" t="n">
         <v>12.55280897536936</v>
@@ -6494,7 +6494,7 @@
         <v>12.57541340344407</v>
       </c>
       <c r="J10" t="n">
-        <v>12.47035390863516</v>
+        <v>12.47035390863515</v>
       </c>
       <c r="K10" t="n">
         <v>12.47082513439931</v>
@@ -6506,7 +6506,7 @@
         <v>12.36907755016685</v>
       </c>
       <c r="N10" t="n">
-        <v>12.56788710437138</v>
+        <v>12.56788710437137</v>
       </c>
       <c r="O10" t="n">
         <v>12.66290757112667</v>
@@ -6521,10 +6521,10 @@
         <v>12.95059165045601</v>
       </c>
       <c r="S10" t="n">
-        <v>12.52720772810205</v>
+        <v>12.52720772810204</v>
       </c>
       <c r="T10" t="n">
-        <v>12.64618262695275</v>
+        <v>12.64618262695274</v>
       </c>
       <c r="U10" t="n">
         <v>12.24975039999241</v>
@@ -6536,10 +6536,10 @@
         <v>11.71140281878951</v>
       </c>
       <c r="X10" t="n">
-        <v>12.3148271757314</v>
+        <v>12.31482717573139</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.55115696889876</v>
+        <v>12.55115696889875</v>
       </c>
       <c r="Z10" t="n">
         <v>12.62406576613879</v>
@@ -6558,85 +6558,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.348719034638786</v>
+        <v>6.348719034638781</v>
       </c>
       <c r="C11" t="n">
-        <v>6.341170527019875</v>
+        <v>6.341170527019866</v>
       </c>
       <c r="D11" t="n">
-        <v>6.307761195850926</v>
+        <v>6.307761195850919</v>
       </c>
       <c r="E11" t="n">
-        <v>4.266909394425974</v>
+        <v>4.266909394425968</v>
       </c>
       <c r="F11" t="n">
-        <v>6.365814457416363</v>
+        <v>6.36581445741636</v>
       </c>
       <c r="G11" t="n">
-        <v>6.264882028762962</v>
+        <v>6.264882028762953</v>
       </c>
       <c r="H11" t="n">
-        <v>6.323106503375603</v>
+        <v>6.323106503375599</v>
       </c>
       <c r="I11" t="n">
-        <v>6.329360592353723</v>
+        <v>6.329360592353712</v>
       </c>
       <c r="J11" t="n">
-        <v>6.297652969855354</v>
+        <v>6.297652969855347</v>
       </c>
       <c r="K11" t="n">
-        <v>6.299370500834186</v>
+        <v>6.299370500834178</v>
       </c>
       <c r="L11" t="n">
-        <v>6.34948575935989</v>
+        <v>6.349485759359879</v>
       </c>
       <c r="M11" t="n">
-        <v>6.270735725948232</v>
+        <v>6.270735725948224</v>
       </c>
       <c r="N11" t="n">
-        <v>6.327035045642129</v>
+        <v>6.327035045642122</v>
       </c>
       <c r="O11" t="n">
-        <v>6.353495689480029</v>
+        <v>6.35349568948002</v>
       </c>
       <c r="P11" t="n">
-        <v>6.34622833101823</v>
+        <v>6.346228331018227</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.349528778862004</v>
+        <v>6.349528778861993</v>
       </c>
       <c r="R11" t="n">
-        <v>6.435800725629731</v>
+        <v>6.435800725629724</v>
       </c>
       <c r="S11" t="n">
-        <v>6.315132886167857</v>
+        <v>6.315132886167855</v>
       </c>
       <c r="T11" t="n">
-        <v>6.349242377467662</v>
+        <v>6.349242377467655</v>
       </c>
       <c r="U11" t="n">
-        <v>6.236289996807896</v>
+        <v>6.236289996807893</v>
       </c>
       <c r="V11" t="n">
-        <v>6.550202059072914</v>
+        <v>6.550202059072916</v>
       </c>
       <c r="W11" t="n">
-        <v>6.082347561899481</v>
+        <v>6.082347561899478</v>
       </c>
       <c r="X11" t="n">
-        <v>6.255513898117413</v>
+        <v>6.255513898117403</v>
       </c>
       <c r="Y11" t="n">
         <v>6.321196077046651</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.34279636990091</v>
+        <v>6.3427963699009</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.230283064513625</v>
+        <v>6.230283064513623</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.293862568743333</v>
+        <v>6.293862568743327</v>
       </c>
     </row>
   </sheetData>
@@ -6805,73 +6805,73 @@
         <v>6.268215581471378</v>
       </c>
       <c r="C2" t="n">
-        <v>6.31460570124624</v>
+        <v>6.314605701246243</v>
       </c>
       <c r="D2" t="n">
-        <v>6.317626518375632</v>
+        <v>6.317626518375633</v>
       </c>
       <c r="E2" t="n">
         <v>4.133703992638577</v>
       </c>
       <c r="F2" t="n">
-        <v>6.252122884187172</v>
+        <v>6.252122884187175</v>
       </c>
       <c r="G2" t="n">
-        <v>6.345280553572717</v>
+        <v>6.345280553572714</v>
       </c>
       <c r="H2" t="n">
-        <v>6.317996897170739</v>
+        <v>6.31799689717074</v>
       </c>
       <c r="I2" t="n">
-        <v>6.303602304386618</v>
+        <v>6.303602304386621</v>
       </c>
       <c r="J2" t="n">
-        <v>6.319691715731619</v>
+        <v>6.319691715731618</v>
       </c>
       <c r="K2" t="n">
-        <v>6.300386693834636</v>
+        <v>6.300386693834639</v>
       </c>
       <c r="L2" t="n">
-        <v>6.237339281611789</v>
+        <v>6.237339281611791</v>
       </c>
       <c r="M2" t="n">
-        <v>6.302850725837533</v>
+        <v>6.302850725837529</v>
       </c>
       <c r="N2" t="n">
         <v>6.334606236649558</v>
       </c>
       <c r="O2" t="n">
-        <v>6.304506100184568</v>
+        <v>6.304506100184567</v>
       </c>
       <c r="P2" t="n">
-        <v>6.268642756132894</v>
+        <v>6.268642756132897</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.309625682929781</v>
+        <v>6.30962568292978</v>
       </c>
       <c r="R2" t="n">
-        <v>6.171627221672797</v>
+        <v>6.171627221672793</v>
       </c>
       <c r="S2" t="n">
         <v>6.295805270174228</v>
       </c>
       <c r="T2" t="n">
-        <v>6.285278695688263</v>
+        <v>6.285278695688267</v>
       </c>
       <c r="U2" t="n">
-        <v>6.314961923209829</v>
+        <v>6.314961923209827</v>
       </c>
       <c r="V2" t="n">
-        <v>6.529803224771103</v>
+        <v>6.529803224771109</v>
       </c>
       <c r="W2" t="n">
-        <v>6.400258238494637</v>
+        <v>6.400258238494634</v>
       </c>
       <c r="X2" t="n">
-        <v>6.478749660843604</v>
+        <v>6.478749660843606</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.355353071739655</v>
+        <v>6.355353071739657</v>
       </c>
       <c r="Z2" t="n">
         <v>6.312306116184629</v>
@@ -6880,7 +6880,7 @@
         <v>6.431631706768065</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.314904654582878</v>
+        <v>6.314904654582875</v>
       </c>
     </row>
     <row r="3">
@@ -6914,7 +6914,7 @@
         <v>12.67356072886218</v>
       </c>
       <c r="J3" t="n">
-        <v>12.67281883926292</v>
+        <v>12.67281883926293</v>
       </c>
       <c r="K3" t="n">
         <v>12.67325739394734</v>
@@ -6944,7 +6944,7 @@
         <v>12.67356072886218</v>
       </c>
       <c r="T3" t="n">
-        <v>12.67266157680923</v>
+        <v>12.67266157680922</v>
       </c>
       <c r="U3" t="n">
         <v>12.67463847789466</v>
@@ -6956,13 +6956,13 @@
         <v>12.67356072886218</v>
       </c>
       <c r="X3" t="n">
-        <v>12.68039547160671</v>
+        <v>12.6803954716067</v>
       </c>
       <c r="Y3" t="n">
         <v>12.67162359581365</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.6734692796547</v>
+        <v>12.67346927965469</v>
       </c>
       <c r="AA3" t="n">
         <v>12.67356072886218</v>
@@ -6978,85 +6978,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-7.896554697736203</v>
+        <v>-7.896554697736227</v>
       </c>
       <c r="C4" t="n">
-        <v>3.344880659684907</v>
+        <v>3.344880659684916</v>
       </c>
       <c r="D4" t="n">
-        <v>3.859189808433794</v>
+        <v>3.859189808433795</v>
       </c>
       <c r="E4" t="n">
         <v>-16.06723443974459</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.37659226511768</v>
+        <v>-12.37659226511763</v>
       </c>
       <c r="G4" t="n">
-        <v>9.233314986528358</v>
+        <v>9.233314986528379</v>
       </c>
       <c r="H4" t="n">
-        <v>4.240153682492304</v>
+        <v>4.240153682492313</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3956272253596724</v>
+        <v>0.3956272253596707</v>
       </c>
       <c r="J4" t="n">
-        <v>4.145796182167856</v>
+        <v>4.145796182167872</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1443744198251333</v>
+        <v>-0.1443744198251316</v>
       </c>
       <c r="L4" t="n">
-        <v>-12.33792481889247</v>
+        <v>-12.33792481889246</v>
       </c>
       <c r="M4" t="n">
-        <v>0.579059425884185</v>
+        <v>0.5790594258841921</v>
       </c>
       <c r="N4" t="n">
-        <v>7.935130176629051</v>
+        <v>7.935130176629059</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8165038919510675</v>
+        <v>0.8165038919510619</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.689034030633171</v>
+        <v>-7.689034030633208</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.815776401606333</v>
+        <v>1.815776401606331</v>
       </c>
       <c r="R4" t="n">
-        <v>-34.4760144987462</v>
+        <v>-34.47601449874624</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.121385937077449</v>
+        <v>-1.121385937077455</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.776447153643761</v>
+        <v>-3.776447153643763</v>
       </c>
       <c r="U4" t="n">
-        <v>2.73665384486496</v>
+        <v>2.736653844864967</v>
       </c>
       <c r="V4" t="n">
-        <v>4.26908607521817</v>
+        <v>4.269086075218176</v>
       </c>
       <c r="W4" t="n">
-        <v>23.32882988697187</v>
+        <v>23.32882988697183</v>
       </c>
       <c r="X4" t="n">
-        <v>41.14077830318627</v>
+        <v>41.14077830318623</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.88230796798189</v>
+        <v>13.8823079679819</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.376175838992257</v>
+        <v>2.376175838992252</v>
       </c>
       <c r="AA4" t="n">
-        <v>32.66467278415319</v>
+        <v>32.66467278415318</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8868079469252813</v>
+        <v>0.8868079469252762</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5279827888024153</v>
+        <v>0.5279827888024164</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5265119885597165</v>
+        <v>0.5265119885597193</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="U5" t="n">
-        <v>0.500716716387513</v>
+        <v>0.5007167163875107</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5181900017175771</v>
+        <v>0.5181900017175772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.500716716387513</v>
+        <v>0.5007167163875107</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5279827888024152</v>
+        <v>0.5279827888024162</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5279827888024234</v>
+        <v>0.5279827888024141</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="F6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="H6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="I6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8195078399983827</v>
+        <v>0.8195078399983785</v>
       </c>
       <c r="K6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="M6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5708834477880163</v>
+        <v>0.5708834477880178</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8494532192602461</v>
+        <v>0.8494532192602543</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5620018544498867</v>
+        <v>0.5620018544498839</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="S6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5556829084842693</v>
+        <v>0.5556829084842698</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5887870587651349</v>
+        <v>0.5887870587651323</v>
       </c>
       <c r="X6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5799292496097476</v>
+        <v>0.5799292496097572</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5654756955691072</v>
+        <v>0.5654756955691139</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.820978640241086</v>
+        <v>0.820978640241082</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5724850459807775</v>
+        <v>0.5724850459807761</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="C7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="D7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="E7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="F7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="G7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="H7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="I7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9516089414443919</v>
+        <v>0.95160894144439</v>
       </c>
       <c r="K7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="L7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="M7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="N7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9511870666198627</v>
+        <v>0.9511870666198708</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9511870666198627</v>
+        <v>0.9511870666198708</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="R7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="S7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="T7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="U7" t="n">
-        <v>0.945548894420509</v>
+        <v>0.9455488944205106</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9432869546022477</v>
+        <v>0.9432869546022478</v>
       </c>
       <c r="W7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="X7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.953079741687089</v>
+        <v>0.9530797416870896</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.041188329972799</v>
+        <v>1.041188329972801</v>
       </c>
       <c r="C8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="D8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="E8" t="n">
-        <v>1.230572511586505</v>
+        <v>1.230572511586509</v>
       </c>
       <c r="F8" t="n">
-        <v>1.104294170860486</v>
+        <v>1.104294170860483</v>
       </c>
       <c r="G8" t="n">
-        <v>1.530257418281955</v>
+        <v>1.530257418281953</v>
       </c>
       <c r="H8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="I8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="J8" t="n">
-        <v>1.444791824253611</v>
+        <v>1.444791824253605</v>
       </c>
       <c r="K8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="L8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="M8" t="n">
-        <v>1.446262624495868</v>
+        <v>1.446262624495866</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1322622788005</v>
+        <v>1.132262278800497</v>
       </c>
       <c r="O8" t="n">
-        <v>1.218552300256536</v>
+        <v>1.218552300256544</v>
       </c>
       <c r="P8" t="n">
-        <v>1.197400530933887</v>
+        <v>1.197400530933888</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9615819857027642</v>
+        <v>0.9615819857027664</v>
       </c>
       <c r="R8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="S8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="U8" t="n">
-        <v>1.244181822800762</v>
+        <v>1.244181822800761</v>
       </c>
       <c r="V8" t="n">
-        <v>1.320937554966334</v>
+        <v>1.320937554966335</v>
       </c>
       <c r="W8" t="n">
-        <v>1.446342233273362</v>
+        <v>1.446342233273356</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9987078497359847</v>
+        <v>0.998707849735976</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.841543926283303</v>
+        <v>1.841543926283307</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.033663866973945</v>
+        <v>1.03366386697394</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.446262624496312</v>
+        <v>1.446262624496313</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.869396596968833</v>
+        <v>1.869396596968835</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.796027294835066</v>
+        <v>1.796027294835064</v>
       </c>
       <c r="C9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="D9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="E9" t="n">
-        <v>2.092220536961552</v>
+        <v>2.092220536961554</v>
       </c>
       <c r="F9" t="n">
         <v>1.293412929710496</v>
       </c>
       <c r="G9" t="n">
-        <v>2.181091870337809</v>
+        <v>2.181091870337807</v>
       </c>
       <c r="H9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="I9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="J9" t="n">
-        <v>2.179620964406519</v>
+        <v>2.179620964406527</v>
       </c>
       <c r="K9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="L9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="M9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="N9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="O9" t="n">
-        <v>2.308701766460362</v>
+        <v>2.308701766460366</v>
       </c>
       <c r="P9" t="n">
-        <v>2.336454729449915</v>
+        <v>2.336454729449919</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.181091870337809</v>
+        <v>2.181091870337807</v>
       </c>
       <c r="R9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="S9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="T9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="U9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="V9" t="n">
-        <v>2.615655229317218</v>
+        <v>2.615655229317223</v>
       </c>
       <c r="W9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="X9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.948932172587695</v>
+        <v>1.948932172587698</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.181091764649232</v>
+        <v>2.181091764649228</v>
       </c>
     </row>
     <row r="10">
@@ -7509,7 +7509,7 @@
         <v>12.88874175186207</v>
       </c>
       <c r="C10" t="n">
-        <v>12.60712545109114</v>
+        <v>12.60712545109115</v>
       </c>
       <c r="D10" t="n">
         <v>12.59601104926508</v>
@@ -7551,7 +7551,7 @@
         <v>12.88604834141862</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.6427326182315</v>
+        <v>12.64273261823149</v>
       </c>
       <c r="R10" t="n">
         <v>13.4553389588519</v>
@@ -7578,7 +7578,7 @@
         <v>12.3608753150475</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.62590441582959</v>
+        <v>12.62590441582958</v>
       </c>
       <c r="AA10" t="n">
         <v>11.9231728126936</v>
@@ -7594,85 +7594,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.366123632677557</v>
+        <v>6.366123632677554</v>
       </c>
       <c r="C11" t="n">
-        <v>6.284843249034589</v>
+        <v>6.284843249034592</v>
       </c>
       <c r="D11" t="n">
-        <v>6.282341167022783</v>
+        <v>6.282341167022785</v>
       </c>
       <c r="E11" t="n">
-        <v>4.313472369381659</v>
+        <v>4.313472369381664</v>
       </c>
       <c r="F11" t="n">
-        <v>6.38949553781817</v>
+        <v>6.389495537818167</v>
       </c>
       <c r="G11" t="n">
-        <v>6.234124523949232</v>
+        <v>6.234124523949229</v>
       </c>
       <c r="H11" t="n">
-        <v>6.281971140188986</v>
+        <v>6.281971140188984</v>
       </c>
       <c r="I11" t="n">
-        <v>6.305690866786038</v>
+        <v>6.305690866786034</v>
       </c>
       <c r="J11" t="n">
-        <v>6.276328965724173</v>
+        <v>6.276328965724176</v>
       </c>
       <c r="K11" t="n">
-        <v>6.310323732836927</v>
+        <v>6.310323732836926</v>
       </c>
       <c r="L11" t="n">
-        <v>6.417689104684863</v>
+        <v>6.417689104684865</v>
       </c>
       <c r="M11" t="n">
-        <v>6.305278972448286</v>
+        <v>6.305278972448288</v>
       </c>
       <c r="N11" t="n">
-        <v>6.25372463307429</v>
+        <v>6.253724633074287</v>
       </c>
       <c r="O11" t="n">
-        <v>6.302237933696514</v>
+        <v>6.302237933696516</v>
       </c>
       <c r="P11" t="n">
-        <v>6.365365625059759</v>
+        <v>6.365365625059755</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.295603326249392</v>
+        <v>6.295603326249397</v>
       </c>
       <c r="R11" t="n">
-        <v>6.526821838935568</v>
+        <v>6.52682183893557</v>
       </c>
       <c r="S11" t="n">
-        <v>6.318960202532859</v>
+        <v>6.318960202532862</v>
       </c>
       <c r="T11" t="n">
-        <v>6.333985964701871</v>
+        <v>6.333985964701872</v>
       </c>
       <c r="U11" t="n">
-        <v>6.289137341890118</v>
+        <v>6.289137341890115</v>
       </c>
       <c r="V11" t="n">
-        <v>6.485117503682505</v>
+        <v>6.485117503682507</v>
       </c>
       <c r="W11" t="n">
-        <v>6.142802213106211</v>
+        <v>6.142802213106206</v>
       </c>
       <c r="X11" t="n">
-        <v>6.030254394728915</v>
+        <v>6.03025439472891</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.213961613695043</v>
+        <v>6.213961613695044</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.290663951563984</v>
+        <v>6.29066395156398</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.090202813566953</v>
+        <v>6.090202813566954</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.312158373761275</v>
+        <v>6.312158373761273</v>
       </c>
     </row>
   </sheetData>
@@ -7838,85 +7838,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.203244858494815</v>
+        <v>6.203244858494805</v>
       </c>
       <c r="C2" t="n">
-        <v>6.257589433991958</v>
+        <v>6.257589433991952</v>
       </c>
       <c r="D2" t="n">
-        <v>6.264367188408922</v>
+        <v>6.264367188408917</v>
       </c>
       <c r="E2" t="n">
-        <v>4.104782859486099</v>
+        <v>4.104782859486098</v>
       </c>
       <c r="F2" t="n">
-        <v>6.227462490021257</v>
+        <v>6.22746249002125</v>
       </c>
       <c r="G2" t="n">
-        <v>6.303396515567927</v>
+        <v>6.30339651556792</v>
       </c>
       <c r="H2" t="n">
-        <v>6.289943443871321</v>
+        <v>6.289943443871313</v>
       </c>
       <c r="I2" t="n">
-        <v>6.278176575610023</v>
+        <v>6.278176575610018</v>
       </c>
       <c r="J2" t="n">
-        <v>6.280330051187172</v>
+        <v>6.280330051187171</v>
       </c>
       <c r="K2" t="n">
-        <v>6.270930977629971</v>
+        <v>6.270930977629959</v>
       </c>
       <c r="L2" t="n">
-        <v>6.18814706963177</v>
+        <v>6.188147069631766</v>
       </c>
       <c r="M2" t="n">
-        <v>6.276772742322649</v>
+        <v>6.276772742322643</v>
       </c>
       <c r="N2" t="n">
         <v>6.307155942925501</v>
       </c>
       <c r="O2" t="n">
-        <v>6.244592954190356</v>
+        <v>6.244592954190348</v>
       </c>
       <c r="P2" t="n">
-        <v>6.222681414950237</v>
+        <v>6.222681414950221</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.279205077939855</v>
+        <v>6.279205077939849</v>
       </c>
       <c r="R2" t="n">
-        <v>6.142786490592492</v>
+        <v>6.142786490592482</v>
       </c>
       <c r="S2" t="n">
-        <v>6.245462590859365</v>
+        <v>6.245462590859353</v>
       </c>
       <c r="T2" t="n">
-        <v>6.258957234547241</v>
+        <v>6.258957234547237</v>
       </c>
       <c r="U2" t="n">
-        <v>6.285443291115782</v>
+        <v>6.285443291115778</v>
       </c>
       <c r="V2" t="n">
-        <v>6.514322953981219</v>
+        <v>6.514322953981217</v>
       </c>
       <c r="W2" t="n">
-        <v>6.354183500542169</v>
+        <v>6.354183500542162</v>
       </c>
       <c r="X2" t="n">
-        <v>6.4938129326657</v>
+        <v>6.493812932665693</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.305892057154733</v>
+        <v>6.305892057154727</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.254376475950516</v>
+        <v>6.254376475950508</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.416250925510824</v>
+        <v>6.416250925510814</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.288317164127309</v>
+        <v>6.288317164127299</v>
       </c>
     </row>
     <row r="3">
@@ -7935,7 +7935,7 @@
         <v>12.64058184244743</v>
       </c>
       <c r="E3" t="n">
-        <v>10.51789945801732</v>
+        <v>10.51789945801731</v>
       </c>
       <c r="F3" t="n">
         <v>12.63990071586543</v>
@@ -7959,7 +7959,7 @@
         <v>12.64058184244743</v>
       </c>
       <c r="M3" t="n">
-        <v>12.63881667656836</v>
+        <v>12.63881667656835</v>
       </c>
       <c r="N3" t="n">
         <v>12.64058184244743</v>
@@ -7974,16 +7974,16 @@
         <v>12.64057188229755</v>
       </c>
       <c r="R3" t="n">
-        <v>12.64277205115149</v>
+        <v>12.64277205115148</v>
       </c>
       <c r="S3" t="n">
         <v>12.64058184244743</v>
       </c>
       <c r="T3" t="n">
-        <v>12.63929055527436</v>
+        <v>12.63929055527435</v>
       </c>
       <c r="U3" t="n">
-        <v>12.64364598305361</v>
+        <v>12.6436459830536</v>
       </c>
       <c r="V3" t="n">
         <v>12.86340228722736</v>
@@ -7992,7 +7992,7 @@
         <v>12.64058184244743</v>
       </c>
       <c r="X3" t="n">
-        <v>12.64371522828568</v>
+        <v>12.64371522828567</v>
       </c>
       <c r="Y3" t="n">
         <v>12.63718312492278</v>
@@ -8004,7 +8004,7 @@
         <v>12.64058184244743</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.6509632800095</v>
+        <v>12.65096328000949</v>
       </c>
     </row>
     <row r="4">
@@ -8014,85 +8014,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-15.28769040255164</v>
+        <v>-15.28769040255167</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.659299576909438</v>
+        <v>-2.65929957690945</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.241618689533705</v>
+        <v>-1.241618689533721</v>
       </c>
       <c r="E4" t="n">
-        <v>-17.39474130354239</v>
+        <v>-17.39474130354238</v>
       </c>
       <c r="F4" t="n">
         <v>-10.69156524531343</v>
       </c>
       <c r="G4" t="n">
-        <v>7.66065500470107</v>
+        <v>7.660655004701075</v>
       </c>
       <c r="H4" t="n">
-        <v>5.418620298138192</v>
+        <v>5.418620298138176</v>
       </c>
       <c r="I4" t="n">
-        <v>2.23264755864066</v>
+        <v>2.23264755864065</v>
       </c>
       <c r="J4" t="n">
-        <v>2.607274366334614</v>
+        <v>2.607274366334608</v>
       </c>
       <c r="K4" t="n">
-        <v>0.517324765317146</v>
+        <v>0.5173247653171367</v>
       </c>
       <c r="L4" t="n">
-        <v>-17.05662059609793</v>
+        <v>-17.0566205960979</v>
       </c>
       <c r="M4" t="n">
-        <v>2.262430068637599</v>
+        <v>2.262430068637591</v>
       </c>
       <c r="N4" t="n">
-        <v>9.389331545583373</v>
+        <v>9.389331545583387</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.249260499659616</v>
+        <v>-5.249260499659627</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.09244868160267</v>
+        <v>-10.09244868160273</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3607202037671</v>
+        <v>2.360720203767094</v>
       </c>
       <c r="R4" t="n">
-        <v>-34.22777680252258</v>
+        <v>-34.22777680252261</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.281634105301681</v>
+        <v>-5.281634105301706</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.352680104911453</v>
+        <v>-2.352680104911477</v>
       </c>
       <c r="U4" t="n">
-        <v>3.040712861951792</v>
+        <v>3.040712861951783</v>
       </c>
       <c r="V4" t="n">
-        <v>5.832180499678561</v>
+        <v>5.832180499678564</v>
       </c>
       <c r="W4" t="n">
-        <v>20.52681528398154</v>
+        <v>20.52681528398151</v>
       </c>
       <c r="X4" t="n">
         <v>52.60010500330195</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.07640735205522</v>
+        <v>10.07640735205521</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.100493862164873</v>
+        <v>-3.100493862164882</v>
       </c>
       <c r="AA4" t="n">
         <v>37.16187406823904</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.458540904120076</v>
+        <v>2.458540904120061</v>
       </c>
     </row>
     <row r="5">
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5091473516192366</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5078431033041839</v>
+        <v>0.5078431033041745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4783903681863407</v>
+        <v>0.478390368186342</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5004138646237095</v>
+        <v>0.500413864623709</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
       <c r="Y5" t="n">
         <v>0.478390368186342</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5091473516192405</v>
+        <v>0.509147351619226</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5091473516192379</v>
+        <v>0.5091473516192345</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="E6" t="n">
-        <v>0.53932338494507</v>
+        <v>0.5393233849450637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="J6" t="n">
-        <v>0.538019136630012</v>
+        <v>0.5380191366300079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.53932338494507</v>
+        <v>0.5393233849450637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5459311886284801</v>
+        <v>0.545931188628469</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5465792848956221</v>
+        <v>0.5465792848956195</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7998775609814379</v>
+        <v>0.7998775609814233</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="T6" t="n">
-        <v>0.53932338494507</v>
+        <v>0.5393233849450637</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5305898979495401</v>
+        <v>0.5305898979495411</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8004600174376398</v>
+        <v>0.8004600174376337</v>
       </c>
       <c r="X6" t="n">
-        <v>0.53932338494507</v>
+        <v>0.5393233849450637</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.554834956747581</v>
+        <v>0.5548349567475679</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.53932338494507</v>
+        <v>0.5393233849450637</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7712313983082526</v>
+        <v>0.77123139830825</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5479678509766051</v>
+        <v>0.5479678509765977</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9152908084192845</v>
+        <v>0.9152908084192786</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9147033068049761</v>
+        <v>0.9147033068049759</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9147033068049761</v>
+        <v>0.9147033068049759</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9074190287210998</v>
+        <v>0.9074190287210923</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9078615697388039</v>
+        <v>0.9078615697388027</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9165950567343237</v>
+        <v>0.9165950567343255</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9855012978035832</v>
+        <v>0.9855012978035786</v>
       </c>
       <c r="C8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="D8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="E8" t="n">
-        <v>1.160146455594245</v>
+        <v>1.160146455594243</v>
       </c>
       <c r="F8" t="n">
-        <v>1.043695860044876</v>
+        <v>1.043695860044875</v>
       </c>
       <c r="G8" t="n">
-        <v>1.436508068209626</v>
+        <v>1.436508068209617</v>
       </c>
       <c r="H8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="I8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="J8" t="n">
-        <v>1.357746009564177</v>
+        <v>1.357746009564172</v>
       </c>
       <c r="K8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="L8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="M8" t="n">
         <v>1.359050257877954</v>
       </c>
       <c r="N8" t="n">
-        <v>1.069487320491215</v>
+        <v>1.069487320491216</v>
       </c>
       <c r="O8" t="n">
         <v>1.149061730031975</v>
       </c>
       <c r="P8" t="n">
-        <v>1.129556119453838</v>
+        <v>1.129556119453833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9120904012440227</v>
+        <v>0.9120904012440104</v>
       </c>
       <c r="R8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="S8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="T8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="U8" t="n">
-        <v>1.171080859598152</v>
+        <v>1.171080859598146</v>
       </c>
       <c r="V8" t="n">
-        <v>1.241993787215332</v>
+        <v>1.241993787215333</v>
       </c>
       <c r="W8" t="n">
-        <v>1.359123671168703</v>
+        <v>1.359123671168699</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9463269058216871</v>
+        <v>0.9463269058216808</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.720804299971165</v>
+        <v>1.72080429997117</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9785624340644999</v>
+        <v>0.9785624340644932</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.359050257879226</v>
+        <v>1.359050257879223</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.749253382551569</v>
+        <v>1.749253382551565</v>
       </c>
     </row>
     <row r="9">
@@ -8454,85 +8454,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.655925222445206</v>
+        <v>1.655925222445203</v>
       </c>
       <c r="C9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="D9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="E9" t="n">
-        <v>1.923606437073798</v>
+        <v>1.923606437073804</v>
       </c>
       <c r="F9" t="n">
-        <v>1.201693306887611</v>
+        <v>1.201693306887607</v>
       </c>
       <c r="G9" t="n">
-        <v>2.003922876075005</v>
+        <v>2.003922876075003</v>
       </c>
       <c r="H9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="I9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="J9" t="n">
-        <v>2.00261868810135</v>
+        <v>2.002618688101357</v>
       </c>
       <c r="K9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="L9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="M9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="N9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="O9" t="n">
-        <v>2.119248842823855</v>
+        <v>2.119248842823859</v>
       </c>
       <c r="P9" t="n">
-        <v>2.144330261931355</v>
+        <v>2.144330261931365</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.003922876075005</v>
+        <v>2.003922876075003</v>
       </c>
       <c r="R9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="S9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="T9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="U9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="V9" t="n">
-        <v>2.396771300094479</v>
+        <v>2.396771300094484</v>
       </c>
       <c r="W9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="X9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.794111236094976</v>
+        <v>1.794111236094966</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.003922936416411</v>
+        <v>2.003922936416407</v>
       </c>
     </row>
     <row r="10">
@@ -8548,13 +8548,13 @@
         <v>12.71708996863861</v>
       </c>
       <c r="D10" t="n">
-        <v>12.68377815969492</v>
+        <v>12.68377815969491</v>
       </c>
       <c r="E10" t="n">
         <v>10.97565618016112</v>
       </c>
       <c r="F10" t="n">
-        <v>12.89437694451326</v>
+        <v>12.89437694451325</v>
       </c>
       <c r="G10" t="n">
         <v>12.45026725880009</v>
@@ -8566,7 +8566,7 @@
         <v>12.60296100421449</v>
       </c>
       <c r="J10" t="n">
-        <v>12.59036133572435</v>
+        <v>12.59036133572434</v>
       </c>
       <c r="K10" t="n">
         <v>12.64286311493164</v>
@@ -8575,10 +8575,10 @@
         <v>13.13477372788197</v>
       </c>
       <c r="M10" t="n">
-        <v>12.60004869726394</v>
+        <v>12.60004869726393</v>
       </c>
       <c r="N10" t="n">
-        <v>12.4322613705311</v>
+        <v>12.43226137053109</v>
       </c>
       <c r="O10" t="n">
         <v>12.79648258161967</v>
@@ -8587,37 +8587,37 @@
         <v>12.92213344583752</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.59668787860267</v>
+        <v>12.59668787860266</v>
       </c>
       <c r="R10" t="n">
         <v>13.40683485076579</v>
       </c>
       <c r="S10" t="n">
-        <v>12.79642993400703</v>
+        <v>12.79642993400702</v>
       </c>
       <c r="T10" t="n">
-        <v>12.70722116755512</v>
+        <v>12.70722116755511</v>
       </c>
       <c r="U10" t="n">
-        <v>12.57912697220365</v>
+        <v>12.57912697220364</v>
       </c>
       <c r="V10" t="n">
         <v>12.72533241076734</v>
       </c>
       <c r="W10" t="n">
-        <v>12.15400732585242</v>
+        <v>12.15400732585241</v>
       </c>
       <c r="X10" t="n">
-        <v>11.35846205113901</v>
+        <v>11.35846205113902</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.41764907934116</v>
+        <v>12.41764907934115</v>
       </c>
       <c r="Z10" t="n">
         <v>12.74318805617812</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.78838069845399</v>
+        <v>11.78838069845398</v>
       </c>
       <c r="AB10" t="n">
         <v>12.60945051074161</v>
@@ -8630,85 +8630,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.388653817711618</v>
+        <v>6.388653817711612</v>
       </c>
       <c r="C11" t="n">
-        <v>6.292864864226286</v>
+        <v>6.29286486422628</v>
       </c>
       <c r="D11" t="n">
-        <v>6.284021650415021</v>
+        <v>6.284021650415018</v>
       </c>
       <c r="E11" t="n">
-        <v>4.313063626845646</v>
+        <v>4.313063626845645</v>
       </c>
       <c r="F11" t="n">
-        <v>6.343249985023642</v>
+        <v>6.343249985023639</v>
       </c>
       <c r="G11" t="n">
-        <v>6.216950550251577</v>
+        <v>6.21695055025157</v>
       </c>
       <c r="H11" t="n">
-        <v>6.241761412771393</v>
+        <v>6.241761412771383</v>
       </c>
       <c r="I11" t="n">
-        <v>6.261058974323539</v>
+        <v>6.261058974323535</v>
       </c>
       <c r="J11" t="n">
-        <v>6.257435586507436</v>
+        <v>6.257435586507435</v>
       </c>
       <c r="K11" t="n">
-        <v>6.272145897728793</v>
+        <v>6.272145897728783</v>
       </c>
       <c r="L11" t="n">
-        <v>6.413005952400583</v>
+        <v>6.413005952400576</v>
       </c>
       <c r="M11" t="n">
-        <v>6.259133188192923</v>
+        <v>6.259133188192918</v>
       </c>
       <c r="N11" t="n">
-        <v>6.212369464325623</v>
+        <v>6.212369464325624</v>
       </c>
       <c r="O11" t="n">
-        <v>6.315936277085966</v>
+        <v>6.315936277085961</v>
       </c>
       <c r="P11" t="n">
-        <v>6.351556297402587</v>
+        <v>6.35155629740258</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.25923771640866</v>
+        <v>6.259237716408656</v>
       </c>
       <c r="R11" t="n">
-        <v>6.490437499340659</v>
+        <v>6.490437499340658</v>
       </c>
       <c r="S11" t="n">
-        <v>6.316373969177374</v>
+        <v>6.316373969177371</v>
       </c>
       <c r="T11" t="n">
-        <v>6.289865879617008</v>
+        <v>6.289865879617002</v>
       </c>
       <c r="U11" t="n">
-        <v>6.25608693556916</v>
+        <v>6.256086935569153</v>
       </c>
       <c r="V11" t="n">
-        <v>6.451500720189318</v>
+        <v>6.451500720189317</v>
       </c>
       <c r="W11" t="n">
-        <v>6.132790544870455</v>
+        <v>6.132790544870453</v>
       </c>
       <c r="X11" t="n">
-        <v>5.909018641205115</v>
+        <v>5.909018641205112</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.206003366801607</v>
+        <v>6.206003366801593</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.301103571605528</v>
+        <v>6.301103571605529</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.028496689189907</v>
+        <v>6.028496689189898</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.269428721817076</v>
+        <v>6.26942872181707</v>
       </c>
     </row>
   </sheetData>
@@ -8874,85 +8874,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.568159837384985</v>
+        <v>6.568159837384984</v>
       </c>
       <c r="C2" t="n">
-        <v>6.525188726999226</v>
+        <v>6.525188726999231</v>
       </c>
       <c r="D2" t="n">
         <v>6.585846418113086</v>
       </c>
       <c r="E2" t="n">
-        <v>4.359409880729784</v>
+        <v>4.35940988072979</v>
       </c>
       <c r="F2" t="n">
-        <v>6.528556067082741</v>
+        <v>6.528556067082742</v>
       </c>
       <c r="G2" t="n">
-        <v>6.715607593276537</v>
+        <v>6.715607593276531</v>
       </c>
       <c r="H2" t="n">
-        <v>6.614225279526068</v>
+        <v>6.614225279526069</v>
       </c>
       <c r="I2" t="n">
-        <v>6.540082344885091</v>
+        <v>6.540082344885096</v>
       </c>
       <c r="J2" t="n">
-        <v>6.625272529289162</v>
+        <v>6.62527252928916</v>
       </c>
       <c r="K2" t="n">
-        <v>6.570524237555544</v>
+        <v>6.570524237555546</v>
       </c>
       <c r="L2" t="n">
-        <v>6.643780126533489</v>
+        <v>6.64378012653348</v>
       </c>
       <c r="M2" t="n">
-        <v>6.700079875192467</v>
+        <v>6.700079875192469</v>
       </c>
       <c r="N2" t="n">
-        <v>6.586206811916078</v>
+        <v>6.586206811916073</v>
       </c>
       <c r="O2" t="n">
-        <v>6.568859527687887</v>
+        <v>6.568859527687888</v>
       </c>
       <c r="P2" t="n">
-        <v>6.586911932113366</v>
+        <v>6.586911932113367</v>
       </c>
       <c r="Q2" t="n">
         <v>6.547049065129857</v>
       </c>
       <c r="R2" t="n">
-        <v>6.527189460378983</v>
+        <v>6.527189460378986</v>
       </c>
       <c r="S2" t="n">
-        <v>6.596066965351506</v>
+        <v>6.596066965351505</v>
       </c>
       <c r="T2" t="n">
         <v>6.546254464268886</v>
       </c>
       <c r="U2" t="n">
-        <v>6.633475839326393</v>
+        <v>6.633475839326396</v>
       </c>
       <c r="V2" t="n">
-        <v>6.732914445369869</v>
+        <v>6.73291444536987</v>
       </c>
       <c r="W2" t="n">
-        <v>6.672447241482653</v>
+        <v>6.672447241482654</v>
       </c>
       <c r="X2" t="n">
-        <v>6.620679188986908</v>
+        <v>6.620679188986906</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.605418563774246</v>
+        <v>6.605418563774247</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.562314162391915</v>
+        <v>6.562314162391917</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.624252743306002</v>
+        <v>6.624252743306004</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.693237559419957</v>
+        <v>6.693237559419962</v>
       </c>
     </row>
     <row r="3">
@@ -8971,7 +8971,7 @@
         <v>12.86906269402864</v>
       </c>
       <c r="E3" t="n">
-        <v>10.67270131970376</v>
+        <v>10.67270131970375</v>
       </c>
       <c r="F3" t="n">
         <v>12.86869909869895</v>
@@ -9050,85 +9050,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.12457090425164</v>
+        <v>18.12457090425129</v>
       </c>
       <c r="C4" t="n">
-        <v>8.369008801332196</v>
+        <v>8.369008801332201</v>
       </c>
       <c r="D4" t="n">
-        <v>25.64985350147242</v>
+        <v>25.64985350147243</v>
       </c>
       <c r="E4" t="n">
-        <v>6.996510513692159</v>
+        <v>6.996510513692021</v>
       </c>
       <c r="F4" t="n">
-        <v>9.360400886331778</v>
+        <v>9.360400886331771</v>
       </c>
       <c r="G4" t="n">
-        <v>53.99470105077722</v>
+        <v>53.99470105077717</v>
       </c>
       <c r="H4" t="n">
-        <v>34.81988237730857</v>
+        <v>34.81988237730859</v>
       </c>
       <c r="I4" t="n">
-        <v>12.62729975282679</v>
+        <v>12.62729975282677</v>
       </c>
       <c r="J4" t="n">
-        <v>34.21569706363656</v>
+        <v>34.21569706363654</v>
       </c>
       <c r="K4" t="n">
-        <v>19.21521019917265</v>
+        <v>19.21521019917266</v>
       </c>
       <c r="L4" t="n">
-        <v>38.57359151593654</v>
+        <v>38.5735915159358</v>
       </c>
       <c r="M4" t="n">
         <v>53.7508858853527</v>
       </c>
       <c r="N4" t="n">
-        <v>25.02471039617396</v>
+        <v>25.02471039617399</v>
       </c>
       <c r="O4" t="n">
-        <v>18.00378604240105</v>
+        <v>18.00378604240102</v>
       </c>
       <c r="P4" t="n">
         <v>23.43869453243967</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.93134737279554</v>
+        <v>13.93134737279546</v>
       </c>
       <c r="R4" t="n">
-        <v>9.154950395635897</v>
+        <v>9.154950395635886</v>
       </c>
       <c r="S4" t="n">
-        <v>24.25048912722898</v>
+        <v>24.25048912722893</v>
       </c>
       <c r="T4" t="n">
-        <v>14.42697641648885</v>
+        <v>14.42697641648882</v>
       </c>
       <c r="U4" t="n">
-        <v>36.02704421883654</v>
+        <v>36.02704421883655</v>
       </c>
       <c r="V4" t="n">
-        <v>11.89804938494818</v>
+        <v>11.8980493849482</v>
       </c>
       <c r="W4" t="n">
-        <v>48.10227676189422</v>
+        <v>48.10227676189412</v>
       </c>
       <c r="X4" t="n">
-        <v>34.7398182330838</v>
+        <v>34.73981823308343</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.83835866665489</v>
+        <v>29.83835866665496</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.81823848623486</v>
+        <v>16.81823848623483</v>
       </c>
       <c r="AA4" t="n">
-        <v>34.88375561711661</v>
+        <v>34.88375561711655</v>
       </c>
       <c r="AB4" t="n">
-        <v>55.86467572856063</v>
+        <v>55.86467572856068</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7046579885698754</v>
+        <v>0.7046579885698765</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6798992179406455</v>
+        <v>0.6798992179406478</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6913754657834078</v>
+        <v>0.691375465783408</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7070533720713421</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6798992179406455</v>
+        <v>0.6798992179406478</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7070533720713429</v>
+        <v>0.7070533720713381</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7070533720713422</v>
+        <v>0.7070533720713382</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="E6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="G6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8265746975637989</v>
+        <v>0.8265746975638005</v>
       </c>
       <c r="K6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="L6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8334697815989539</v>
+        <v>0.8334697815989496</v>
       </c>
       <c r="O6" t="n">
         <v>1.374086831003744</v>
       </c>
       <c r="P6" t="n">
-        <v>1.373797405529915</v>
+        <v>1.373797405529916</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="R6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8289700810652644</v>
+        <v>0.828970081065264</v>
       </c>
       <c r="U6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8132921747773322</v>
+        <v>0.8132921747773313</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8596726186147335</v>
+        <v>0.8596726186147327</v>
       </c>
       <c r="X6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8444289214042798</v>
+        <v>0.8444289214043053</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.345453946268391</v>
+        <v>1.345453946268386</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8438316954496888</v>
+        <v>0.8438316954496887</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="C7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="D7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="E7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="F7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="G7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="H7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="I7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="J7" t="n">
-        <v>1.327796906970718</v>
+        <v>1.32779690697072</v>
       </c>
       <c r="K7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="L7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="M7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="N7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="O7" t="n">
-        <v>1.328154413475839</v>
+        <v>1.328154413475837</v>
       </c>
       <c r="P7" t="n">
-        <v>1.328154413475839</v>
+        <v>1.328154413475837</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="R7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="S7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="T7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="U7" t="n">
-        <v>1.327958953163745</v>
+        <v>1.327958953163754</v>
       </c>
       <c r="V7" t="n">
-        <v>1.314514384184251</v>
+        <v>1.314514384184252</v>
       </c>
       <c r="W7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="X7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.330192290472188</v>
+        <v>1.330192290472181</v>
       </c>
     </row>
     <row r="8">
@@ -9402,82 +9402,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.586173488163666</v>
+        <v>1.586173488163663</v>
       </c>
       <c r="C8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="D8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="E8" t="n">
-        <v>1.911300803075258</v>
+        <v>1.911300803075254</v>
       </c>
       <c r="F8" t="n">
-        <v>1.694511113883535</v>
+        <v>1.694511113883526</v>
       </c>
       <c r="G8" t="n">
-        <v>2.425788064580142</v>
+        <v>2.425788064580151</v>
       </c>
       <c r="H8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="I8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="J8" t="n">
-        <v>2.279193722535708</v>
+        <v>2.279193722535712</v>
       </c>
       <c r="K8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="L8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="M8" t="n">
-        <v>2.281589106037755</v>
+        <v>2.281589106037762</v>
       </c>
       <c r="N8" t="n">
-        <v>1.742525661576498</v>
+        <v>1.742525661576494</v>
       </c>
       <c r="O8" t="n">
-        <v>1.890664976509315</v>
+        <v>1.890664976509316</v>
       </c>
       <c r="P8" t="n">
-        <v>1.854352450893332</v>
+        <v>1.854352450893338</v>
       </c>
       <c r="Q8" t="n">
         <v>1.449508447273775</v>
       </c>
       <c r="R8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="S8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="T8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="U8" t="n">
-        <v>1.942014547368289</v>
+        <v>1.942014547368288</v>
       </c>
       <c r="V8" t="n">
-        <v>2.075676550903759</v>
+        <v>2.075676550903758</v>
       </c>
       <c r="W8" t="n">
-        <v>2.281725774714538</v>
+        <v>2.281725774714535</v>
       </c>
       <c r="X8" t="n">
-        <v>1.513244670207425</v>
+        <v>1.513244670207432</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.972765893117989</v>
+        <v>2.972765893117992</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.573255786067558</v>
+        <v>1.573255786067563</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.281589106037166</v>
+        <v>2.281589106037172</v>
       </c>
       <c r="AB8" t="n">
         <v>3.008008868232178</v>
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.038200526900436</v>
+        <v>3.038200526900427</v>
       </c>
       <c r="C9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="D9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="E9" t="n">
-        <v>3.579910630721479</v>
+        <v>3.579910630721468</v>
       </c>
       <c r="F9" t="n">
-        <v>2.118965239968037</v>
+        <v>2.118965239968031</v>
       </c>
       <c r="G9" t="n">
-        <v>3.742448097425029</v>
+        <v>3.742448097425031</v>
       </c>
       <c r="H9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="I9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="J9" t="n">
-        <v>3.74005266811386</v>
+        <v>3.740052668113859</v>
       </c>
       <c r="K9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="L9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="M9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="N9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="O9" t="n">
-        <v>3.975834820163398</v>
+        <v>3.97583482016339</v>
       </c>
       <c r="P9" t="n">
-        <v>4.026592428117186</v>
+        <v>4.026592428117182</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.742448097425029</v>
+        <v>3.742448097425031</v>
       </c>
       <c r="R9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="S9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="T9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="U9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="V9" t="n">
-        <v>4.539455858394722</v>
+        <v>4.539455858394721</v>
       </c>
       <c r="W9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="X9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.317849436536093</v>
+        <v>3.317849436536094</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.74244805161532</v>
+        <v>3.742448051615326</v>
       </c>
     </row>
     <row r="10">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.45272348792534</v>
+        <v>12.45272348792535</v>
       </c>
       <c r="C10" t="n">
         <v>12.70446987385887</v>
@@ -9596,37 +9596,37 @@
         <v>11.57553160908591</v>
       </c>
       <c r="H10" t="n">
-        <v>12.19390769686226</v>
+        <v>12.19390769686225</v>
       </c>
       <c r="I10" t="n">
         <v>12.62407394831044</v>
       </c>
       <c r="J10" t="n">
-        <v>12.08101557371675</v>
+        <v>12.08101557371674</v>
       </c>
       <c r="K10" t="n">
         <v>12.44333677482794</v>
       </c>
       <c r="L10" t="n">
-        <v>12.00828592456798</v>
+        <v>12.00828592456801</v>
       </c>
       <c r="M10" t="n">
-        <v>11.68931901152662</v>
+        <v>11.68931901152663</v>
       </c>
       <c r="N10" t="n">
-        <v>12.35125301818113</v>
+        <v>12.35125301818112</v>
       </c>
       <c r="O10" t="n">
-        <v>12.44358018992789</v>
+        <v>12.44358018992788</v>
       </c>
       <c r="P10" t="n">
         <v>12.3389855284304</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.58200800559642</v>
+        <v>12.58200800559643</v>
       </c>
       <c r="R10" t="n">
-        <v>12.69955578506869</v>
+        <v>12.6995557850687</v>
       </c>
       <c r="S10" t="n">
         <v>12.28849945803917</v>
@@ -9644,7 +9644,7 @@
         <v>11.84053073879995</v>
       </c>
       <c r="X10" t="n">
-        <v>12.15446390631548</v>
+        <v>12.15446390631549</v>
       </c>
       <c r="Y10" t="n">
         <v>12.22686579176148</v>
@@ -9653,10 +9653,10 @@
         <v>12.48757422644284</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.1255789049596</v>
+        <v>12.12557890495959</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.79270062170442</v>
+        <v>11.79270062170441</v>
       </c>
     </row>
     <row r="11">
@@ -9666,82 +9666,82 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.378724171813656</v>
+        <v>6.37872417181366</v>
       </c>
       <c r="C11" t="n">
         <v>6.450742010551906</v>
       </c>
       <c r="D11" t="n">
-        <v>6.352195866361408</v>
+        <v>6.352195866361411</v>
       </c>
       <c r="E11" t="n">
-        <v>4.296728403132739</v>
+        <v>4.29672840313274</v>
       </c>
       <c r="F11" t="n">
         <v>6.447111036402007</v>
       </c>
       <c r="G11" t="n">
-        <v>6.127097689360069</v>
+        <v>6.127097689360066</v>
       </c>
       <c r="H11" t="n">
-        <v>6.307027604224059</v>
+        <v>6.307027604224053</v>
       </c>
       <c r="I11" t="n">
-        <v>6.42861168485051</v>
+        <v>6.428611684850511</v>
       </c>
       <c r="J11" t="n">
-        <v>6.269058912155508</v>
+        <v>6.269058912155509</v>
       </c>
       <c r="K11" t="n">
-        <v>6.376914891264224</v>
+        <v>6.376914891264228</v>
       </c>
       <c r="L11" t="n">
-        <v>6.252123953296085</v>
+        <v>6.252123953296098</v>
       </c>
       <c r="M11" t="n">
-        <v>6.163407299552092</v>
+        <v>6.163407299552095</v>
       </c>
       <c r="N11" t="n">
-        <v>6.350601759243926</v>
+        <v>6.350601759243927</v>
       </c>
       <c r="O11" t="n">
-        <v>6.375583002500456</v>
+        <v>6.375583002500457</v>
       </c>
       <c r="P11" t="n">
-        <v>6.345805072469374</v>
+        <v>6.34580507246937</v>
       </c>
       <c r="Q11" t="n">
         <v>6.41644279900413</v>
       </c>
       <c r="R11" t="n">
-        <v>6.450081264597899</v>
+        <v>6.450081264597903</v>
       </c>
       <c r="S11" t="n">
-        <v>6.331908842831038</v>
+        <v>6.331908842831037</v>
       </c>
       <c r="T11" t="n">
-        <v>6.417462655921143</v>
+        <v>6.417462655921144</v>
       </c>
       <c r="U11" t="n">
-        <v>6.27086980812362</v>
+        <v>6.270869808123622</v>
       </c>
       <c r="V11" t="n">
         <v>6.609747999700931</v>
       </c>
       <c r="W11" t="n">
-        <v>6.204461924116741</v>
+        <v>6.204461924116745</v>
       </c>
       <c r="X11" t="n">
-        <v>6.295273928753364</v>
+        <v>6.295273928753367</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.31395023037943</v>
+        <v>6.313950230379425</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.388760440110157</v>
+        <v>6.388760440110161</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.285965249937338</v>
+        <v>6.285965249937335</v>
       </c>
       <c r="AB11" t="n">
         <v>6.198765799175622</v>
@@ -9910,31 +9910,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.393578218040654</v>
+        <v>6.393578218040652</v>
       </c>
       <c r="C2" t="n">
-        <v>6.402988669144915</v>
+        <v>6.402988669144911</v>
       </c>
       <c r="D2" t="n">
-        <v>6.419658633309731</v>
+        <v>6.419658633309729</v>
       </c>
       <c r="E2" t="n">
         <v>4.265607761289395</v>
       </c>
       <c r="F2" t="n">
-        <v>6.350124262552289</v>
+        <v>6.35012426255229</v>
       </c>
       <c r="G2" t="n">
-        <v>6.580765117303408</v>
+        <v>6.580765117303407</v>
       </c>
       <c r="H2" t="n">
-        <v>6.482026306197571</v>
+        <v>6.482026306197569</v>
       </c>
       <c r="I2" t="n">
         <v>6.395818689728705</v>
       </c>
       <c r="J2" t="n">
-        <v>6.460655810317475</v>
+        <v>6.460655810317474</v>
       </c>
       <c r="K2" t="n">
         <v>6.4133737216242</v>
@@ -9943,52 +9943,52 @@
         <v>6.331126185919064</v>
       </c>
       <c r="M2" t="n">
-        <v>6.404780428919688</v>
+        <v>6.404780428919689</v>
       </c>
       <c r="N2" t="n">
-        <v>6.414032003603881</v>
+        <v>6.414032003603879</v>
       </c>
       <c r="O2" t="n">
-        <v>6.385492352671642</v>
+        <v>6.385492352671641</v>
       </c>
       <c r="P2" t="n">
-        <v>6.436707206372225</v>
+        <v>6.436707206372223</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.403676783988964</v>
+        <v>6.403676783988965</v>
       </c>
       <c r="R2" t="n">
-        <v>6.292568974155063</v>
+        <v>6.292568974155062</v>
       </c>
       <c r="S2" t="n">
-        <v>6.365599164712235</v>
+        <v>6.365599164712231</v>
       </c>
       <c r="T2" t="n">
-        <v>6.370276605969404</v>
+        <v>6.370276605969401</v>
       </c>
       <c r="U2" t="n">
-        <v>6.428347692463973</v>
+        <v>6.428347692463971</v>
       </c>
       <c r="V2" t="n">
-        <v>6.634371041994925</v>
+        <v>6.634371041994923</v>
       </c>
       <c r="W2" t="n">
-        <v>6.526114970453154</v>
+        <v>6.526114970453153</v>
       </c>
       <c r="X2" t="n">
-        <v>6.556898845814613</v>
+        <v>6.556898845814612</v>
       </c>
       <c r="Y2" t="n">
         <v>6.586799344668417</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.426874913647374</v>
+        <v>6.426874913647373</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.471787692669679</v>
+        <v>6.471787692669678</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.522811189426116</v>
+        <v>6.522811189426114</v>
       </c>
     </row>
     <row r="3">
@@ -10013,7 +10013,7 @@
         <v>12.77171745717787</v>
       </c>
       <c r="G3" t="n">
-        <v>12.77202063112744</v>
+        <v>12.77202063112743</v>
       </c>
       <c r="H3" t="n">
         <v>12.77223063603398</v>
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.385373044406864</v>
+        <v>-1.385373044406862</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154485860314888</v>
+        <v>1.154485860314891</v>
       </c>
       <c r="D4" t="n">
-        <v>5.113798016100306</v>
+        <v>5.113798016100302</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.049826102876251</v>
+        <v>-2.049826102876247</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.43227669018002</v>
+        <v>-12.43227669017999</v>
       </c>
       <c r="G4" t="n">
-        <v>39.6486628575693</v>
+        <v>39.64866285756922</v>
       </c>
       <c r="H4" t="n">
         <v>22.6367128235953</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.085172688686978</v>
+        <v>-1.085172688686976</v>
       </c>
       <c r="J4" t="n">
-        <v>14.57810682082035</v>
+        <v>14.57810682082034</v>
       </c>
       <c r="K4" t="n">
-        <v>3.451478001119532</v>
+        <v>3.451478001119535</v>
       </c>
       <c r="L4" t="n">
         <v>-15.28219498799703</v>
       </c>
       <c r="M4" t="n">
-        <v>1.593968309500855</v>
+        <v>1.593968309500853</v>
       </c>
       <c r="N4" t="n">
-        <v>3.64348666611799</v>
+        <v>3.643486666117986</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.811533532583021</v>
+        <v>-2.811533532583019</v>
       </c>
       <c r="P4" t="n">
-        <v>8.65321949517481</v>
+        <v>8.653219495174813</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.063784169336205</v>
+        <v>1.063784169336203</v>
       </c>
       <c r="R4" t="n">
-        <v>-29.27306632811646</v>
+        <v>-29.27306632811648</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.344944492175893</v>
+        <v>-7.344944492175903</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.476857691919669</v>
+        <v>-7.476857691919675</v>
       </c>
       <c r="U4" t="n">
-        <v>6.501650089427129</v>
+        <v>6.501650089427143</v>
       </c>
       <c r="V4" t="n">
-        <v>7.544766661339354</v>
+        <v>7.544766661339344</v>
       </c>
       <c r="W4" t="n">
-        <v>32.02010994958916</v>
+        <v>32.02010994958902</v>
       </c>
       <c r="X4" t="n">
-        <v>37.88124208523928</v>
+        <v>37.88124208523925</v>
       </c>
       <c r="Y4" t="n">
-        <v>47.21696233610615</v>
+        <v>47.21696233610609</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.176635051639865</v>
+        <v>6.176635051639862</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.23206624512346</v>
+        <v>18.23206624512344</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.64693069957515</v>
+        <v>30.64693069957518</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.6141578754143058</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6141578754143058</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="F5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.6141578754143058</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6141578754143058</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6120420878104025</v>
+        <v>0.6120420878104027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6141578754143058</v>
+        <v>0.6141578754143059</v>
       </c>
       <c r="L5" t="n">
+        <v>0.6141578754143061</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="M5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
       <c r="N5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="U5" t="n">
+        <v>0.5862431651089499</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6002505023197146</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6141578754143066</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5862431651089499</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.5862431651089495</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.6002505023197156</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>0.6141578754143059</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.6141578754143059</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.5862431651089495</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.6141578754143058</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.6141578754143059</v>
+        <v>0.6141578754143066</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="C6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="D6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="E6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="F6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="G6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="I6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="J6" t="n">
-        <v>1.075151937181193</v>
+        <v>1.07515193718119</v>
       </c>
       <c r="K6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="L6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="M6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6852236840603814</v>
+        <v>0.685223684060385</v>
       </c>
       <c r="O6" t="n">
-        <v>1.106041514433886</v>
+        <v>1.106041514433889</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6719672789168116</v>
+        <v>0.6719672789168138</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="R6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="S6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="T6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="U6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6681183414340301</v>
+        <v>0.6681183414340293</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7058818331332801</v>
+        <v>0.7058818331331803</v>
       </c>
       <c r="X6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6940008461912113</v>
+        <v>0.6940008461912135</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.077267724785095</v>
+        <v>1.077267724785091</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.682025714528617</v>
+        <v>0.6820257145286186</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6930314923205987</v>
+        <v>0.6930314923206008</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="C7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="D7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="E7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="F7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="G7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="H7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="I7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="J7" t="n">
-        <v>1.106954266520295</v>
+        <v>1.106954266520296</v>
       </c>
       <c r="K7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="L7" t="n">
         <v>1.109070054124198</v>
       </c>
       <c r="M7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="N7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="O7" t="n">
-        <v>1.107173749370278</v>
+        <v>1.107173749370277</v>
       </c>
       <c r="P7" t="n">
-        <v>1.107173749370278</v>
+        <v>1.107173749370277</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="R7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="S7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="T7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="U7" t="n">
-        <v>1.104728311639015</v>
+        <v>1.104728311639016</v>
       </c>
       <c r="V7" t="n">
         <v>1.095162681029608</v>
       </c>
       <c r="W7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="X7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.109070054124197</v>
+        <v>1.109070054124198</v>
       </c>
     </row>
     <row r="8">
@@ -10441,31 +10441,31 @@
         <v>1.268193862071485</v>
       </c>
       <c r="C8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="D8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="E8" t="n">
-        <v>1.511615040814244</v>
+        <v>1.511615040814243</v>
       </c>
       <c r="F8" t="n">
-        <v>1.349305695356408</v>
+        <v>1.349305695356407</v>
       </c>
       <c r="G8" t="n">
         <v>1.896809055368701</v>
       </c>
       <c r="H8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="I8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="J8" t="n">
         <v>1.786732235700488</v>
       </c>
       <c r="K8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="L8" t="n">
         <v>1.788848023304392</v>
@@ -10477,28 +10477,28 @@
         <v>1.38525394475865</v>
       </c>
       <c r="O8" t="n">
-        <v>1.496165101806745</v>
+        <v>1.496165101806746</v>
       </c>
       <c r="P8" t="n">
-        <v>1.468978097233029</v>
+        <v>1.468978097233026</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.165873436078239</v>
+        <v>1.165873436078241</v>
       </c>
       <c r="R8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="S8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="T8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="U8" t="n">
-        <v>1.532828521989136</v>
+        <v>1.532828521989134</v>
       </c>
       <c r="V8" t="n">
-        <v>1.630547717700027</v>
+        <v>1.630547717700029</v>
       </c>
       <c r="W8" t="n">
         <v>1.788950346598301</v>
@@ -10507,16 +10507,16 @@
         <v>1.21359242440954</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.303280547458939</v>
+        <v>2.30328054745894</v>
       </c>
       <c r="Z8" t="n">
         <v>1.258522443733396</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.788848023304391</v>
+        <v>1.788848023304392</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.332714830958056</v>
+        <v>2.33271483095806</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.342029756824002</v>
+        <v>2.342029756824007</v>
       </c>
       <c r="C9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="D9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="E9" t="n">
-        <v>2.744778354343614</v>
+        <v>2.744778354343619</v>
       </c>
       <c r="F9" t="n">
-        <v>1.658600151226557</v>
+        <v>1.658600151226561</v>
       </c>
       <c r="G9" t="n">
-        <v>2.865621100856018</v>
+        <v>2.865621100856027</v>
       </c>
       <c r="H9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="I9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86350490501871</v>
+        <v>2.863504905018712</v>
       </c>
       <c r="K9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="L9" t="n">
-        <v>2.865620692622613</v>
+        <v>2.865620692622619</v>
       </c>
       <c r="M9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="N9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="O9" t="n">
-        <v>3.039138586683871</v>
+        <v>3.039138586683877</v>
       </c>
       <c r="P9" t="n">
-        <v>3.076875662792734</v>
+        <v>3.076875662792735</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.865621100856018</v>
+        <v>2.865621100856027</v>
       </c>
       <c r="R9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="S9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="T9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="U9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="V9" t="n">
-        <v>3.455926457497367</v>
+        <v>3.455926457497371</v>
       </c>
       <c r="W9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="X9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.549942079963643</v>
+        <v>2.549942079963647</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.865620692622612</v>
+        <v>2.865620692622618</v>
       </c>
     </row>
     <row r="10">
@@ -10623,7 +10623,7 @@
         <v>12.67035043873608</v>
       </c>
       <c r="E10" t="n">
-        <v>10.67605268736822</v>
+        <v>10.67605268736823</v>
       </c>
       <c r="F10" t="n">
         <v>13.07291661830837</v>
@@ -10635,7 +10635,7 @@
         <v>12.30818535174705</v>
       </c>
       <c r="I10" t="n">
-        <v>12.80992426735767</v>
+        <v>12.80992426735766</v>
       </c>
       <c r="J10" t="n">
         <v>12.39857995325069</v>
@@ -10671,7 +10671,7 @@
         <v>12.95377967216133</v>
       </c>
       <c r="U10" t="n">
-        <v>12.62478246974422</v>
+        <v>12.62478246974421</v>
       </c>
       <c r="V10" t="n">
         <v>12.79520648903147</v>
@@ -10683,7 +10683,7 @@
         <v>11.90904404515628</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.67250372603997</v>
+        <v>11.67250372603996</v>
       </c>
       <c r="Z10" t="n">
         <v>12.62538969080163</v>
@@ -10705,7 +10705,7 @@
         <v>6.41708911247138</v>
       </c>
       <c r="C11" t="n">
-        <v>6.398562729909115</v>
+        <v>6.398562729909113</v>
       </c>
       <c r="D11" t="n">
         <v>6.373302818866258</v>
@@ -10714,19 +10714,19 @@
         <v>4.294487534349289</v>
       </c>
       <c r="F11" t="n">
-        <v>6.48717084073144</v>
+        <v>6.487170840731437</v>
       </c>
       <c r="G11" t="n">
         <v>6.097330750207337</v>
       </c>
       <c r="H11" t="n">
-        <v>6.270884223022441</v>
+        <v>6.270884223022442</v>
       </c>
       <c r="I11" t="n">
-        <v>6.412969412103458</v>
+        <v>6.412969412103456</v>
       </c>
       <c r="J11" t="n">
-        <v>6.292401223786074</v>
+        <v>6.292401223786076</v>
       </c>
       <c r="K11" t="n">
         <v>6.382986200271915</v>
@@ -10735,52 +10735,52 @@
         <v>6.52248158330693</v>
       </c>
       <c r="M11" t="n">
-        <v>6.396452201951469</v>
+        <v>6.396452201951467</v>
       </c>
       <c r="N11" t="n">
-        <v>6.38253826550149</v>
+        <v>6.382538265501486</v>
       </c>
       <c r="O11" t="n">
         <v>6.428998915189634</v>
       </c>
       <c r="P11" t="n">
-        <v>6.343067812713965</v>
+        <v>6.343067812713967</v>
       </c>
       <c r="Q11" t="n">
         <v>6.399880963592059</v>
       </c>
       <c r="R11" t="n">
-        <v>6.586537518806132</v>
+        <v>6.586537518806129</v>
       </c>
       <c r="S11" t="n">
-        <v>6.464540911440225</v>
+        <v>6.464540911440222</v>
       </c>
       <c r="T11" t="n">
-        <v>6.453291113019322</v>
+        <v>6.453291113019318</v>
       </c>
       <c r="U11" t="n">
-        <v>6.360767927668346</v>
+        <v>6.360767927668347</v>
       </c>
       <c r="V11" t="n">
         <v>6.551595313183204</v>
       </c>
       <c r="W11" t="n">
-        <v>6.193525308985479</v>
+        <v>6.193525308985481</v>
       </c>
       <c r="X11" t="n">
-        <v>6.161036366423027</v>
+        <v>6.161036366423025</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.087301497709775</v>
+        <v>6.087301497709776</v>
       </c>
       <c r="Z11" t="n">
         <v>6.360103425293167</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.285241486293452</v>
+        <v>6.285241486293454</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.226885439856733</v>
+        <v>6.226885439856731</v>
       </c>
     </row>
   </sheetData>
